--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1205,7 +1205,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Selecting locations scopes the report data; All locations includes every accessible location</t>
+          <t>Selecting locations scopes the data; All locations covers every accessible one</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1233,19 +1233,21 @@
         <is>
           <t>1. Select only location A in the location filter and note the customers/totals.
 2. Select locations A and B together and note the change.
-3. Select "All locations."</t>
+3. Select "All locations."
+4. With "All locations" active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
-3. With "All locations," the report includes data from every location the user has access to.</t>
+3. With "All locations," the report includes data from every location the user has access to.
+4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 4 S4-R5; S4-R6</t>
+          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -2310,7 +2312,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Asset label = year make model plus the most specific identifier: Unit, then plate, then last 8 of VIN</t>
+          <t>Asset label = year make model plus the serial number as the identifier</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2330,7 +2332,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1. One customer has four ZZAUTOTEST assets with invoices in range: (a) one with a unit number, (b) one with a plate but no unit, (c) one with only a VIN of 8+ characters, (d) one with only a VIN shorter than 8 characters.</t>
+          <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a serial number recorded, (b) one with no serial number.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2341,16 +2343,13 @@
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Every label starts with the vehicle's year, make, and model.
-2. Asset (a) adds " · Unit {unit}".
-3. Asset (b) adds " · {plate}".
-4. Asset (c) adds " · VIN …" followed by the last 8 characters of the VIN.
-5. Asset (d) shows the whole VIN after " · VIN …" (shorter than 8).
-6. An asset with none of unit/plate/VIN gets no suffix at all.</t>
+2. Asset (a) shows its SERIAL NUMBER after the year/make/model as the identifier.
+3. For asset (b) (no serial number), note what the label shows instead — what stands in when the serial number is missing is confirmed in the build (the older wording used the unit number, then the plate, then the last 8 of the VIN).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2394,7 +2393,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R9</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R9)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2438,7 +2437,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R10</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R10)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2447,7 +2446,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Two assets producing the same label get stable (#1)/(#2) suffixes that survive reloads</t>
+          <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2485,7 +2484,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R11</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R11)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3491,7 +3490,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>The overflow menu holds Download (CSV), Download (PDF) and Print in that order, with no separate export buttons</t>
+          <t>The overflow menu holds only Download (CSV) and Download (PDF) — no Print item</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3524,13 +3523,13 @@
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
-2. The menu items read, in order: "Download (CSV)", "Download (PDF)", "Print" (Print is the third item).
+2. The menu items read, in order: "Download (CSV)", "Download (PDF)" — and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons — all exports live behind this one menu.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R1; S14-R2; Story 15 S15-R1; S15-R2; Story 16 S16-R1; S16-R2; Story 20 S20-R16</t>
+          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — the 'Print' third menu item REMOVED per kickoff video P25 31:14, overriding Story 16 / SV-8614, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4114,7 +4113,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>An export over 10,000 data rows is refused with the too-large toast — no file downloads and no print dialog opens</t>
+          <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4141,13 +4140,12 @@
         <is>
           <t>1. With the over-cap filter set, choose "Download (CSV)".
 2. Choose "Download (PDF)".
-3. Choose "Print".
-4. Narrow the filters below the cap and re-try one export.</t>
+3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. For each of CSV, PDF, and Print: no file is generated, no download starts, and no print dialog opens.
+          <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This export is too large to generate. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
 4. Below the cap the export succeeds normally.</t>
@@ -4155,7 +4153,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; Story 16 S16-R6; §7</t>
+          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4210,84 +4208,132 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>The download menu also offers a compressed (summary) version of the report</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the download (overflow) menu and read the options.
+2. Download the compressed (summary) version and open the file.
+3. Download the expanded (full, nested) version and compare the two files.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. Besides the existing expanded (nested) download, the menu offers a compressed (summary) download option. (The exact menu wording is confirmed in the build.)
+2. The compressed file gives one summary line per customer, without the per-invoice detail rows. (The exact file shape is confirmed in the build once the spec update lands.)
+3. The expanded download still contains the full nested detail, and both files reflect exactly the filtered data shown on screen.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>SV-8582 (EPIC-LEVEL, stated explicitly: no child story exists yet for the SBC compressed download — kickoff video P21 32:10-33:03 + 48:39, user ruling 2026-07-28; overrides the current spec's single flat export, S14-R6; S14-R10; S15-R16)</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
           <t>Filters, sort and visible columns are saved and restored on the next visit, shown immediately without a default flash</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved; a reload clears all expansion</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -4295,141 +4341,141 @@
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is discarded and that setting falls back to its default</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R7</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month.
 2. Product Type = "Parts &amp; Service."
@@ -4439,135 +4485,135 @@
 6. All nine toggleable columns visible.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-N1</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>When both a saved view and a page-link range exist, the saved view wins and the link value is ignored</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R9</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: the all-customers state restores as all (including new customers); an id set is intersected and never forces an empty view</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>No matching data shows the empty-state message in the table body while the toolbar stays interactive</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -4575,7 +4621,7 @@
 4. Look at the table header row's chevron.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -4583,181 +4629,181 @@
 4. The header-row chevron is hidden when the table has no visible rows.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>The empty-state message never appears while the table is still loading</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Change a filter and watch the table area during the load.
 2. Watch what appears once loading finishes with zero customers.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
 2. The message appears only after the table finishes its initial loading and shows zero customers.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 17 S17-N1</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>A narrowed customer selection with no data shows the empty state but the selection is kept and the customers reappear</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter is narrowed to specific customers who have data in the current range but none in an adjacent range.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range so that none of the selected customers have data.
 2. Read the table and the Customer filter.
 3. Change the range back.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The empty-state message is shown.
 2. The Customer filter selection is kept (not cleared).
 3. When the filters change back to a range where the selected customers have data, they reappear.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 17 S17-E1</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the fetching-error toast which auto-fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md §7 User Feedback Summary</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme: paddings, surfaces, alignment, separator, arrow size and square corners</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser with dev tools available.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the page background, toolbar surface, and paddings with dev tools.
 2. Check the toolbar's position against the top of the page and the table against the side edges.
@@ -4765,7 +4811,7 @@
 4. Check the line between the toolbar and the headers, the date-range picker's dropdown arrow size, the table corners, and the outermost cell paddings.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The page has no padding; the page background is the standard blue-grey (#f9fafb in light mode).
 2. The toolbar surface is white (#ffffff); its padding is 32px top, 24px bottom, and 2rem left and right; it touches the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4776,48 +4822,48 @@
 7. When the table content does not fill the viewport, the blue-grey page background shows through below the table — no white strip.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level: white header/customer/totals rows, blue-grey asset/invoice rows, pinned Subtotal matching its row</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4826,183 +4872,183 @@
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Dark mode swaps every surface for its dark equivalent while the PDF always renders in light-mode colors</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R18</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch and below 1024px the toolbar splits into two rows</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with the Subtotal pinned, chevrons toggle, and invoice links open in the same tab</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>A customer's asset and invoice rows are fetched from the server only on first expand, and expand-all fetches at most one request per visible customer</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -5010,209 +5056,209 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server: a header click re-fetches the customer rows ordered by that column as a fresh first page</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
 3. The ordering is not done by re-shuffling rows already in the browser.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>The Customer filter's type-ahead fetches matching customers from the server per query instead of loading the full list up front</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated and the totals row is server-computed over the full filtered set</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Exports are generated on the server and the 10,000-row cap is counted server-side before any file is produced</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22; Story 16 S16-R6</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sales By Customer appears in the Reports navigation and opens the report</t>
+          <t>Sales By Customer appears in Reports navigation and opens with correct titles</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -518,18 +518,21 @@
         <is>
           <t>1. Open the Reports area from the main navigation.
 2. Look through the Reports left-side navigation for the report entry.
-3. Click the "Sales By Customer" entry.</t>
+3. Click the "Sales By Customer" entry.
+4. Read the page title at the top of the report and the browser tab's title.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. "Sales By Customer" is listed in the Reports left-side navigation.
-2. Clicking it opens the Sales By Customer report in the main content area.</t>
+2. Clicking it opens the Sales By Customer report in the main content area.
+3. The page title reads "Sales By Customer."
+4. The browser tab title reads "Sales By Customer - Report | ShopView".</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 1 S1-R1</t>
+          <t>specs/sbc-sales-by-customer.md Story 1 S1-R1; S1-R3; S1-R4</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -538,12 +541,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Page title and browser tab title read Sales By Customer</t>
+          <t>A user with the dedicated Sales By Customer View permission can see and open the report</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SBC — Access &amp; Navigation</t>
+          <t>SBC — Permissions</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -553,216 +556,169 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in with the Sales By Customer report View permission.
-2. You have opened the Sales By Customer report.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the page title shown at the top of the report.
-2. Read the browser tab's title.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. The page title reads "Sales By Customer."
-2. The browser tab title reads "Sales By Customer - Report | ShopView".</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 1 S1-R3; S1-R4</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>A user with the dedicated Sales By Customer View permission can see and open the report</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Permissions</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role has the dedicated Sales By Customer report View permission (create a ZZAUTOTEST custom role if needed).
 2. You are signed in as that user.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area.
 2. Click "Sales By Customer" in the left-side navigation.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
 3. Access is granted by the dedicated Sales By Customer permission itself — the report is not tied to a generic "all reports" permission.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 1 S1-R2</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>A user without the Sales By Customer View permission cannot see or open the report</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>SBC — Permissions</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. A test user exists whose role does NOT have the Sales By Customer report View permission (use/create a ZZAUTOTEST role).
 2. You know the report's direct page address (copy it from a permitted session first).
 3. You are signed in as the unpermitted user.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area and look through the left-side navigation.
 2. Paste the report's direct page address into the browser and try to open it.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 1 S1-N1</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Opening an invoice you lack permission for shows the standard access-denied state and back returns to the report</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>SBC — Permissions</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user who can view the report but lacks permission to open the underlying invoice destination.
 2. The report shows at least one customer; you have expanded down to an invoice detail row.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Click the invoice number link on a detail row.
 2. Look at the destination page.
 3. Press the browser back button.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-N2</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Location access is enforced: the report never includes data from a location the user cannot access</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Location access enforced: no data from a location the user cannot access</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SBC — Permissions</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. The organization has at least two locations, each with invoices in the chosen date range (seed ZZAUTOTEST data if needed).
 2. A non-administrator test user is assigned to only ONE of the locations.
 3. An administrator account is also available.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the administrator, open the report, and open the location filter — note the locations listed.
 2. Sign in as the non-administrator, open the report, and open the location filter — note the locations listed.
-3. As the non-administrator, attempt to request a location you are not assigned to (for example by editing the page link if the location is carried there, or any other means available).
+3. As the non-administrator, attempt to request a location you are not assigned to by these routes: (a) edit the page link (URL) if the location selection is carried there, and open the edited link; (b) restore a saved view stored while an extra location was assigned (set that saved view up first if practical).
 4. Check the report data.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. The administrator's filter lists every location in the organization.
 2. The non-administrator's filter lists only the locations assigned to them.
@@ -770,377 +726,242 @@
 4. The report data never includes invoices from a location the user does not have access to.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 4 S4-R7; S4-R8; S4-R9; S4-N1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Date range picker offers eleven options in the specified order</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>SBC — Date Range Filter</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Find the date range picker in the report toolbar.
 2. Open it and read the options from top to bottom.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R1; S2-R2</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Date range defaults to This Month when nothing is saved and no range is in the page link</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Custom range opens a start/end date dialog and cannot exceed a 366-day span</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>SBC — Date Range Filter</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1. Your browser has no saved view for this report (first visit, or clear the browser's site data first).
-2. You open the report by its plain address with no date range in the page link.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Sales By Customer report.
-2. Read the date range picker's current value.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. The date range picker shows "This Month."</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 2 S2-R5</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Custom range opens a start/end date dialog and cannot exceed a 366-day span</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Date Range Filter</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Open the date range picker and choose "Custom."
 2. In the dialog that opens, pick a start and end date less than 366 days apart and apply.
 3. Open "Custom" again and try to pick a start and end date MORE than 366 days apart.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Choosing "Custom" opens a date-picker dialog for a start and end date.
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R3; S2-R4; S2-N2</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Changing the date range writes the chosen value to the page link for sharing and bookmarking</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>SBC — Date Range Filter</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range (for example to "Last Month").
 2. Look at the browser's address bar.
 3. Copy the page link, open it in a fresh browser profile with no saved view for this report, and check the date range.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R6; S2-R9 (context)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Product Type dropdown offers exactly three options with Parts &amp; Service as the default</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Product Type: three options with Parts &amp; Service default; S/P prefix filtering</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SBC — Product Type Filter</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Sales By Customer report with no saved view (first visit or cleared browser storage).</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Find the "Product Type" dropdown in the report toolbar.
-2. Read its current value before touching it.
-3. Open it and read the options in order.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. A "Product Type" dropdown is visible in the report toolbar.
-2. The default selection on first load is "Parts &amp; Service."
-3. It offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only."</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Service only shows only invoices starting with S; Parts only shows only invoices starting with P</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Product Type Filter</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Sales By Customer report with no saved view (first visit or cleared browser storage), so the first-load default can be read.
+2. The date range contains at least one service invoice (number starting with S) and one parts invoice (number starting with P) — seed ZZAUTOTEST data if needed.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the "Product Type" dropdown in the report toolbar; read its value before touching it, then open it and read the options in order.
+2. Set Product Type to "Service only," expand a customer down to invoice rows, and read the invoice numbers.
+3. Set Product Type to "Parts only" and read the invoice numbers again.
+4. Set Product Type back to "Parts &amp; Service."</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
+2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
+3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
+4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
+5. The whole invoice is classified by its number prefix — there is no per-line-item split.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Location filter is the rightmost filter, lists accessible locations, and pins All locations to the top</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Location Filter</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Sales By Customer report.
-2. The date range contains at least one service invoice (number starting with S) and one parts invoice (number starting with P) — seed ZZAUTOTEST data if needed.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Set Product Type to "Service only," expand a customer down to invoice rows, and read the invoice numbers.
-2. Set Product Type to "Parts only" and read the invoice numbers again.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
-2. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
-3. The whole invoice is classified by its number prefix — there is no per-line-item split.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 3 S3-R5; S3-R6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Parts &amp; Service applies no product-type filter</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Product Type Filter</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Sales By Customer report with both S and P invoices in the date range.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Set Product Type to "Parts only" and note the visible customers/totals.
-2. Set Product Type back to "Parts &amp; Service."</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included again and counts/totals cover both.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 3 S3-R4</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Location filter is the rightmost filter, lists accessible locations, and pins All locations to the top</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Location Filter</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report as a user with access to two or more locations.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Look at the report toolbar's filters from left to right.
 2. Open the location filter and read its options.
 3. Click the "All locations" option, then click it again.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. The location filter is the rightmost filter in the toolbar.
 2. It lists the locations the signed-in user has access to.
@@ -1148,88 +969,42 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 4 S4-R1; S4-R2; S4-R3</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Location filter defaults to the user's active location on first load</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Selecting locations scopes the data; All locations covers every accessible one</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1. Your browser has no saved view for this report.
-2. You are working in a known active location (check the application's location switcher).</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Sales By Customer report.
-2. Read the location filter's current selection.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. The filter defaults to the single location you are currently working in (your active location) — not all locations.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 4 S4-R4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Selecting locations scopes the data; All locations covers every accessible one</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Location Filter</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. At least two accessible locations each have invoices in the chosen date range (seed ZZAUTOTEST data if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A in the location filter and note the customers/totals.
 2. Select locations A and B together and note the change.
@@ -1237,7 +1012,7 @@
 4. With "All locations" active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
@@ -1245,48 +1020,48 @@
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Customer filter sits between Product Type and Location, carries a search icon, and shows the Search customers… hint</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer in the current results.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar filters from left to right.
 2. Open the Customer filter without typing anything.
 3. Read what the dropdown shows before any query is typed.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
@@ -1294,187 +1069,191 @@
 4. The hint yields to the typed query while you are searching.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Typing in the Customer filter lists matching customers by contains match, with checkmarks on selected ones</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. At least two customers with distinct names have invoices in the current date range/Product Type/location (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and type a fragment from the MIDDLE of a customer's name, in different letter case (for example type "corp" for "Acme Corp").
 2. Read the list of customers shown.
 3. Click one listed customer to select it and look at its row in the dropdown.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R2</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Pinned control toggles between All customers and Clear all with the matching action</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Pinned control toggles All customers and Clear all; clearing shows empty state</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with several customers in the current results.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter while it is in the all-customers state and read the pinned control at the top of the dropdown.
-2. Activate it.
+2. Activate it ("Clear all") and read the table body, the totals row, and the filter's collapsed label.
 3. Read the pinned control again and activate it once more.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
-3. The control is pinned to the top of the dropdown in both states.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R3</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+3. The control is pinned to the top of the dropdown in both states.
+4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>First load starts in the all-customers state and the report shows every customer</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. Your browser has no saved view for this report.
-2. Several customers have invoices in the default date range.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+2. Several customers have invoices in the default date range.
+3. A customer exists that has invoices ONLY in a wider date range than the current one (seed a ZZAUTOTEST invoice dated last month if needed).</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read the Customer filter's collapsed label.
-3. Check the customer rows shown.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+3. Check the customer rows shown.
+4. Widen the date range so the customer with no matching invoices now has one; re-check the label and the rows.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
-3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
+4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Collapsed label reads None, the customer's name, or N selected, and shows the query text while typing</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and use "Clear all" to empty the selection; read the collapsed label.
 2. Select exactly one customer; read the collapsed label.
@@ -1482,7 +1261,7 @@
 4. Start typing a search query in the filter field and watch the field text, then clear the query or click away.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
@@ -1490,191 +1269,96 @@
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R5</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Changing the customer selection narrows the table to the selected customers and refreshes the totals</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Note the customers and the totals row values.
 2. Open the Customer filter, clear all, and select exactly two customers.
 3. Read the table rows and the totals row.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Clearing every customer shows the empty state with a zero totals row</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>A subset selection reconciles on a filter change: kept if present, dropped if absent, new customers not auto-added</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Sales By Customer report with data on screen.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Customer filter and activate "Clear all" so no customer is selected.
-2. Read the table body and the totals row.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1. The report shows the empty-state message "No sales data found for the selected filters."
-2. The totals row shows zeros.
-3. The Customer filter's collapsed label reads "None."</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-N1; S17-E1</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>In the all-customers state a filter change keeps every customer included, including newly-appearing ones</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Customer Filter</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report in the all-customers state.
-2. A customer exists that has invoices ONLY in a wider date range than the current one (seed a ZZAUTOTEST invoice dated last month if needed).</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. With the current (narrow) date range, confirm that customer is not shown.
-2. Widen the date range so that customer's invoice now matches.
-3. Check the table and the Customer filter label.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1. The filter stays in the all-customers state (label still "All customers").
-2. Every customer matching the new filters is included — including the newly-present customer, without any manual re-selection.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R9; S18-E1</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>A subset selection reconciles on a filter change: kept if present, dropped if absent, new customers not auto-added</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Customer Filter</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with three customers A, B, C where: A has invoices in both this month and last month; B has invoices only in this month; C has invoices only in last month (seed ZZAUTOTEST data as needed).
 2. Date range is This Month; you have selected exactly customers A and B in the Customer filter.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range to Last Month.
 2. Read the table rows and the Customer filter selection.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
@@ -1682,49 +1366,49 @@
 4. The Customer filter selection itself is not cleared by the date change.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Each customer gets one summary row with its name followed by the invoice count in parentheses</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. A customer has a known number of matching invoices in the current date range (seed ZZAUTOTEST data so the count is predictable).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Find that customer's row at the top level of the table.
 2. Read the text at the start of the row.
 3. Narrow the date range so fewer of that customer's invoices match, and re-read the count.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
@@ -1732,512 +1416,469 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>A customer with no matching invoices in the current view is not shown</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose invoices all fall OUTSIDE the current date range (seed if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains none of that customer's invoices.
 2. Look for the customer in the table.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-N1</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Expanding a customer reveals its asset rows with vehicle icon, label, count, rolled-up columns and indentation</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Expanding a customer reveals asset rows; chevrons toggle and are independent</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1. A customer in the current view has invoices on at least two different vehicles (seed ZZAUTOTEST work orders on two assets if needed).</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Click the chevron control on that customer's summary row.
-2. Read the rows that appear beneath the summary row.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1. A customer in the current view has invoices on at least two different vehicles (seed ZZAUTOTEST work orders on two assets if needed).
+2. At least two customers with assets are in the current view.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Click the chevron control on customer A's summary row and read the rows that appear beneath it.
+2. Expand one of customer A's assets, then expand customer B.
+3. Click customer A's chevron again and check customer B.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
 3. Each asset row shows the same financial columns as the customer row, rolled up for that asset.
 4. The Date cell is blank on asset rows.
-5. Asset rows are indented one level under the customer.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+5. Asset rows are indented one level under the customer.
+6. Each chevron toggles back to collapsed on a second activation.
+7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Expanding an asset reveals its invoice detail rows with number link, date and per-invoice columns</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded a customer and can see its asset rows.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron on an asset row.
 2. Read the invoice detail rows that appear.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Invoices group into one asset row per vehicle record, with a snapshot fallback for older invoices with no vehicle id</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. A customer has two or more invoices on the SAME vehicle record and at least one invoice on a different vehicle (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer.
 2. Count the asset rows and compare each asset's invoice count with the invoices you created.
 3. If the environment has an older invoice with no vehicle record linked (only a stored vehicle snapshot), check which asset row it lands under.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Asset rows order A to Z case-insensitively with the Parts Sales bucket always last, regardless of column sort</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. A customer has invoices on at least two vehicles AND at least one no-vehicle invoice (counter/parts sale) in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the asset rows top to bottom.
 2. Click a financial column header to change the table sort, and re-read the asset rows.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Chevrons toggle closed on a second click and every customer's and asset's expansion is independent</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Header-row chevron expands or collapses every customer on the current page, with matching icon and tooltip</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>1. At least two customers with assets are in the current view.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Expand customer A, then expand one of its assets.
-2. Expand customer B.
-3. Click customer A's chevron again.
-4. Check customer B.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>1. Each chevron toggles back to collapsed on a second activation.
-2. Collapsing customer A does not affect customer B's expansion.
-3. Each asset's expansion state is likewise independent.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R15</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Header-row chevron expands or collapses every customer on the current page, with matching icon and tooltip</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Tree &amp; Rows</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. Several customers are visible on the current page.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Hover the chevron in the table header row and read the tooltip.
 2. Click it and watch the customer rows.
 3. Hover it again and read the tooltip, then click it again.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Any change that reloads customer rows collapses all expansion, but typing in the Customer filter does not</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Reload-causing changes collapse expansion; Customer filter typing does not</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with at least one customer expanded down to invoice rows.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with at least one customer expanded down to invoice rows.
+2. Enough customers exist to fill more than one page of results (seed ZZAUTOTEST customers if needed).</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. With rows expanded, open the Customer filter and TYPE a search query (do not change the selection); watch the expanded rows.
 2. Now change the date range (or Product Type, location, Customer selection, or sort).
-3. Look at the previously expanded rows.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+3. Look at the previously expanded rows, the loading state, and the set of customers on the page.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
-2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
+3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Edge: a single-invoice asset can still be expanded, and a customer with only no-vehicle work shows a single Parts Sales row</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Customer A has an asset with exactly one invoice; customer B has ONLY no-vehicle (counter/parts sale) invoices in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Expand customer A and click the chevron of the single-invoice asset.
 2. Expand customer B and read its asset rows.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket — absence of a vehicle decides, not the prefix</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. A customer has an invoice whose number starts with S but whose work order has NO vehicle (seed a ZZAUTOTEST no-vehicle service work order and invoice it, if the app allows).</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Expand that customer.
 2. Find which asset row the S invoice sits under.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-E3</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Reversed and voided invoices are excluded from every row, count and total under every Product Type</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. A customer has a known set of invoices in the current range, one of which you then reverse (or void) — seed ZZAUTOTEST data and note the totals before and after.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Note the customer's invoice count "(N)" and totals with all invoices normal.
 2. Reverse (or void) one of the invoices in the application.
@@ -2245,55 +1886,55 @@
 4. Expand down to invoice rows and look for the reversed invoice.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Every row type renders the same columns in the same order, blank cells keep their position, and summary rows use the specified font weights</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a customer expanded down to invoice rows and the totals row visible.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
 3. Inspect the font weights on a customer summary row (dev tools).</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
@@ -2301,324 +1942,238 @@
 4. Every cell on a customer summary row uses font-weight 600, except the Subtotal cell which uses font-weight 700.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Asset label = year make model plus the serial number as the identifier</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Asset label = year make model + serial number, with missing-data fallbacks</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a serial number recorded, (b) one with no serial number.</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a serial number recorded, (b) one with no serial number, (c) one with a VIN but no year, make, or model, (d) one with no year, make, model, or VIN (blank the fields as far as the asset form allows).</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read each asset row's label.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1. Every label starts with the vehicle's year, make, and model.
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. Labels for assets that have them start with the vehicle's year, make, and model.
 2. Asset (a) shows its SERIAL NUMBER after the year/make/model as the identifier.
-3. For asset (b) (no serial number), note what the label shows instead — what stands in when the serial number is missing is confirmed in the build (the older wording used the unit number, then the plate, then the last 8 of the VIN).</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>An asset with no year, make or model is labeled with the VIN on its own</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+3. For asset (b) (no serial number), note what the label shows instead — what stands in when the serial number is missing is confirmed in the build (the older wording used the unit number, then the plate, then the last 8 of the VIN).
+4. Asset (c) (no year/make/model) is labeled with the VIN on its own.
+5. Asset (d) (no year/make/model/VIN) is labeled "Unknown Asset."</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28; S8-R9; S8-R10 fallback rules kept)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1. A ZZAUTOTEST asset exists with a VIN but no year, make, or model, and has an invoice in range.</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Expand the owning customer and read that asset row's label.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1. The label is the VIN on its own (no year/make/model base, no "VIN …" suffix form).</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R9)</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>An asset with no year, make, model or VIN is labeled Unknown Asset</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Asset Labels</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1. A ZZAUTOTEST asset exists with no year, make, model, or VIN, and has an invoice in range (if the app's asset form forces a value, blank the fields as far as it allows).</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1. Expand the owning customer and read that asset row's label.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1. The label reads "Unknown Asset."</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R10)</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Asset Labels</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. One customer has TWO ZZAUTOTEST assets whose labels come out identical (same year/make/model and same identifier situation), each with an invoice in range.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the two asset labels.
 2. Note which asset carries " (#1)" and which " (#2)".
 3. Reload the page and expand again.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R11)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Invoice number opens in the same tab: S invoices to the work order Finance tab, P invoices to the part sale Part Requests tab</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded an asset and can see at least one S invoice and (under another customer/asset if needed) one P invoice.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Click a service (S) invoice number link and note where it opens.
 2. Go back, then click a parts (P) invoice number link and note where it opens.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Browser back from an invoice returns to the report with filters, sort and columns restored and rows collapsed</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with non-default filters set (for example Last Month + Service only), a non-default sort, and one column hidden.
 2. You have expanded down to an invoice detail row.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Watch the browser address bar, then click an invoice number link.
 2. From the invoice page, press the browser back button.
 3. Check the report's filters, sort, visible columns, and row expansion.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Customer name is plain text; the invoice link keeps the primary color with no underline and never turns visited-purple</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded down to invoice detail rows and have already clicked at least one invoice link earlier in the session.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Try clicking the customer NAME on a summary row.
 2. Look at an invoice number link at rest, on hover, and one you have already visited.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
@@ -2626,420 +2181,284 @@
 4. The link never recolors to the browser's visited-link (purple) color.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Clicking an invoice deleted or reversed after the report loaded shows the standard not-found state and back returns</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with an invoice detail row visible.
 2. In another tab/session, that invoice is deleted or reversed AFTER the report loaded (do not refresh the report).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Back in the report (unrefreshed), click that invoice's number link.
 2. Read the destination page, then press the browser back button.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-N1</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Every column is sortable except the chevron column; text sorts alphabetically and numbers by value</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>All columns sortable except chevron; text alphabetical, numbers by value</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1. Several customers with differing values are in the current view.</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1. Several customers with differing values are in the current view.
+2. A customer with multiple assets and invoices is in the view.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
-3. Compare a text sort (Customer) and a numeric sort (Subtotal) against the values.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+3. Compare a text sort (Customer) and a numeric sort (Subtotal) against the values.
+4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Every column is sortable except the chevron column.
-2. Text columns sort alphabetically; numeric columns sort by value (not as text).</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+2. Text columns sort alphabetically; numeric columns sort by value (not as text).
+3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Default sort is Customer name ascending case-insensitive; clicking a header replaces it</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. No saved view exists (first visit or cleared storage).
 2. Customer names with mixed upper/lower-case first letters exist in the view (seed ZZAUTOTEST names like "acme test" and "Best Test").</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the customer order.
 2. Click the Subtotal header and read the order again.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Missing values sort to the bottom ascending and to the top descending; a Margin % em dash counts as missing</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer row shows an em dash (—) in Margin % (Subtotal zero or below — seed a zero-subtotal case if possible) alongside rows with real Margin % values.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Margin % ascending and note where the em-dash row lands.
 2. Sort by Margin % descending and note it again.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R3</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sorting by Date orders customers by their most recent invoice date even though the Date cell is blank on customer rows</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. Two customers exist whose most recent invoice dates differ clearly (seed ZZAUTOTEST invoices on different dates).</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date column header.
 2. Compare the customer order with each customer's most recent invoice date (expand to check the invoice dates).</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Sorting reorders only the customer summary rows; asset and invoice ordering is untouched</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Sorting</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1. A customer with multiple assets and invoices is in the view.</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Sort by Subtotal descending.
-2. Expand a customer and an asset; read the asset order and the invoice order.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>1. Only the customer summary rows are reordered by the sort.
-2. Asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R6</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Changing the sort shows the loading state, collapses expanded rows, and can change which customers are on the page</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Sorting</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>1. Enough customers exist to fill more than one page of results (seed ZZAUTOTEST customers if needed).
-2. At least one customer is expanded.</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>1. Click a column header to change the sort and watch the table.
-2. When the new order arrives, check the previously expanded rows and the set of customers on the page.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1. While the re-fetch is in flight the table shows the standard loading state; it clears when the re-ordered page arrives.
-2. All previously expanded customer rows are collapsed (assets/invoices re-fetch lazily on the next expand).
-3. The page shows the first page of the newly ordered full set — the customers on the page can change.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R8a; S10-R8b; S10-R8c</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>With no customer rows the sort headers are still present and produce no visible change</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Sorting</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>1. The current filters produce no matching customers (the empty state is showing).</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Click several column headers.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>1. The sort controls on the headers are still present.
-2. Clicking them produces no visible change (the empty state remains).</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-N1</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Financial columns appear in the specified order and Subtotal/Margin follow the spec's composition rules</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known labor, parts, and shop-supply amounts and known costs, in the current range.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Expand down to that invoice's detail row and read its values.
 3. Recalculate Subtotal and Margin by hand from the known amounts.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
@@ -3047,48 +2466,48 @@
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Margin % = Margin over Subtotal to one decimal with a percent sign, em dash when Subtotal is zero or below, monochrome on all row types</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Rows with a normal positive Subtotal exist, and (if seedable) one row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on a customer row, an asset row, and an invoice row; recalculate one by hand (Margin ÷ Subtotal × 100).
 2. Find (or seed) a row with Subtotal ≤ 0 and read its Margin % cell.
 3. Look at the Margin % coloring.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
@@ -3096,47 +2515,47 @@
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim and the value shows +green / -red / 0.0 default on every row type</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist where billed hours exceed worked hours, where worked exceeds billed, and where they are equal (seed ZZAUTOTEST work orders with clocked time).</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
@@ -3146,143 +2565,143 @@
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is never blank: no-labor rows show 0.0 and values that round to zero show 0.0 in the default color</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice (no labor at all) exists in range; if possible also an invoice whose delta rounds to zero (for example +0.04).</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
 2. If seeded, read the near-zero row's Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Invoice subtotals sum exactly to their asset row and asset subtotals sum exactly to the customer row</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. A customer with two or more assets, each with two or more invoices, is in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and every asset.
 2. Sum the invoice-level values by hand for each column and compare with each asset row.
 3. Sum the asset rows and compare with the customer row.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R13</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Subtotal is the rightmost column, pinned during horizontal scroll and bold everywhere, unconditionally</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, on a window narrow enough to force horizontal scrolling (or with all columns visible).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Subtotal column is the last column on the right.
 2. Scroll the table sideways and watch the Subtotal column.
 3. Inspect the font weight of the Subtotal header, a customer row, an asset row, an invoice row, and the totals row.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
@@ -3290,95 +2709,95 @@
 4. This holds regardless of permission, data, filters, or sort — the Subtotal column is always present, pinned, and bold.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>The totals row covers the full filtered set of customers, not only the customers on the current page</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page of results, with known amounts (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read the totals row on page 1.
 2. Move to page 2 and read the totals row again.
 3. Compare the totals against the sum over ALL matching customers (not just one page).</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R6</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Column selector is a separate toolbar button with the Column Selection tooltip and nine toggles in order, all on by default</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no saved column selection (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector button in the toolbar's action area, next to the overflow menu.
 2. Hover it and read the tooltip.
 3. Click it and read the toggle list top to bottom.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
@@ -3386,237 +2805,194 @@
 4. With no saved selection, all nine toggleable columns default to visible.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>A toggle hides the column's header and cells together; Customer, Subtotal and the chevron column are never in the list</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Column toggles hide header+cells; Customer, Subtotal and chevron never in list</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data and the column selector open.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Turn the "Shop Supplies" toggle off, then on again, watching the table.
-2. Read the toggle list for Customer, Subtotal, or a chevron entry.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+2. Read the toggle list for Customer, Subtotal, or a chevron entry.
+3. Turn all nine toggles off and read the table.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
-2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Hiding all nine toggleable columns is allowed and the table still shows Customer, Subtotal and the totals Subtotal</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Column Selector</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data.</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the column selector and turn all nine toggles off.
-2. Read the table.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>1. All nine columns can be hidden — nothing blocks the last toggle.
-2. The table still renders the Customer and Subtotal columns.
-3. The totals row still shows its Subtotal.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 13 S13-N1</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
+3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>The overflow menu holds only Download (CSV) and Download (PDF) — no Print item</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download (CSV)", "Download (PDF)" — and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons — all exports live behind this one menu.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — the 'Print' third menu item REMOVED per kickoff video P25 31:14, overriding Story 16 / SV-8614, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CSV download is a plain .csv file named by the active date range per the filename map</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CSV and PDF downloads are named by the active date range per the filename map</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Set the range to This Month and choose "Download (CSV)"; note the downloaded filename.
 2. Repeat for at least Today, Last Quarter, and a Custom range.
-3. Open a downloaded file in a text editor and in a spreadsheet.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
+3. Open a downloaded file in a text editor and in a spreadsheet.
+4. Repeat steps 1-2 choosing "Download (PDF)" and note the filenames.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The filename follows the range map: Today → sales-by-customer-today.csv; Yesterday → sales-by-customer-yesterday.csv; This Week → sales-by-customer-this_week.csv; Last Week → sales-by-customer-last_week.csv; This Month → sales-by-customer-this_month.csv; Last Month → sales-by-customer-last_month.csv; This Year → sales-by-customer-this_year.csv; Last Year → sales-by-customer-last_year.csv; This Quarter → sales-by-customer-this_quarter.csv; Last Quarter → sales-by-customer-last_quarter.csv; Custom → sales-by-customer-custom.csv.
 2. For Custom the literal word "custom" is used — the actual start/end dates are not in the filename.
-3. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R4; S14-R5</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+3. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
+4. The PDF download follows the same range-to-filename map with a .pdf extension — for example, sales-by-customer-this_month.pdf, sales-by-customer-custom.pdf.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 14 S14-R4; S14-R5; Story 15 S15-R4</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>CSV has twelve columns in exact order, is flat (customer then invoice rows), and follows the blank-cell rules</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The CSV has twelve columns in this exact order: Customer, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
 2. On customer rows the Invoice # and Date cells are blank.
@@ -3625,47 +3001,47 @@
 5. The CSV is flat — Customer then Invoice rows; the on-screen asset layer is NOT represented (this is per spec, not a defect).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 14 S14-R6; S14-R7; S14-R8; S14-R9; S14-R10 (context note)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>CSV value formats: Margin % plain number, dates mm-dd-yyyy, currency plain numbers, no color</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
@@ -3673,232 +3049,189 @@
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 14 S14-R10; S14-R11; S14-R12; S14-R13</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF contain exactly the customers matching the active filters and sort, including the Customer filter selection</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CSV action shows a loading state while exporting and a CSV export failed toast on failure</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CSV and PDF actions show a loading state and their own export failed toast</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a large enough data set that the export takes a visible moment.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and immediately look at the menu action.
-2. To provoke a failure, disconnect the network (or use browser dev tools offline mode) and choose "Download (CSV)" again.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>1. While the export is in progress, the menu's CSV action shows a loading state and is non-interactive.
-2. If the export fails, an error toast is shown: "CSV export failed." (dismissed by the user).</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-E1; S14-N1; §7</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>PDF download uses the same range-based filename map with a .pdf extension</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+2. To provoke a failure, disconnect the network (or use browser dev tools offline mode) and choose "Download (CSV)" again.
+3. Repeat both checks for "Download (PDF)".</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1. While an export is in progress, that menu action shows a loading state and is non-interactive (CSV and PDF alike).
+2. If the CSV export fails, an error toast is shown: "CSV export failed." (dismissed by the user).
+3. If the PDF export fails, the toast reads "PDF export failed." — identical behavior, different wording.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data.</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>1. Set the range to This Month and choose "Download (PDF)"; note the filename.
-2. Repeat for one other preset and a Custom range.</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>1. The file follows the same range-to-filename map as the CSV, with a .pdf extension — for example, sales-by-customer-this_month.pdf, sales-by-customer-custom.pdf.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 15 S15-R4</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>PDF page is A4 landscape with 25px margins and a footer with the ShopView label and page numbers</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Exports</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>1. The PDF is A4 landscape with 25px margins on all sides, using the application's standard font.
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 15 S15-R5; S15-R6</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>PDF header shows the title, organization, date range in Mon D, YYYY form and the Product Type line; location is not shown</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows, in order: the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3906,48 +3239,48 @@
 4. The location filter is NOT shown in the header; it scopes the data only.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion, and falls back from the uploaded logo to the ShopView logo to none</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With no uploaded logo, the bundled ShopView logo is used.
@@ -3955,47 +3288,47 @@
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 15 S15-R12; S15-R13; S15-R14; S15-R15</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>PDF body matches the CSV's twelve flat columns with on-screen date/dash/bold rules and exact Inv. Hrs colors</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Read the body table's columns and row structure.
 2. Check a date cell, a customer row's Date cell, a Margin % dash, the Subtotal column weight, and the Inv. Hrs colors (use a color picker on the PDF if available).</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The body table has twelve columns in the same exact order and labels as the CSV, and is flat — Customer then Invoice rows, no asset layer.
 2. Body dates show as "Mon DD YYYY" — for example, "May 14 2026."
@@ -4005,145 +3338,48 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 15 S15-R16; S15-R17; S15-R18; S15-R19; S15-R20; S15-R21</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>PDF action shows a loading state while exporting and a PDF export failed toast on failure</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>An export over 10,000 data rows is refused with the too-large toast</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>1. Choose "Download (PDF)" and immediately look at the menu action.
-2. Provoke a failure (offline mode) and choose "Download (PDF)" again.</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>1. While the export is in progress, the menu's PDF action shows a loading state and is non-interactive.
-2. If the export fails, an error toast is shown: "PDF export failed." (dismissed by the user).</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 15 S15-E1; S15-N1; §7</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Print fetches the report PDF and opens the native print dialog in the current tab, disabled while the table is first loading</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Exports</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data fully loaded.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the overflow menu and choose "Print"; watch the action and the browser.
-2. Cancel the print dialog and check the page behind it.
-3. Reload the report and try to activate Print while the table is still in its initial loading state.
-4. Provoke a failure (offline mode) and choose Print again.</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>1. Print fetches the report's PDF (same content as the PDF download) and then opens the browser's native print dialog in the current tab — no new browser tab is opened.
-2. The page behind the print dialog is unchanged.
-3. The Print action shows a loading state while the PDF is fetched and is non-interactive during that time.
-4. Print is disabled while the report table is still in its initial loading state.
-5. If the PDF request fails, an error toast is shown: "PDF generation failed."</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 16 S16-R3; S16-R3a; S16-R3b; S16-R3c; S16-R4; S16-R5; S16-N1; §7</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>An export over 10,000 data rows is refused with the too-large toast</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Exports</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose "Download (CSV)".
 2. Choose "Download (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This export is too large to generate. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -4151,189 +3387,189 @@
 4. Below the cap the export succeeds normally.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Exporting with no matching customers still downloads a file with headers and a zero totals row, with no warning</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and open the file.
 2. Choose "Download (PDF)" and open the file.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R10</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>The download menu also offers a compressed (summary) version of the report</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the options.
 2. Download the compressed (summary) version and open the file.
 3. Download the expanded (full, nested) version and compare the two files.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Besides the existing expanded (nested) download, the menu offers a compressed (summary) download option. (The exact menu wording is confirmed in the build.)
 2. The compressed file gives one summary line per customer, without the per-invoice detail rows. (The exact file shape is confirmed in the build once the spec update lands.)
 3. The expanded download still contains the full nested detail, and both files reflect exactly the filtered data shown on screen.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (EPIC-LEVEL, stated explicitly: no child story exists yet for the SBC compressed download — kickoff video P21 32:10-33:03 + 48:39, user ruling 2026-07-28; overrides the current spec's single flat export, S14-R6; S14-R10; S15-R16)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Filters, sort and visible columns are saved and restored on the next visit, shown immediately without a default flash</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved; a reload clears all expansion</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -4341,469 +3577,425 @@
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is discarded and that setting falls back to its default</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R7</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>1. Clear the browser's site data for the application (or use a fresh browser profile).</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
+2. You open the report by its plain address with no date range in the page link.
+3. You are working in a known active location (check the application's location switcher).</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>1. Date range = This Month.
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
-3. Location = your active location.
+3. Location = the single location you are currently working in (your active location) — not all locations.
 4. Customer filter = all customers selected (label "All customers").
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 6 S6-N1</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>When both a saved view and a page-link range exist, the saved view wins and the link value is ignored</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R9</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: the all-customers state restores as all (including new customers); an id set is intersected and never forces an empty view</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>No matching data shows the empty-state message in the table body while the toolbar stays interactive</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
 3. Also provoke the empty state via Product Type and via a location with no data, and re-check.
-4. Look at the table header row's chevron.</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
+4. Look at the table header row's chevron.
+5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
-4. The header-row chevron is hidden when the table has no visible rows.</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+4. The header-row chevron is hidden when the table has no visible rows.
+5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>The empty-state message never appears while the table is still loading</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Change a filter and watch the table area during the load.
 2. Watch what appears once loading finishes with zero customers.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
 2. The message appears only after the table finishes its initial loading and shows zero customers.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 17 S17-N1</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>A narrowed customer selection with no data shows the empty state but the selection is kept and the customers reappear</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>A failed data fetch shows the fetching-error toast which auto-fades after 5 seconds</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>1. The Customer filter is narrowed to specific customers who have data in the current range but none in an adjacent range.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. Change the date range so that none of the selected customers have data.
-2. Read the table and the Customer filter.
-3. Change the range back.</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>1. The empty-state message is shown.
-2. The Customer filter selection is kept (not cleared).
-3. When the filters change back to a range where the selected customers have data, they reappear.</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 17 S17-E1</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>A failed data fetch shows the fetching-error toast which auto-fades after 5 seconds</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Empty &amp; Edge States</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md §7 User Feedback Summary</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme: paddings, surfaces, alignment, separator, arrow size and square corners</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser with dev tools available.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the page background, toolbar surface, and paddings with dev tools.
 2. Check the toolbar's position against the top of the page and the table against the side edges.
@@ -4811,7 +4003,7 @@
 4. Check the line between the toolbar and the headers, the date-range picker's dropdown arrow size, the table corners, and the outermost cell paddings.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The page has no padding; the page background is the standard blue-grey (#f9fafb in light mode).
 2. The toolbar surface is white (#ffffff); its padding is 32px top, 24px bottom, and 2rem left and right; it touches the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4822,48 +4014,48 @@
 7. When the table content does not fill the viewport, the blue-grey page background shows through below the table — no white strip.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level: white header/customer/totals rows, blue-grey asset/invoice rows, pinned Subtotal matching its row</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4872,183 +4064,183 @@
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Dark mode swaps every surface for its dark equivalent while the PDF always renders in light-mode colors</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R18</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch and below 1024px the toolbar splits into two rows</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with the Subtotal pinned, chevrons toggle, and invoice links open in the same tab</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>A customer's asset and invoice rows are fetched from the server only on first expand, and expand-all fetches at most one request per visible customer</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -5056,209 +4248,209 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server: a header click re-fetches the customer rows ordered by that column as a fresh first page</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
 3. The ordering is not done by re-shuffling rows already in the browser.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>The Customer filter's type-ahead fetches matching customers from the server per query instead of loading the full list up front</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated and the totals row is server-computed over the full filtered set</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Exports are generated on the server and the 10,000-row cap is counted server-side before any file is produced</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22; Story 16 S16-R6</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -1017,12 +1017,13 @@
           <t>1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
 3. With "All locations," the report includes data from every location the user has access to.
-4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
+4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins)) + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1953,7 +1954,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Asset label = year make model + serial number, with missing-data fallbacks</t>
+          <t>Asset identified by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1973,7 +1974,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a serial number recorded, (b) one with no serial number, (c) one with a VIN but no year, make, or model, (d) one with no year, make, model, or VIN (blank the fields as far as the asset form allows).</t>
+          <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a VIN recorded, (b) one with no VIN but a Unit # recorded, (c) one with no VIN or Unit # but a plate recorded, (d) one with no VIN, Unit #, or plate (blank the fields as far as the asset form allows).</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1983,16 +1984,16 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. Labels for assets that have them start with the vehicle's year, make, and model.
-2. Asset (a) shows its SERIAL NUMBER after the year/make/model as the identifier.
-3. For asset (b) (no serial number), note what the label shows instead — what stands in when the serial number is missing is confirmed in the build (the older wording used the unit number, then the plate, then the last 8 of the VIN).
-4. Asset (c) (no year/make/model) is labeled with the VIN on its own.
-5. Asset (d) (no year/make/model/VIN) is labeled "Unknown Asset."</t>
+          <t>1. Asset (a) is identified by its VIN.
+2. Asset (b) (no VIN) is identified by its Unit # instead.
+3. Asset (c) (no VIN or Unit #) is identified by its plate instead.
+4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
+5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28; S8-R9; S8-R10 fallback rules kept)</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to VIN, falling back to Unit #, then plate, by Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), superseding the kickoff video's serial-number ruling P24 AND the spec's year/make/model + unit/plate/VIN-suffix rule)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2864,7 +2865,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>The overflow menu holds only Download (CSV) and Download (PDF) — no Print item</t>
+          <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2897,13 +2898,13 @@
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
-2. The menu items read, in order: "Download (CSV)", "Download (PDF)" — and there is NO "Print" item anywhere in the menu.
-3. There are no separate always-visible export buttons — all exports live behind this one menu.</t>
+2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
+3. There are no separate always-visible export buttons - all exports live behind this one menu.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — the 'Print' third menu item REMOVED per kickoff video P25 31:14, overriding Story 16 / SV-8614, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to the four Summary/Expanded items by Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) [ratifies + extends video P21]; 'Print' REMOVED per video P25 31:14, CONFIRMED by the same message)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2962,7 +2963,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>CSV has twelve columns in exact order, is flat (customer then invoice rows), and follows the blank-cell rules</t>
+          <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2994,16 +2995,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. The CSV has twelve columns in this exact order: Customer, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
+          <t>1. The Expanded View CSV has the twelve columns in this exact order: Customer, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
 2. On customer rows the Invoice # and Date cells are blank.
 3. On invoice rows the Customer cell is blank and the Invoice # and Date cells are filled.
-4. Customer names are plain — the "(N)" invoice count is not included.
-5. The CSV is flat — Customer then Invoice rows; the on-screen asset layer is NOT represented (this is per spec, not a defect).</t>
+4. Customer names are plain - the "(N)" invoice count is not included.
+5. The rows follow the Expanded View's Customer, then Asset, then Invoice breakdown - note how the asset level appears (this level is NEW; its exact representation is confirmed from the updated spec and the build - the older spec had no asset rows in the file).
+6. The file carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R6; S14-R7; S14-R8; S14-R9; S14-R10 (context note)</t>
+          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R6; S14-R7; S14-R8; S14-R9 - file now the Expanded View CSV with a Customer-&gt;Asset-&gt;Invoice breakdown + a Locations: line per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins); the old S14-R10 flat/no-asset-layer rule is superseded)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3202,7 +3204,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PDF header shows the title, organization, date range in Mon D, YYYY form and the Product Type line; location is not shown</t>
+          <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3234,14 +3236,14 @@
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
-2. The text block shows, in order: the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
-3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash — for example, "May 1, 2026 — May 31, 2026" — and always shows both dates (every range is bounded).
-4. The location filter is NOT shown in the header; it scopes the data only.</t>
+2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
+3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
+4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11</t>
+          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - the old 'location is not shown in the header' rule is REVERSED by the Locations: line added to every export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3299,7 +3301,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>PDF body matches the CSV's twelve flat columns with on-screen date/dash/bold rules and exact Inv. Hrs colors</t>
+          <t>Expanded View PDF body matches the CSV's columns and on-screen rules</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3330,17 +3332,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. The body table has twelve columns in the same exact order and labels as the CSV, and is flat — Customer then Invoice rows, no asset layer.
-2. Body dates show as "Mon DD YYYY" — for example, "May 14 2026."
+          <t>1. The Expanded View PDF's body table has the twelve columns in the same exact order and labels as the Expanded View CSV, with the same Customer, then Asset, then Invoice breakdown (the asset level is NEW - its exact representation is confirmed from the updated spec and the build).
+2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
 3. The Date cell is blank on customer rows, matching the screen.
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
-5. The Subtotal column is bold — header, every row, and the totals row.
+5. The Subtotal column is bold - header, every row, and the totals row.
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 15 S15-R16; S15-R17; S15-R18; S15-R19; S15-R20; S15-R21</t>
+          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R16; S15-R17; S15-R18; S15-R19; S15-R20; S15-R21 - body now the Expanded View with a Customer-&gt;Asset-&gt;Invoice breakdown per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins); the old flat/no-asset-layer shape is superseded)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3444,7 +3446,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>The download menu also offers a compressed (summary) version of the report</t>
+          <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3469,21 +3471,22 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Open the download (overflow) menu and read the options.
-2. Download the compressed (summary) version and open the file.
-3. Download the expanded (full, nested) version and compare the two files.</t>
+          <t>1. Open the download (overflow) menu and read the four items.
+2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
+3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. Besides the existing expanded (nested) download, the menu offers a compressed (summary) download option. (The exact menu wording is confirmed in the build.)
-2. The compressed file gives one summary line per customer, without the per-invoice detail rows. (The exact file shape is confirmed in the build once the spec update lands.)
-3. The expanded download still contains the full nested detail, and both files reflect exactly the filtered data shown on screen.</t>
+          <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
+2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
+3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
+4. All four files reflect exactly the filtered data shown on screen.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8582 (EPIC-LEVEL, stated explicitly: no child story exists yet for the SBC compressed download — kickoff video P21 32:10-33:03 + 48:39, user ruling 2026-07-28; overrides the current spec's single flat export, S14-R6; S14-R10; S15-R16)</t>
+          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Stories 14/15 - Summary/Expanded split for both PDF and CSV per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) ['matching Sales By Rep'], ratifying + extending kickoff video P21 32:10-33:03 + 48:39; overrides the old single-flat-export S14-R6; S14-R10; S15-R16)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales By Customer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales By Customer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4295,19 +4295,21 @@
       <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
-2. Compare the returned first page with the previous page contents.</t>
+2. Compare the returned first page with the previous page contents.
+3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
-3. The ordering is not done by re-shuffling rows already in the browser.</t>
+3. The ordering is not done by re-shuffling rows already in the browser.
+4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b</t>
+          <t>specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sales By Customer appears in Reports navigation and opens with correct titles</t>
+          <t>Sales By Customer listed under Performance, below existing links; titles correct</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -517,14 +517,14 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area from the main navigation.
-2. Look through the Reports left-side navigation for the report entry.
+2. Find the Performance group and read its entries from top to bottom.
 3. Click the "Sales By Customer" entry.
 4. Read the page title at the top of the report and the browser tab's title.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Customer" is listed in the Reports left-side navigation.
+          <t>1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".</t>
@@ -532,7 +532,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 1 S1-R1; S1-R3; S1-R4</t>
+          <t>SV-8600 (specs/sbc-sales-by-customer.md Story 1 S1-R1; S1-R3; S1-R4 — Performance group + below-the-anchors placement per the PRD companion video 2026-07-30 01:18-02:05; the SBC spec names no nav group)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -511,7 +511,7 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Your role has the Sales By Customer report View permission.</t>
+2. Your role has the ordinary reports access (the standard "can this person see reports" setting).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (specs/sbc-sales-by-customer.md Story 1 S1-R1; S1-R3; S1-R4 — Performance group + below-the-anchors placement per the PRD companion video 2026-07-30 01:18-02:05; the SBC spec names no nav group)</t>
+          <t>SV-8600 (SBC spec Story 1 S1-R1; S1-R3; S1-R4 — Performance group + below-the-anchors placement per the PRD companion video 2026-07-30; access = ordinary reports permission per Chris Ward answer 2026-07-31 Q4=A)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A user with the dedicated Sales By Customer View permission can see and open the report</t>
+          <t>Ordinary reports access opens Sales By Customer — no separate permission</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role has the dedicated Sales By Customer report View permission (create a ZZAUTOTEST custom role if needed).
+          <t>1. A test user exists whose role has the ordinary reports access (the standard "can this person see reports" setting) and NO report-specific permission (create a ZZAUTOTEST custom role if needed; restore afterwards).
 2. You are signed in as that user.</t>
         </is>
       </c>
@@ -575,12 +575,13 @@
         <is>
           <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
-3. Access is granted by the dedicated Sales By Customer permission itself — the report is not tied to a generic "all reports" permission.</t>
+3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it as the known pending change — do not change the test.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 1 S1-R2</t>
+          <t>SV-8600 (SBC spec Story 1 S1-R2 — OVERRULED by Chris Ward answer 2026-07-31 Q4=A "the intention is to not hide these from normal reports access"; S1-R2 + the build still use a dedicated permission, dev change ticket raised)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -589,7 +590,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A user without the Sales By Customer View permission cannot see or open the report</t>
+          <t>Without reports access, Sales By Customer is not listed and cannot open</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -609,7 +610,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role does NOT have the Sales By Customer report View permission (use/create a ZZAUTOTEST role).
+          <t>1. A test user exists whose role does NOT have reports access (use/create a ZZAUTOTEST role; restore afterwards).
 2. You know the report's direct page address (copy it from a permitted session first).
 3. You are signed in as the unpermitted user.</t>
         </is>
@@ -623,12 +624,13 @@
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. "Sales By Customer" does not appear in the Reports navigation.
-2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).</t>
+2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
+3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 1 S1-N1</t>
+          <t>SV-8600 (SBC spec Story 1 S1-N1 — permission model RULED to the ordinary reports access by Chris Ward answer 2026-07-31 Q4=A; the build still ships a dedicated permission)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -931,7 +933,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Location filter is the rightmost filter, lists accessible locations, and pins All locations to the top</t>
+          <t>Location filter: rightmost, lists accessible locations, All locations on top</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -958,7 +960,8 @@
         <is>
           <t>1. Look at the report toolbar's filters from left to right.
 2. Open the location filter and read its options.
-3. Click the "All locations" option, then click it again.</t>
+3. Click the "All locations" option, then click it again.
+4. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -966,12 +969,13 @@
           <t>1. The location filter is the rightmost filter in the toolbar.
 2. It lists the locations the signed-in user has access to.
 3. An "All locations" option is pinned to the top.
-4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.</t>
+4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
+5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 4 S4-R1; S4-R2; S4-R3</t>
+          <t>SV-8600 (SBC spec Story 4 S4-R1; S4-R2; S4-R3 + single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A, applied suite-wide)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1032,37 +1036,94 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>The Location column shows only with more than one location; Multiple on totals</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Location Filter</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Sales By Customer report as a user with access to two or more locations.
+2. At least one customer has invoices at two different locations, and at least one asset has invoices at two different locations.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Select two or more locations in the Location filter and read the column headers.
+2. Read the Location cell on a customer row whose invoices are all at one location.
+3. Read the Location cell on a customer row and an asset row whose invoices span two locations.
+4. Expand to an invoice row and read its Location cell.
+5. Open the column selector and look for Location in the list.
+6. Narrow the Location filter to a single location and read the headers again.
+7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
+2. A customer or asset row whose invoices are all at one location shows that location's name.
+3. A customer or asset row whose invoices come from more than one location shows "Multiple".
+4. An invoice row always shows its own exact location — never "Multiple".
+5. Location is NOT offered in the column selector — it appears and disappears on its own, following the location scope.
+6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
+7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>SV-8600 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S20-R19 — per-row Location column with automatic visibility, "Multiple" on aggregating rows)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Customer filter sits between Product Type and Location, carries a search icon, and shows the Search customers… hint</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer in the current results.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar filters from left to right.
 2. Open the Customer filter without typing anything.
 3. Read what the dropdown shows before any query is typed.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
@@ -1070,97 +1131,97 @@
 4. The hint yields to the typed query while you are searching.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Typing in the Customer filter lists matching customers by contains match, with checkmarks on selected ones</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. At least two customers with distinct names have invoices in the current date range/Product Type/location (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and type a fragment from the MIDDLE of a customer's name, in different letter case (for example type "corp" for "Acme Corp").
 2. Read the list of customers shown.
 3. Click one listed customer to select it and look at its row in the dropdown.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R2</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Pinned control toggles All customers and Clear all; clearing shows empty state</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with several customers in the current results.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter while it is in the all-customers state and read the pinned control at the top of the dropdown.
 2. Activate it ("Clear all") and read the table body, the totals row, and the filter's collapsed label.
 3. Read the pinned control again and activate it once more.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
@@ -1168,43 +1229,43 @@
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>First load starts in the all-customers state and the report shows every customer</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. Your browser has no saved view for this report.
 2. Several customers have invoices in the default date range.
 3. A customer exists that has invoices ONLY in a wider date range than the current one (seed a ZZAUTOTEST invoice dated last month if needed).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read the Customer filter's collapsed label.
@@ -1212,7 +1273,7 @@
 4. Widen the date range so the customer with no matching invoices now has one; re-check the label and the rows.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
@@ -1220,41 +1281,41 @@
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Collapsed label reads None, the customer's name, or N selected, and shows the query text while typing</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and use "Clear all" to empty the selection; read the collapsed label.
 2. Select exactly one customer; read the collapsed label.
@@ -1262,7 +1323,7 @@
 4. Start typing a search query in the filter field and watch the field text, then clear the query or click away.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
@@ -1270,96 +1331,96 @@
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R5</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Changing the customer selection narrows the table to the selected customers and refreshes the totals</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Note the customers and the totals row values.
 2. Open the Customer filter, clear all, and select exactly two customers.
 3. Read the table rows and the totals row.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>A subset selection reconciles on a filter change: kept if present, dropped if absent, new customers not auto-added</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with three customers A, B, C where: A has invoices in both this month and last month; B has invoices only in this month; C has invoices only in last month (seed ZZAUTOTEST data as needed).
 2. Date range is This Month; you have selected exactly customers A and B in the Customer filter.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range to Last Month.
 2. Read the table rows and the Customer filter selection.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
@@ -1367,49 +1428,49 @@
 4. The Customer filter selection itself is not cleared by the date change.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Each customer gets one summary row with its name followed by the invoice count in parentheses</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. A customer has a known number of matching invoices in the current date range (seed ZZAUTOTEST data so the count is predictable).</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Find that customer's row at the top level of the table.
 2. Read the text at the start of the row.
 3. Narrow the date range so fewer of that customer's invoices match, and re-read the count.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
@@ -1417,95 +1478,95 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>A customer with no matching invoices in the current view is not shown</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose invoices all fall OUTSIDE the current date range (seed if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains none of that customer's invoices.
 2. Look for the customer in the table.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-N1</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Expanding a customer reveals asset rows; chevrons toggle and are independent</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. A customer in the current view has invoices on at least two different vehicles (seed ZZAUTOTEST work orders on two assets if needed).
 2. At least two customers with assets are in the current view.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron control on customer A's summary row and read the rows that appear beneath it.
 2. Expand one of customer A's assets, then expand customer B.
 3. Click customer A's chevron again and check customer B.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
@@ -1516,370 +1577,370 @@
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Expanding an asset reveals its invoice detail rows with number link, date and per-invoice columns</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded a customer and can see its asset rows.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron on an asset row.
 2. Read the invoice detail rows that appear.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Invoices group into one asset row per vehicle record, with a snapshot fallback for older invoices with no vehicle id</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. A customer has two or more invoices on the SAME vehicle record and at least one invoice on a different vehicle (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer.
 2. Count the asset rows and compare each asset's invoice count with the invoices you created.
 3. If the environment has an older invoice with no vehicle record linked (only a stored vehicle snapshot), check which asset row it lands under.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R3</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Asset rows order A to Z case-insensitively with the Parts Sales bucket always last, regardless of column sort</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. A customer has invoices on at least two vehicles AND at least one no-vehicle invoice (counter/parts sale) in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the asset rows top to bottom.
 2. Click a financial column header to change the table sort, and re-read the asset rows.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Header-row chevron expands or collapses every customer on the current page, with matching icon and tooltip</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. Several customers are visible on the current page.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Hover the chevron in the table header row and read the tooltip.
 2. Click it and watch the customer rows.
 3. Hover it again and read the tooltip, then click it again.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Reload-causing changes collapse expansion; Customer filter typing does not</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one customer expanded down to invoice rows.
 2. Enough customers exist to fill more than one page of results (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. With rows expanded, open the Customer filter and TYPE a search query (do not change the selection); watch the expanded rows.
 2. Now change the date range (or Product Type, location, Customer selection, or sort).
 3. Look at the previously expanded rows, the loading state, and the set of customers on the page.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Edge: a single-invoice asset can still be expanded, and a customer with only no-vehicle work shows a single Parts Sales row</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Customer A has an asset with exactly one invoice; customer B has ONLY no-vehicle (counter/parts sale) invoices in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Expand customer A and click the chevron of the single-invoice asset.
 2. Expand customer B and read its asset rows.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket — absence of a vehicle decides, not the prefix</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. A customer has an invoice whose number starts with S but whose work order has NO vehicle (seed a ZZAUTOTEST no-vehicle service work order and invoice it, if the app allows).</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Expand that customer.
 2. Find which asset row the S invoice sits under.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-E3</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Reversed and voided invoices are excluded from every row, count and total under every Product Type</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. A customer has a known set of invoices in the current range, one of which you then reverse (or void) — seed ZZAUTOTEST data and note the totals before and after.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Note the customer's invoice count "(N)" and totals with all invoices normal.
 2. Reverse (or void) one of the invoices in the application.
@@ -1887,55 +1948,55 @@
 4. Expand down to invoice rows and look for the reversed invoice.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Every row type renders the same columns in the same order, blank cells keep their position, and summary rows use the specified font weights</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a customer expanded down to invoice rows and the totals row visible.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
 3. Inspect the font weights on a customer summary row (dev tools).</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
@@ -1943,46 +2004,46 @@
 4. Every cell on a customer summary row uses font-weight 600, except the Subtotal cell which uses font-weight 700.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Asset identified by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a VIN recorded, (b) one with no VIN but a Unit # recorded, (c) one with no VIN or Unit # but a plate recorded, (d) one with no VIN, Unit #, or plate (blank the fields as far as the asset form allows).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read each asset row's label.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
@@ -1991,190 +2052,190 @@
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to VIN, falling back to Unit #, then plate, by Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), superseding the kickoff video's serial-number ruling P24 AND the spec's year/make/model + unit/plate/VIN-suffix rule)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. One customer has TWO ZZAUTOTEST assets whose labels come out identical (same year/make/model and same identifier situation), each with an invoice in range.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the two asset labels.
 2. Note which asset carries " (#1)" and which " (#2)".
 3. Reload the page and expand again.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R11)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Invoice number opens in the same tab: S invoices to the work order Finance tab, P invoices to the part sale Part Requests tab</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded an asset and can see at least one S invoice and (under another customer/asset if needed) one P invoice.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Click a service (S) invoice number link and note where it opens.
 2. Go back, then click a parts (P) invoice number link and note where it opens.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Browser back from an invoice returns to the report with filters, sort and columns restored and rows collapsed</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with non-default filters set (for example Last Month + Service only), a non-default sort, and one column hidden.
 2. You have expanded down to an invoice detail row.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Watch the browser address bar, then click an invoice number link.
 2. From the invoice page, press the browser back button.
 3. Check the report's filters, sort, visible columns, and row expansion.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Customer name is plain text; the invoice link keeps the primary color with no underline and never turns visited-purple</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded down to invoice detail rows and have already clicked at least one invoice link earlier in the session.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Try clicking the customer NAME on a summary row.
 2. Look at an invoice number link at rest, on hover, and one you have already visited.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
@@ -2182,89 +2243,89 @@
 4. The link never recolors to the browser's visited-link (purple) color.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Clicking an invoice deleted or reversed after the report loaded shows the standard not-found state and back returns</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with an invoice detail row visible.
 2. In another tab/session, that invoice is deleted or reversed AFTER the report loaded (do not refresh the report).</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Back in the report (unrefreshed), click that invoice's number link.
 2. Read the destination page, then press the browser back button.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 9 S9-N1</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>All columns sortable except chevron; text alphabetical, numbers by value</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. Several customers with differing values are in the current view.
 2. A customer with multiple assets and invoices is in the view.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
@@ -2272,194 +2333,194 @@
 4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Default sort is Customer name ascending case-insensitive; clicking a header replaces it</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. No saved view exists (first visit or cleared storage).
 2. Customer names with mixed upper/lower-case first letters exist in the view (seed ZZAUTOTEST names like "acme test" and "Best Test").</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the customer order.
 2. Click the Subtotal header and read the order again.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Missing values sort to the bottom ascending and to the top descending; a Margin % em dash counts as missing</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer row shows an em dash (—) in Margin % (Subtotal zero or below — seed a zero-subtotal case if possible) alongside rows with real Margin % values.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Margin % ascending and note where the em-dash row lands.
 2. Sort by Margin % descending and note it again.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R3</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sorting by Date orders customers by their most recent invoice date even though the Date cell is blank on customer rows</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. Two customers exist whose most recent invoice dates differ clearly (seed ZZAUTOTEST invoices on different dates).</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date column header.
 2. Compare the customer order with each customer's most recent invoice date (expand to check the invoice dates).</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R5</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Financial columns appear in the specified order and Subtotal/Margin follow the spec's composition rules</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known labor, parts, and shop-supply amounts and known costs, in the current range.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Expand down to that invoice's detail row and read its values.
 3. Recalculate Subtotal and Margin by hand from the known amounts.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
@@ -2467,48 +2528,48 @@
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Margin % = Margin over Subtotal to one decimal with a percent sign, em dash when Subtotal is zero or below, monochrome on all row types</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. Rows with a normal positive Subtotal exist, and (if seedable) one row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on a customer row, an asset row, and an invoice row; recalculate one by hand (Margin ÷ Subtotal × 100).
 2. Find (or seed) a row with Subtotal ≤ 0 and read its Margin % cell.
 3. Look at the Margin % coloring.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
@@ -2516,47 +2577,47 @@
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim and the value shows +green / -red / 0.0 default on every row type</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist where billed hours exceed worked hours, where worked exceeds billed, and where they are equal (seed ZZAUTOTEST work orders with clocked time).</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
@@ -2566,143 +2627,143 @@
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is never blank: no-labor rows show 0.0 and values that round to zero show 0.0 in the default color</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice (no labor at all) exists in range; if possible also an invoice whose delta rounds to zero (for example +0.04).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
 2. If seeded, read the near-zero row's Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Invoice subtotals sum exactly to their asset row and asset subtotals sum exactly to the customer row</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. A customer with two or more assets, each with two or more invoices, is in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and every asset.
 2. Sum the invoice-level values by hand for each column and compare with each asset row.
 3. Sum the asset rows and compare with the customer row.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R13</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Subtotal is the rightmost column, pinned during horizontal scroll and bold everywhere, unconditionally</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, on a window narrow enough to force horizontal scrolling (or with all columns visible).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Subtotal column is the last column on the right.
 2. Scroll the table sideways and watch the Subtotal column.
 3. Inspect the font weight of the Subtotal header, a customer row, an asset row, an invoice row, and the totals row.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
@@ -2710,95 +2771,95 @@
 4. This holds regardless of permission, data, filters, or sort — the Subtotal column is always present, pinned, and bold.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>The totals row covers the full filtered set of customers, not only the customers on the current page</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page of results, with known amounts (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Read the totals row on page 1.
 2. Move to page 2 and read the totals row again.
 3. Compare the totals against the sum over ALL matching customers (not just one page).</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R6</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Column selector is a separate toolbar button with the Column Selection tooltip and nine toggles in order, all on by default</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no saved column selection (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector button in the toolbar's action area, next to the overflow menu.
 2. Hover it and read the tooltip.
 3. Click it and read the toggle list top to bottom.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
@@ -2806,155 +2867,105 @@
 4. With no saved selection, all nine toggleable columns default to visible.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Column toggles hide header+cells; Customer, Subtotal and chevron never in list</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data and the column selector open.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Turn the "Shop Supplies" toggle off, then on again, watching the table.
 2. Read the toggle list for Customer, Subtotal, or a chevron entry.
 3. Turn all nine toggles off and read the table.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to the four Summary/Expanded items by Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) [ratifies + extends video P21]; 'Print' REMOVED per video P25 31:14, CONFIRMED by the same message)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CSV and PDF downloads are named by the active date range per the filename map</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Exports</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with data.</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Set the range to This Month and choose "Download (CSV)"; note the downloaded filename.
-2. Repeat for at least Today, Last Quarter, and a Custom range.
-3. Open a downloaded file in a text editor and in a spreadsheet.
-4. Repeat steps 1-2 choosing "Download (PDF)" and note the filenames.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>1. The filename follows the range map: Today → sales-by-customer-today.csv; Yesterday → sales-by-customer-yesterday.csv; This Week → sales-by-customer-this_week.csv; Last Week → sales-by-customer-last_week.csv; This Month → sales-by-customer-this_month.csv; Last Month → sales-by-customer-last_month.csv; This Year → sales-by-customer-this_year.csv; Last Year → sales-by-customer-last_year.csv; This Quarter → sales-by-customer-this_quarter.csv; Last Quarter → sales-by-customer-last_quarter.csv; Custom → sales-by-customer-custom.csv.
-2. For Custom the literal word "custom" is used — the actual start/end dates are not in the filename.
-3. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
-4. The PDF download follows the same range-to-filename map with a .pdf extension — for example, sales-by-customer-this_month.pdf, sales-by-customer-custom.pdf.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R4; S14-R5; Story 15 S15-R4</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2963,87 +2974,140 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>Download file names carry the version and the active date range</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with data.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Set the range to This Month, choose "Download Summary (CSV)" and note the downloaded file name.
+2. Choose "Download Expanded View (CSV)" and note that file name.
+3. Repeat both for at least Today, Last Quarter, and a Custom range.
+4. Open a downloaded file in a text editor and in a spreadsheet.
+5. Repeat steps 1-3 for "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
+2. {range} follows this map: Today → today; Yesterday → yesterday; This Week → this_week; Last Week → last_week; This Month → this_month; Last Month → last_month; This Year → this_year; Last Year → last_year; This Quarter → this_quarter; Last Quarter → last_quarter; Custom → custom.
+3. For Custom the literal word "custom" is used — the actual start and end dates are not in the file name.
+4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
+5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1. The Expanded View CSV has the twelve columns in this exact order: Customer, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
-2. On customer rows the Invoice # and Date cells are blank.
-3. On invoice rows the Customer cell is blank and the Invoice # and Date cells are filled.
-4. Customer names are plain - the "(N)" invoice count is not included.
-5. The rows follow the Expanded View's Customer, then Asset, then Invoice breakdown - note how the asset level appears (this level is NEW; its exact representation is confirmed from the updated spec and the build - the older spec had no asset rows in the file).
-6. The file carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R6; S14-R7; S14-R8; S14-R9 - file now the Expanded View CSV with a Customer-&gt;Asset-&gt;Invoice breakdown + a Locations: line per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins); the old S14-R10 flat/no-asset-layer rule is superseded)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. The Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
+2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
+3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
+4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
+5. Customer names are plain — the "(N)" invoice count is not included.
+6. Work with no vehicle appears as an asset row named "Parts Sales".
+7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R13 — the Expanded CSV now has thirteen columns INCLUDING Asset, with per-level blank-cell rules; the old flat twelve-column shape is superseded)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>CSV value formats: Margin % plain number, dates mm-dd-yyyy, currency plain numbers, no color</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
@@ -3051,105 +3115,57 @@
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 14 S14-R10; S14-R11; S14-R12; S14-R13</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF contain exactly the customers matching the active filters and sort, including the Customer filter selection</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CSV and PDF actions show a loading state and their own export failed toast</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Exports</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with a large enough data set that the export takes a visible moment.</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Choose "Download (CSV)" and immediately look at the menu action.
-2. To provoke a failure, disconnect the network (or use browser dev tools offline mode) and choose "Download (CSV)" again.
-3. Repeat both checks for "Download (PDF)".</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>1. While an export is in progress, that menu action shows a loading state and is non-interactive (CSV and PDF alike).
-2. If the CSV export fails, an error toast is shown: "CSV export failed." (dismissed by the user).
-3. If the PDF export fails, the toast reads "PDF export failed." — identical behavior, different wording.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3158,82 +3174,130 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>Each download item shows a loading state and its own export-failed toast</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with a large enough data set that a download takes a visible moment.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
+2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
+3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
+2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
+3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item, four items)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 15 S15-R5; S15-R6</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3241,48 +3305,48 @@
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - the old 'location is not shown in the header' rule is REVERSED by the Locations: line added to every export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion, and falls back from the uploaded logo to the ShopView logo to none</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With no uploaded logo, the bundled ShopView logo is used.
@@ -3290,289 +3354,291 @@
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 15 S15-R12; S15-R13; S15-R14; S15-R15</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF body matches the CSV's columns and on-screen rules</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Read the body table's columns and row structure.
 2. Check a date cell, a customer row's Date cell, a Margin % dash, the Subtotal column weight, and the Inv. Hrs colors (use a color picker on the PDF if available).</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>1. The Expanded View PDF's body table has the twelve columns in the same exact order and labels as the Expanded View CSV, with the same Customer, then Asset, then Invoice breakdown (the asset level is NEW - its exact representation is confirmed from the updated spec and the build).
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1. The Expanded View PDF's body table has the same thirteen columns, in the same order and with the same labels, as the Expanded View CSV — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
-3. The Date cell is blank on customer rows, matching the screen.
+3. The Date cell is blank on customer rows and on asset rows, matching the screen.
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
 5. The Subtotal column is bold - header, every row, and the totals row.
-6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R16; S15-R17; S15-R18; S15-R19; S15-R20; S15-R21 - body now the Expanded View with a Customer-&gt;Asset-&gt;Invoice breakdown per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins); the old flat/no-asset-layer shape is superseded)</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
+7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 — Expanded PDF body = the Expanded columns with the asset layer, one block per customer; the title is the same for both versions)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose "Download (CSV)".
 2. Choose "Download (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. For both CSV and PDF: no file is generated and no download starts.
-2. An error toast is shown each time: "This export is too large to generate. Narrow the date range or filters, then try again." (dismissed by the user).
+2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
 4. Below the cap the export succeeds normally.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Exporting with no matching customers still downloads a file with headers and a zero totals row, with no warning</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and open the file.
 2. Choose "Download (PDF)" and open the file.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R10</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the four items.
 2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
 3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
-4. All four files reflect exactly the filtered data shown on screen.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Stories 14/15 - Summary/Expanded split for both PDF and CSV per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) ['matching Sales By Rep'], ratifying + extending kickoff video P21 32:10-33:03 + 48:39; overrides the old single-flat-export S14-R6; S14-R10; S15-R16)</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+4. All four files reflect exactly the filtered data shown on screen.
+5. The Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 — the four-item Summary/Expanded menu and the Summary column list are now spec-ratified)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Filters, sort and visible columns are saved and restored on the next visit, shown immediately without a default flash</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved; a reload clears all expansion</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -3580,143 +3646,143 @@
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is discarded and that setting falls back to its default</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-R7</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -3726,135 +3792,135 @@
 6. All nine toggleable columns visible.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>When both a saved view and a page-link range exist, the saved view wins and the link value is ignored</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 2 S2-R9</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: the all-customers state restores as all (including new customers); an id set is intersected and never forces an empty view</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R8</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -3863,7 +3929,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -3872,133 +3938,133 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>The empty-state message never appears while the table is still loading</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Change a filter and watch the table area during the load.
 2. Watch what appears once loading finishes with zero customers.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
 2. The message appears only after the table finishes its initial loading and shows zero customers.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 17 S17-N1</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the fetching-error toast which auto-fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md §7 User Feedback Summary</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme: paddings, surfaces, alignment, separator, arrow size and square corners</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser with dev tools available.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the page background, toolbar surface, and paddings with dev tools.
 2. Check the toolbar's position against the top of the page and the table against the side edges.
@@ -4006,7 +4072,7 @@
 4. Check the line between the toolbar and the headers, the date-range picker's dropdown arrow size, the table corners, and the outermost cell paddings.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The page has no padding; the page background is the standard blue-grey (#f9fafb in light mode).
 2. The toolbar surface is white (#ffffff); its padding is 32px top, 24px bottom, and 2rem left and right; it touches the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4017,48 +4083,48 @@
 7. When the table content does not fill the viewport, the blue-grey page background shows through below the table — no white strip.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level: white header/customer/totals rows, blue-grey asset/invoice rows, pinned Subtotal matching its row</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4067,183 +4133,183 @@
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Dark mode swaps every surface for its dark equivalent while the PDF always renders in light-mode colors</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 20 S20-R18</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch and below 1024px the toolbar splits into two rows</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with the Subtotal pinned, chevrons toggle, and invoice links open in the same tab</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>A customer's asset and invoice rows are fetched from the server only on first expand, and expand-all fetches at most one request per visible customer</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4251,55 +4317,55 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server: a header click re-fetches the customer rows ordered by that column as a fresh first page</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -4307,155 +4373,155 @@
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>The Customer filter's type-ahead fetches matching customers from the server per query instead of loading the full list up front</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated and the totals row is server-computed over the full filtered set</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Exports are generated on the server and the 10,000-row cap is counted server-side before any file is produced</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22; Story 16 S16-R6</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -527,7 +527,8 @@
           <t>1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
-4. The browser tab title reads "Sales By Customer - Report | ShopView".</t>
+4. The browser tab title reads "Sales By Customer - Report | ShopView".
+5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it as the known pending change — do not change the test.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -581,7 +582,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (SBC spec Story 1 S1-R2 — OVERRULED by Chris Ward answer 2026-07-31 Q4=A "the intention is to not hide these from normal reports access"; S1-R2 + the build still use a dedicated permission, dev change ticket raised)</t>
+          <t>SV-8600 (SBC spec Story 1 S1-R2 — OVERRULED by Chris Ward answer 2026-07-31 Q4=A "the intention is to not hide these from normal reports access"; S1-R2 + the build still use a dedicated permission; dev change ticket raised)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -625,7 +626,8 @@
         <is>
           <t>1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
-3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.</t>
+3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it as the known pending change — do not change the test.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -639,7 +641,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Opening an invoice you lack permission for shows the standard access-denied state and back returns to the report</t>
+          <t>Opening an invoice you lack permission for shows access-denied; back works</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -678,7 +680,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 9 S9-N2</t>
+          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N2)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -730,7 +732,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 4 S4-R7; S4-R8; S4-R9; S4-N1</t>
+          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R7; S4-R8; S4-R9; S4-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -777,7 +779,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 2 S2-R1; S2-R2</t>
+          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R1; S2-R2)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -825,7 +827,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 2 S2-R3; S2-R4; S2-N2</t>
+          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R3; S2-R4; S2-N2)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -834,7 +836,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Changing the date range writes the chosen value to the page link for sharing and bookmarking</t>
+          <t>Changing the date range writes it into the page link for sharing</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -872,7 +874,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 2 S2-R6; S2-R9 (context)</t>
+          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R6; S2-R9 (context))</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -924,7 +926,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6</t>
+          <t>SV-8602 (specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -975,7 +977,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (SBC spec Story 4 S4-R1; S4-R2; S4-R3 + single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A, applied suite-wide)</t>
+          <t>SV-8603 (SBC spec Story 4 S4-R1; S4-R2; S4-R3 + single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A; applied suite-wide)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1027,7 +1029,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins)) + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins)</t>
+          <t>SV-8603 (SBC spec Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10; [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward msg 2026-07-29 [newest-wins]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S20-R19 — per-row Location column with automatic visibility, "Multiple" on aggregating rows)</t>
+          <t>SV-8603 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1093,7 +1095,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Customer filter sits between Product Type and Location, carries a search icon, and shows the Search customers… hint</t>
+          <t>Customer filter sits between Product Type and Location, carries a search icon</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1133,7 +1135,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1142,7 +1144,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Typing in the Customer filter lists matching customers by contains match, with checkmarks on selected ones</t>
+          <t>Typing in the Customer filter lists matching customers by contains match</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1182,7 +1184,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R2</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1231,7 +1233,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1283,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1292,7 +1294,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Collapsed label reads None, the customer's name, or N selected, and shows the query text while typing</t>
+          <t>Collapsed label reads None, the customer's name, or N selected</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1333,7 +1335,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R5</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1342,7 +1344,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Changing the customer selection narrows the table to the selected customers and refreshes the totals</t>
+          <t>Changing the customer selection narrows the table and refreshes the totals</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1381,7 +1383,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1390,7 +1392,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A subset selection reconciles on a filter change: kept if present, dropped if absent, new customers not auto-added</t>
+          <t>A subset customer selection reconciles on a filter change; kept if present</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1430,7 +1432,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1439,7 +1441,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Each customer gets one summary row with its name followed by the invoice count in parentheses</t>
+          <t>Each customer gets one summary row with its invoice count in parentheses</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1480,7 +1482,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5</t>
+          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1526,7 +1528,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 7 S7-N1</t>
+          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-N1)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1579,7 +1581,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1588,7 +1590,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Expanding an asset reveals its invoice detail rows with number link, date and per-invoice columns</t>
+          <t>Expanding an asset reveals its invoice rows with number link and date</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1626,7 +1628,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1635,7 +1637,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Invoices group into one asset row per vehicle record, with a snapshot fallback for older invoices with no vehicle id</t>
+          <t>Invoices group into one asset row per vehicle record</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1673,7 +1675,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R3</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R3)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1682,7 +1684,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Asset rows order A to Z case-insensitively with the Parts Sales bucket always last, regardless of column sort</t>
+          <t>Asset rows order A to Z with the Parts Sales bucket always last</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1720,7 +1722,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1729,7 +1731,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Header-row chevron expands or collapses every customer on the current page, with matching icon and tooltip</t>
+          <t>Header-row chevron expands or collapses every customer on the current page</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1768,7 +1770,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1817,7 +1819,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1826,7 +1828,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Edge: a single-invoice asset can still be expanded, and a customer with only no-vehicle work shows a single Parts Sales row</t>
+          <t>Edge: a single-invoice asset can still be expanded</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1863,7 +1865,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1872,7 +1874,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket — absence of a vehicle decides, not the prefix</t>
+          <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1908,7 +1910,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-E3</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E3)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1917,7 +1919,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Reversed and voided invoices are excluded from every row, count and total under every Product Type</t>
+          <t>Reversed and voided invoices are excluded from every row; count and total</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1957,7 +1959,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions</t>
+          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1966,7 +1968,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Every row type renders the same columns in the same order, blank cells keep their position, and summary rows use the specified font weights</t>
+          <t>Every row type renders the same columns in the same order</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2006,7 +2008,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16</t>
+          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2054,7 +2056,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to VIN, falling back to Unit #, then plate, by Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), superseding the kickoff video's serial-number ruling P24 AND the spec's year/make/model + unit/plate/VIN-suffix rule)</t>
+          <t>SV-8606 (SBC spec Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward msg 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's year/make/model rule)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2110,7 +2112,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Invoice number opens in the same tab: S invoices to the work order Finance tab, P invoices to the part sale Part Requests tab</t>
+          <t>The invoice number opens the invoice in the same browser tab</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2148,7 +2150,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b</t>
+          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2157,7 +2159,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Browser back from an invoice returns to the report with filters, sort and columns restored and rows collapsed</t>
+          <t>Browser back from an invoice restores filters; sort and columns; rows shut</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2197,7 +2199,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4</t>
+          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2206,7 +2208,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Customer name is plain text; the invoice link keeps the primary color with no underline and never turns visited-purple</t>
+          <t>Customer name is plain text; the invoice link never turns visited-purple</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2245,7 +2247,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8</t>
+          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2254,7 +2256,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Clicking an invoice deleted or reversed after the report loaded shows the standard not-found state and back returns</t>
+          <t>An invoice deleted after load shows the not-found state and back returns</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2292,7 +2294,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 9 S9-N1</t>
+          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N1)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2342,7 +2344,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6</t>
+          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2351,7 +2353,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Default sort is Customer name ascending case-insensitive; clicking a header replaces it</t>
+          <t>Default sort is Customer name ascending case-insensitive</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2389,7 +2391,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7</t>
+          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2398,7 +2400,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Missing values sort to the bottom ascending and to the top descending; a Margin % em dash counts as missing</t>
+          <t>Missing values sort to the bottom ascending and to the top descending</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2435,7 +2437,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R3</t>
+          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2444,7 +2446,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Sorting by Date orders customers by their most recent invoice date even though the Date cell is blank on customer rows</t>
+          <t>Sorting by Date orders customers by their most recent invoice date</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2481,7 +2483,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R5</t>
+          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2490,7 +2492,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Financial columns appear in the specified order and Subtotal/Margin follow the spec's composition rules</t>
+          <t>Financial columns run in the specified order with Subtotal and Margin rules</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2530,7 +2532,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1</t>
+          <t>SV-8605 (specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2539,7 +2541,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Margin % = Margin over Subtotal to one decimal with a percent sign, em dash when Subtotal is zero or below, monochrome on all row types</t>
+          <t>Margin % is Margin over Subtotal to one decimal; em dash when Subtotal &lt;= 0</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2579,7 +2581,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14</t>
+          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2588,7 +2590,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs heading is verbatim and the value shows +green / -red / 0.0 default on every row type</t>
+          <t>Inv. Hrs heading is verbatim; value shows +green / -red / 0.0 on every row</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2629,7 +2631,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6</t>
+          <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2638,7 +2640,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs is never blank: no-labor rows show 0.0 and values that round to zero show 0.0 in the default color</t>
+          <t>Inv. Hrs is never blank: no-labor rows and near-zero values both show 0.0</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2676,7 +2678,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2</t>
+          <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2685,7 +2687,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Invoice subtotals sum exactly to their asset row and asset subtotals sum exactly to the customer row</t>
+          <t>Invoice subtotals sum to their asset row and asset subtotals to the customer</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2724,7 +2726,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R13</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R13)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2733,7 +2735,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Subtotal is the rightmost column, pinned during horizontal scroll and bold everywhere, unconditionally</t>
+          <t>Subtotal is the rightmost column; pinned on scroll and bold everywhere</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2773,7 +2775,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1</t>
+          <t>SV-8609 (specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2782,7 +2784,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>The totals row covers the full filtered set of customers, not only the customers on the current page</t>
+          <t>The totals row covers the whole filtered set; not just the current page</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2820,7 +2822,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R6</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2829,7 +2831,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Column selector is a separate toolbar button with the Column Selection tooltip and nine toggles in order, all on by default</t>
+          <t>Column selector is its own toolbar button with nine toggles all on</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2869,7 +2871,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7</t>
+          <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2917,7 +2919,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1</t>
+          <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2965,7 +2967,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to the four Summary/Expanded items by Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) [ratifies + extends video P21]; 'Print' REMOVED per video P25 31:14, CONFIRMED by the same message)</t>
+          <t>SV-8612; SV-8613 (SBC spec S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to 4 Summary/Expanded items by Chris Ward msg 2026-07-29 [newest-wins] [extends video P21]; 'Print' REMOVED per video P25 [same msg confirms])</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3069,7 +3071,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R13 — the Expanded CSV now has thirteen columns INCLUDING Asset, with per-level blank-cell rules; the old flat twelve-column shape is superseded)</t>
+          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R13 — the Expanded CSV now has thirteen columns INCLUDING Asset; with per-level blank-cell rules; the old flat twelve-column shape is superseded)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3078,7 +3080,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CSV value formats: Margin % plain number, dates mm-dd-yyyy, currency plain numbers, no color</t>
+          <t>CSV formats: Margin % plain; dates mm-dd-yyyy; currency plain; no color</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3117,7 +3119,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R10; S14-R11; S14-R12; S14-R13</t>
+          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3126,7 +3128,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CSV and PDF contain exactly the customers matching the active filters and sort, including the Customer filter selection</t>
+          <t>CSV and PDF hold exactly the customers matching the active filters and sort</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3165,7 +3167,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7</t>
+          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3213,7 +3215,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item, four items)</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3259,7 +3261,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 15 S15-R5; S15-R6</t>
+          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R5; S15-R6)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3307,7 +3309,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - the old 'location is not shown in the header' rule is REVERSED by the Locations: line added to every export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
+          <t>SV-8613 (SBC spec Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - old 'location not in the header' rule REVERSED by the Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3316,7 +3318,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>PDF logo is embedded, scales without distortion, and falls back from the uploaded logo to the ShopView logo to none</t>
+          <t>PDF logo is embedded, scales without distortion</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3356,7 +3358,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 15 S15-R12; S15-R13; S15-R14; S15-R15</t>
+          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R12; S15-R13; S15-R14; S15-R15)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3407,7 +3409,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 — Expanded PDF body = the Expanded columns with the asset layer, one block per customer; the title is the same for both versions)</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 — Expanded PDF body = the Expanded columns with the asset layer; one block per customer; the title is the same for both versions)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3456,7 +3458,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3465,7 +3467,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Exporting with no matching customers still downloads a file with headers and a zero totals row, with no warning</t>
+          <t>A no-match export still downloads headers and a zero totals row</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3502,7 +3504,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R10</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R10)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3561,7 +3563,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Filters, sort and visible columns are saved and restored on the next visit, shown immediately without a default flash</t>
+          <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3599,7 +3601,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8</t>
+          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3608,7 +3610,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Type-ahead search text, expansion state and scroll position are not saved; a reload clears all expansion</t>
+          <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3648,7 +3650,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22</t>
+          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3657,7 +3659,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>A saved value that is no longer valid is discarded and that setting falls back to its default</t>
+          <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3696,7 +3698,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6</t>
+          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3742,7 +3744,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 6 S6-R7</t>
+          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R7)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3794,7 +3796,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4</t>
+          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3803,7 +3805,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>When both a saved view and a page-link range exist, the saved view wins and the link value is ignored</t>
+          <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3841,7 +3843,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 2 S2-R9</t>
+          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R9)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3850,7 +3852,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Customer filter restore: the all-customers state restores as all (including new customers); an id set is intersected and never forces an empty view</t>
+          <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3888,7 +3890,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R8</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3940,7 +3942,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1</t>
+          <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3986,7 +3988,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 17 S17-N1</t>
+          <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3995,7 +3997,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>A failed data fetch shows the fetching-error toast which auto-fades after 5 seconds</t>
+          <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4032,7 +4034,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md §7 User Feedback Summary</t>
+          <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4041,7 +4043,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Page and toolbar match the suite theme: paddings, surfaces, alignment, separator, arrow size and square corners</t>
+          <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4085,7 +4087,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17</t>
+          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4094,7 +4096,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Row surfaces alternate by tree level: white header/customer/totals rows, blue-grey asset/invoice rows, pinned Subtotal matching its row</t>
+          <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4135,7 +4137,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14</t>
+          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4144,7 +4146,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Dark mode swaps every surface for its dark equivalent while the PDF always renders in light-mode colors</t>
+          <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4181,7 +4183,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 20 S20-R18</t>
+          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R18)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4190,7 +4192,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>On a phone every toolbar control works on touch and below 1024px the toolbar splits into two rows</t>
+          <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4229,7 +4231,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3</t>
+          <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4238,7 +4240,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>On touch the table scrolls sideways with the Subtotal pinned, chevrons toggle, and invoice links open in the same tab</t>
+          <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4277,7 +4279,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6</t>
+          <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4286,7 +4288,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>A customer's asset and invoice rows are fetched from the server only on first expand, and expand-all fetches at most one request per visible customer</t>
+          <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4326,7 +4328,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16</t>
+          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4335,7 +4337,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Sorting is applied on the server: a header click re-fetches the customer rows ordered by that column as a fresh first page</t>
+          <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4375,7 +4377,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist)</t>
+          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4384,7 +4386,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>The Customer filter's type-ahead fetches matching customers from the server per query instead of loading the full list up front</t>
+          <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4423,7 +4425,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4432,7 +4434,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Customer rows are server-paginated and the totals row is server-computed over the full filtered set</t>
+          <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4471,7 +4473,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11</t>
+          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4480,7 +4482,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Exports are generated on the server and the 10,000-row cap is counted server-side before any file is produced</t>
+          <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4517,7 +4519,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22; Story 16 S16-R6</t>
+          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -1070,7 +1070,8 @@
 4. Expand to an invoice row and read its Location cell.
 5. Open the column selector and look for Location in the list.
 6. Narrow the Location filter to a single location and read the headers again.
-7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.</t>
+7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.
+8. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1081,12 +1082,13 @@
 4. An invoice row always shows its own exact location — never "Multiple".
 5. Location is NOT offered in the column selector — it appears and disappears on its own, following the location scope.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+8. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8603 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows)</t>
+          <t>SV-8603; SV-8612; SV-8613 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -3019,7 +3021,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3060,7 +3062,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
+          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3071,7 +3073,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R13 — the Expanded CSV now has thirteen columns INCLUDING Asset; with per-level blank-cell rules; the old flat twelve-column shape is superseded)</t>
+          <t>SV-8612; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3119,7 +3121,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R10; S14-R11; S14-R12; S14-R13)</t>
+          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3261,7 +3263,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R5; S15-R6)</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3358,7 +3360,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R12; S15-R13; S15-R14; S15-R15)</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3398,7 +3400,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded View PDF's body table has the same thirteen columns, in the same order and with the same labels, as the Expanded View CSV — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
+          <t>1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
 3. The Date cell is blank on customer rows and on asset rows, matching the screen.
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
@@ -3409,7 +3411,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 — Expanded PDF body = the Expanded columns with the asset layer; one block per customer; the title is the same for both versions)</t>
+          <t>SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3458,7 +3460,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3549,12 +3551,12 @@
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. The Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns.</t>
+5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 — the four-item Summary/Expanded menu and the Summary column list are now spec-ratified)</t>
+          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 + Story 4 S4-R13 — four-item Summary/Expanded menu and the Summary column list; plus the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales By Customer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sales By Customer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -528,12 +528,12 @@
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
-5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it as the known pending change — do not change the test.</t>
+5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (SBC spec Story 1 S1-R1; S1-R3; S1-R4 — Performance group + below-the-anchors placement per the PRD companion video 2026-07-30; access = ordinary reports permission per Chris Ward answer 2026-07-31 Q4=A)</t>
+          <t>SV-8600 (SBC spec S1-R1; S1-R3; S1-R4 — Confluence 577634305 v-2026-07-31; Performance-group placement per the PRD video 2026-07-30; access = ordinary reports permission per Chris Ward 2026-07-31 Q4=A + SV-8598 sheet Q1=A)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -577,12 +577,12 @@
           <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it as the known pending change — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (SBC spec Story 1 S1-R2 — OVERRULED by Chris Ward answer 2026-07-31 Q4=A "the intention is to not hide these from normal reports access"; S1-R2 + the build still use a dedicated permission; dev change ticket raised)</t>
+          <t>SV-8600 (SBC spec S1-R2 — Confluence 577634305 v-2026-07-31 — now reads "gated by ordinary reports access; not by a report-specific permission"; Chris Ward Q1=A; built atom hidden-and-inert per his ruling; SV-8780 Ready to Fix)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -627,12 +627,12 @@
           <t>1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it as the known pending change — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8600 (SBC spec Story 1 S1-N1 — permission model RULED to the ordinary reports access by Chris Ward answer 2026-07-31 Q4=A; the build still ships a dedicated permission)</t>
+          <t>SV-8600 (SBC spec S1-N1 — Confluence 577634305 v-2026-07-31 — now reads "A user without reports access does not see the report in navigation and cannot open it by direct link"; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -741,173 +741,222 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>No Sales By Customer permission is offered in the role permission editor</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Permissions</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as an administrator who can edit roles and their permissions.
+2. Create a throwaway custom role named starting with ZZAUTOTEST to work in, and delete it when you have finished.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the area where a role's permissions are switched on and off.
+2. Read through the reports-related permissions from top to bottom.
+3. Search the permission list for "Sales By Customer".</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
+2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
+3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SV-8598 (SBC spec S1-R2 — Confluence 577634305 v-2026-07-31 — "there is no dedicated Sales By Customer View permission"; Chris Ward Q1=A + his ruling to hide an already-built permission from the front end; SV-8780)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Date range picker offers eleven options in the specified order</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>SBC — Date Range Filter</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Find the date range picker in the report toolbar.
 2. Open it and read the options from top to bottom.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R1; S2-R2)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Custom range opens a start/end date dialog and cannot exceed a 366-day span</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>SBC — Date Range Filter</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Open the date range picker and choose "Custom."
 2. In the dialog that opens, pick a start and end date less than 366 days apart and apply.
 3. Open "Custom" again and try to pick a start and end date MORE than 366 days apart.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Choosing "Custom" opens a date-picker dialog for a start and end date.
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R3; S2-R4; S2-N2)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Changing the date range writes it into the page link for sharing</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>SBC — Date Range Filter</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range (for example to "Last Month").
 2. Look at the browser's address bar.
 3. Copy the page link, open it in a fresh browser profile with no saved view for this report, and check the date range.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R6; S2-R9 (context))</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Product Type: three options with Parts &amp; Service default; S/P prefix filtering</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>SBC — Product Type Filter</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with no saved view (first visit or cleared browser storage), so the first-load default can be read.
 2. The date range contains at least one service invoice (number starting with S) and one parts invoice (number starting with P) — seed ZZAUTOTEST data if needed.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Find the "Product Type" dropdown in the report toolbar; read its value before touching it, then open it and read the options in order.
 2. Set Product Type to "Service only," expand a customer down to invoice rows, and read the invoice numbers.
@@ -915,7 +964,7 @@
 4. Set Product Type back to "Parts &amp; Service."</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
 2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
@@ -924,41 +973,41 @@
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>SV-8602 (specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Location filter: rightmost, lists accessible locations, All locations on top</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report as a user with access to two or more locations.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Look at the report toolbar's filters from left to right.
 2. Open the location filter and read its options.
@@ -966,7 +1015,7 @@
 4. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. The location filter is the rightmost filter in the toolbar.
 2. It lists the locations the signed-in user has access to.
@@ -975,42 +1024,42 @@
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>SV-8603 (SBC spec Story 4 S4-R1; S4-R2; S4-R3 + single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A; applied suite-wide)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Selecting locations scopes the data; All locations covers every accessible one</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. At least two accessible locations each have invoices in the chosen date range (seed ZZAUTOTEST data if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A in the location filter and note the customers/totals.
 2. Select locations A and B together and note the change.
@@ -1018,7 +1067,7 @@
 4. With "All locations" active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
@@ -1027,42 +1076,42 @@
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>SV-8603 (SBC spec Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10; [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward msg 2026-07-29 [newest-wins]</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>The Location column shows only with more than one location; Multiple on totals</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report as a user with access to two or more locations.
 2. At least one customer has invoices at two different locations, and at least one asset has invoices at two different locations.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations in the Location filter and read the column headers.
 2. Read the Location cell on a customer row whose invoices are all at one location.
@@ -1074,7 +1123,7 @@
 8. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
 2. A customer or asset row whose invoices are all at one location shows that location's name.
@@ -1086,48 +1135,48 @@
 8. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>SV-8603; SV-8612; SV-8613 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Customer filter sits between Product Type and Location, carries a search icon</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer in the current results.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar filters from left to right.
 2. Open the Customer filter without typing anything.
 3. Read what the dropdown shows before any query is typed.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
@@ -1135,97 +1184,97 @@
 4. The hint yields to the typed query while you are searching.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Typing in the Customer filter lists matching customers by contains match</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. At least two customers with distinct names have invoices in the current date range/Product Type/location (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and type a fragment from the MIDDLE of a customer's name, in different letter case (for example type "corp" for "Acme Corp").
 2. Read the list of customers shown.
 3. Click one listed customer to select it and look at its row in the dropdown.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Pinned control toggles All customers and Clear all; clearing shows empty state</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with several customers in the current results.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter while it is in the all-customers state and read the pinned control at the top of the dropdown.
 2. Activate it ("Clear all") and read the table body, the totals row, and the filter's collapsed label.
 3. Read the pinned control again and activate it once more.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
@@ -1233,43 +1282,43 @@
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>First load starts in the all-customers state and the report shows every customer</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. Your browser has no saved view for this report.
 2. Several customers have invoices in the default date range.
 3. A customer exists that has invoices ONLY in a wider date range than the current one (seed a ZZAUTOTEST invoice dated last month if needed).</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read the Customer filter's collapsed label.
@@ -1277,7 +1326,7 @@
 4. Widen the date range so the customer with no matching invoices now has one; re-check the label and the rows.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
@@ -1285,41 +1334,41 @@
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Collapsed label reads None, the customer's name, or N selected</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and use "Clear all" to empty the selection; read the collapsed label.
 2. Select exactly one customer; read the collapsed label.
@@ -1327,7 +1376,7 @@
 4. Start typing a search query in the filter field and watch the field text, then clear the query or click away.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
@@ -1335,96 +1384,96 @@
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Changing the customer selection narrows the table and refreshes the totals</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Note the customers and the totals row values.
 2. Open the Customer filter, clear all, and select exactly two customers.
 3. Read the table rows and the totals row.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>A subset customer selection reconciles on a filter change; kept if present</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with three customers A, B, C where: A has invoices in both this month and last month; B has invoices only in this month; C has invoices only in last month (seed ZZAUTOTEST data as needed).
 2. Date range is This Month; you have selected exactly customers A and B in the Customer filter.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range to Last Month.
 2. Read the table rows and the Customer filter selection.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
@@ -1432,49 +1481,49 @@
 4. The Customer filter selection itself is not cleared by the date change.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Each customer gets one summary row with its invoice count in parentheses</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. A customer has a known number of matching invoices in the current date range (seed ZZAUTOTEST data so the count is predictable).</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Find that customer's row at the top level of the table.
 2. Read the text at the start of the row.
 3. Narrow the date range so fewer of that customer's invoices match, and re-read the count.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
@@ -1482,95 +1531,95 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>A customer with no matching invoices in the current view is not shown</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose invoices all fall OUTSIDE the current date range (seed if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains none of that customer's invoices.
 2. Look for the customer in the table.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-N1)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Expanding a customer reveals asset rows; chevrons toggle and are independent</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. A customer in the current view has invoices on at least two different vehicles (seed ZZAUTOTEST work orders on two assets if needed).
 2. At least two customers with assets are in the current view.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron control on customer A's summary row and read the rows that appear beneath it.
 2. Expand one of customer A's assets, then expand customer B.
 3. Click customer A's chevron again and check customer B.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
@@ -1581,370 +1630,370 @@
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Expanding an asset reveals its invoice rows with number link and date</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded a customer and can see its asset rows.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron on an asset row.
 2. Read the invoice detail rows that appear.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Invoices group into one asset row per vehicle record</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. A customer has two or more invoices on the SAME vehicle record and at least one invoice on a different vehicle (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer.
 2. Count the asset rows and compare each asset's invoice count with the invoices you created.
 3. If the environment has an older invoice with no vehicle record linked (only a stored vehicle snapshot), check which asset row it lands under.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R3)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Asset rows order A to Z with the Parts Sales bucket always last</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. A customer has invoices on at least two vehicles AND at least one no-vehicle invoice (counter/parts sale) in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the asset rows top to bottom.
 2. Click a financial column header to change the table sort, and re-read the asset rows.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Header-row chevron expands or collapses every customer on the current page</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Several customers are visible on the current page.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Hover the chevron in the table header row and read the tooltip.
 2. Click it and watch the customer rows.
 3. Hover it again and read the tooltip, then click it again.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Reload-causing changes collapse expansion; Customer filter typing does not</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one customer expanded down to invoice rows.
 2. Enough customers exist to fill more than one page of results (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. With rows expanded, open the Customer filter and TYPE a search query (do not change the selection); watch the expanded rows.
 2. Now change the date range (or Product Type, location, Customer selection, or sort).
 3. Look at the previously expanded rows, the loading state, and the set of customers on the page.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Edge: a single-invoice asset can still be expanded</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. Customer A has an asset with exactly one invoice; customer B has ONLY no-vehicle (counter/parts sale) invoices in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Expand customer A and click the chevron of the single-invoice asset.
 2. Expand customer B and read its asset rows.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. A customer has an invoice whose number starts with S but whose work order has NO vehicle (seed a ZZAUTOTEST no-vehicle service work order and invoice it, if the app allows).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Expand that customer.
 2. Find which asset row the S invoice sits under.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E3)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Reversed and voided invoices are excluded from every row; count and total</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. A customer has a known set of invoices in the current range, one of which you then reverse (or void) — seed ZZAUTOTEST data and note the totals before and after.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Note the customer's invoice count "(N)" and totals with all invoices normal.
 2. Reverse (or void) one of the invoices in the application.
@@ -1952,55 +2001,55 @@
 4. Expand down to invoice rows and look for the reversed invoice.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Every row type renders the same columns in the same order</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a customer expanded down to invoice rows and the totals row visible.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
 3. Inspect the font weights on a customer summary row (dev tools).</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
@@ -2008,46 +2057,46 @@
 4. Every cell on a customer summary row uses font-weight 600, except the Subtotal cell which uses font-weight 700.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Asset identified by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a VIN recorded, (b) one with no VIN but a Unit # recorded, (c) one with no VIN or Unit # but a plate recorded, (d) one with no VIN, Unit #, or plate (blank the fields as far as the asset form allows).</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read each asset row's label.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
@@ -2056,190 +2105,190 @@
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward msg 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's year/make/model rule)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. One customer has TWO ZZAUTOTEST assets whose labels come out identical (same year/make/model and same identifier situation), each with an invoice in range.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the two asset labels.
 2. Note which asset carries " (#1)" and which " (#2)".
 3. Reload the page and expand again.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R11)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>The invoice number opens the invoice in the same browser tab</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded an asset and can see at least one S invoice and (under another customer/asset if needed) one P invoice.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Click a service (S) invoice number link and note where it opens.
 2. Go back, then click a parts (P) invoice number link and note where it opens.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Browser back from an invoice restores filters; sort and columns; rows shut</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with non-default filters set (for example Last Month + Service only), a non-default sort, and one column hidden.
 2. You have expanded down to an invoice detail row.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Watch the browser address bar, then click an invoice number link.
 2. From the invoice page, press the browser back button.
 3. Check the report's filters, sort, visible columns, and row expansion.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Customer name is plain text; the invoice link never turns visited-purple</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded down to invoice detail rows and have already clicked at least one invoice link earlier in the session.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Try clicking the customer NAME on a summary row.
 2. Look at an invoice number link at rest, on hover, and one you have already visited.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
@@ -2247,89 +2296,89 @@
 4. The link never recolors to the browser's visited-link (purple) color.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>An invoice deleted after load shows the not-found state and back returns</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with an invoice detail row visible.
 2. In another tab/session, that invoice is deleted or reversed AFTER the report loaded (do not refresh the report).</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Back in the report (unrefreshed), click that invoice's number link.
 2. Read the destination page, then press the browser back button.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N1)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>All columns sortable except chevron; text alphabetical, numbers by value</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. Several customers with differing values are in the current view.
 2. A customer with multiple assets and invoices is in the view.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
@@ -2337,194 +2386,194 @@
 4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Default sort is Customer name ascending case-insensitive</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. No saved view exists (first visit or cleared storage).
 2. Customer names with mixed upper/lower-case first letters exist in the view (seed ZZAUTOTEST names like "acme test" and "Best Test").</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the customer order.
 2. Click the Subtotal header and read the order again.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Missing values sort to the bottom ascending and to the top descending</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer row shows an em dash (—) in Margin % (Subtotal zero or below — seed a zero-subtotal case if possible) alongside rows with real Margin % values.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Margin % ascending and note where the em-dash row lands.
 2. Sort by Margin % descending and note it again.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sorting by Date orders customers by their most recent invoice date</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Two customers exist whose most recent invoice dates differ clearly (seed ZZAUTOTEST invoices on different dates).</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date column header.
 2. Compare the customer order with each customer's most recent invoice date (expand to check the invoice dates).</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Financial columns run in the specified order with Subtotal and Margin rules</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known labor, parts, and shop-supply amounts and known costs, in the current range.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Expand down to that invoice's detail row and read its values.
 3. Recalculate Subtotal and Margin by hand from the known amounts.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
@@ -2532,48 +2581,48 @@
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Margin % is Margin over Subtotal to one decimal; em dash when Subtotal &lt;= 0</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Rows with a normal positive Subtotal exist, and (if seedable) one row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on a customer row, an asset row, and an invoice row; recalculate one by hand (Margin ÷ Subtotal × 100).
 2. Find (or seed) a row with Subtotal ≤ 0 and read its Margin % cell.
 3. Look at the Margin % coloring.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
@@ -2581,47 +2630,47 @@
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim; value shows +green / -red / 0.0 on every row</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist where billed hours exceed worked hours, where worked exceeds billed, and where they are equal (seed ZZAUTOTEST work orders with clocked time).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
@@ -2631,143 +2680,143 @@
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is never blank: no-labor rows and near-zero values both show 0.0</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice (no labor at all) exists in range; if possible also an invoice whose delta rounds to zero (for example +0.04).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
 2. If seeded, read the near-zero row's Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Invoice subtotals sum to their asset row and asset subtotals to the customer</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. A customer with two or more assets, each with two or more invoices, is in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and every asset.
 2. Sum the invoice-level values by hand for each column and compare with each asset row.
 3. Sum the asset rows and compare with the customer row.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R13)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Subtotal is the rightmost column; pinned on scroll and bold everywhere</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, on a window narrow enough to force horizontal scrolling (or with all columns visible).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Subtotal column is the last column on the right.
 2. Scroll the table sideways and watch the Subtotal column.
 3. Inspect the font weight of the Subtotal header, a customer row, an asset row, an invoice row, and the totals row.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
@@ -2775,95 +2824,95 @@
 4. This holds regardless of permission, data, filters, or sort — the Subtotal column is always present, pinned, and bold.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8609 (specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The totals row covers the whole filtered set; not just the current page</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page of results, with known amounts (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Read the totals row on page 1.
 2. Move to page 2 and read the totals row again.
 3. Compare the totals against the sum over ALL matching customers (not just one page).</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Column selector is its own toolbar button with nine toggles all on</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no saved column selection (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector button in the toolbar's action area, next to the overflow menu.
 2. Hover it and read the tooltip.
 3. Click it and read the toggle list top to bottom.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
@@ -2871,137 +2920,137 @@
 4. With no saved selection, all nine toggleable columns default to visible.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Column toggles hide header+cells; Customer, Subtotal and chevron never in list</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data and the column selector open.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Turn the "Shop Supplies" toggle off, then on again, watching the table.
 2. Read the toggle list for Customer, Subtotal, or a chevron entry.
 3. Turn all nine toggles off and read the table.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to 4 Summary/Expanded items by Chris Ward msg 2026-07-29 [newest-wins] [extends video P21]; 'Print' REMOVED per video P25 [same msg confirms])</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Download file names carry the version and the active date range</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Set the range to This Month, choose "Download Summary (CSV)" and note the downloaded file name.
 2. Choose "Download Expanded View (CSV)" and note that file name.
@@ -3010,7 +3059,7 @@
 5. Repeat steps 1-3 for "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
 2. {range} follows this map: Today → today; Yesterday → yesterday; This Week → this_week; Last Week → last_week; This Month → this_month; Last Month → last_month; This Year → this_year; Last Year → last_year; This Quarter → this_quarter; Last Quarter → last_quarter; Custom → custom.
@@ -3019,48 +3068,48 @@
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
@@ -3071,47 +3120,47 @@
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>CSV formats: Margin % plain; dates mm-dd-yyyy; currency plain; no color</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
@@ -3119,189 +3168,189 @@
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF hold exactly the customers matching the active filters and sort</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Each download item shows a loading state and its own export-failed toast</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a large enough data set that a download takes a visible moment.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
 2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
 3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3309,48 +3358,48 @@
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - old 'location not in the header' rule REVERSED by the Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With no uploaded logo, the bundled ShopView logo is used.
@@ -3358,47 +3407,47 @@
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF body matches the CSV's columns and on-screen rules</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Read the body table's columns and row structure.
 2. Check a date cell, a customer row's Date cell, a Margin % dash, the Subtotal column weight, and the Inv. Hrs colors (use a color picker on the PDF if available).</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
@@ -3409,48 +3458,48 @@
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose "Download (CSV)".
 2. Choose "Download (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3458,94 +3507,94 @@
 4. Below the cap the export succeeds normally.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>A no-match export still downloads headers and a zero totals row</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and open the file.
 2. Choose "Download (PDF)" and open the file.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the four items.
 2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
 3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
@@ -3554,95 +3603,95 @@
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 + Story 4 S4-R13 — four-item Summary/Expanded menu and the Summary column list; plus the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -3650,143 +3699,143 @@
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R7)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -3796,135 +3845,135 @@
 6. All nine toggleable columns visible.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R9)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -3933,7 +3982,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -3942,133 +3991,133 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>The empty-state message never appears while the table is still loading</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Change a filter and watch the table area during the load.
 2. Watch what appears once loading finishes with zero customers.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
 2. The message appears only after the table finishes its initial loading and shows zero customers.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-N1)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser with dev tools available.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the page background, toolbar surface, and paddings with dev tools.
 2. Check the toolbar's position against the top of the page and the table against the side edges.
@@ -4076,7 +4125,7 @@
 4. Check the line between the toolbar and the headers, the date-range picker's dropdown arrow size, the table corners, and the outermost cell paddings.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The page has no padding; the page background is the standard blue-grey (#f9fafb in light mode).
 2. The toolbar surface is white (#ffffff); its padding is 32px top, 24px bottom, and 2rem left and right; it touches the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4087,48 +4136,48 @@
 7. When the table content does not fill the viewport, the blue-grey page background shows through below the table — no white strip.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4137,183 +4186,183 @@
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R18)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4321,55 +4370,55 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -4377,155 +4426,155 @@
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -828,7 +828,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R1; S2-R2)</t>
+          <t>SV-8601 (SBC spec v12 2026-07-29 Story 2 S2-R1; S2-R2 — S2-R2 CLOSES the eleven-option list and its order itself; so the closed list IS the requirement; re-check this case whenever S2-R2 changes)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8602 (specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6)</t>
+          <t>SV-8602 (SBC spec v12 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6 — S3-R2 CLOSES the list itself ("exactly three options ... in this order"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1)</t>
+          <t>SV-8605 (SBC spec v12 2026-07-29 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2917,12 +2917,13 @@
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
-4. With no saved selection, all nine toggleable columns default to visible.</t>
+4. With no saved selection, all nine toggleable columns default to visible.
+5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7)</t>
+          <t>SV-8611 (SBC spec v12 2026-07-29 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3018,7 +3019,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to 4 Summary/Expanded items by Chris Ward msg 2026-07-29 [newest-wins] [extends video P21]; 'Print' REMOVED per video P25 [same msg confirms])</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3360,7 +3361,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - old 'location not in the header' rule REVERSED by the Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3605,7 +3606,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 + Story 4 S4-R13 — four-item Summary/Expanded menu and the Summary column list; plus the automatic Location column in every export)</t>
+          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -828,7 +828,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (SBC spec v12 2026-07-29 Story 2 S2-R1; S2-R2 — S2-R2 CLOSES the eleven-option list and its order itself; so the closed list IS the requirement; re-check this case whenever S2-R2 changes)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R1; S2-R2 — S2-R2 CLOSES the eleven-option list and its order itself; so the closed list IS the requirement; re-check this case whenever S2-R2 changes)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8602 (SBC spec v12 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6 — S3-R2 CLOSES the list itself ("exactly three options ... in this order"); so the closed list IS the requirement)</t>
+          <t>SV-8602 (SBC spec v13 2026-07-31 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6 — S3-R2 CLOSES the list itself ("exactly three options ... in this order"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (SBC spec v12 2026-07-29 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (SBC spec v12 2026-07-29 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
+          <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
+          <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -862,9 +862,9 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Open the date range picker and choose "Custom."
-2. In the dialog that opens, pick a start and end date less than 366 days apart and apply.
-3. Open "Custom" again and try to pick a start and end date MORE than 366 days apart.</t>
+          <t>1. Open the date range picker. A month calendar is shown inside it, which is how a custom start and end date are picked on this build.
+2. Pick a start and end date less than 366 days apart on that calendar and apply.
+3. Open the picker again and try to pick a start and end date MORE than 366 days apart.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4577,6 +4577,60 @@
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>The back end serves SBC report data and export on ordinary reports access</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SBC — API</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
+2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as the user WHO HAS ordinary reports access and open Sales By Customer.
+2. In the network panel, find the request the page makes for the report's data and read its response code.
+3. From the three-dot menu choose "Download Summary (CSV)" and read the response code of the export request.
+4. Sign out and sign in as the user WITHOUT reports access.
+5. Try to open Sales By Customer by typing its address directly, and read the response code of the data request.
+6. Ask for the same export by its address and read that response code too.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
+2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
+3. For the user WITHOUT reports access, the data request is refused with HTTP 403 and a message reading "Access denied." — no report data comes back.
+4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
+5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>SV-8600 (SBC spec v13 2026-07-31 S1-R2; S1-N1 — the back-end half of the ordinary-reports-access gate; the SBC twin of the Parts Velocity back-end case C30391; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -528,7 +528,9 @@
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
-5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -577,7 +579,9 @@
           <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -627,7 +631,9 @@
           <t>1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-N1).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -675,12 +681,14 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard access-denied state.
-2. Pressing back returns you to the Sales By Customer report.</t>
+2. Pressing back returns you to the Sales By Customer report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N2).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N2)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-N2)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -727,12 +735,14 @@
           <t>1. The administrator's filter lists every location in the organization.
 2. The non-administrator's filter lists only the locations assigned to them.
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
-4. The report data never includes invoices from a location the user does not have access to.</t>
+4. The report data never includes invoices from a location the user does not have access to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R7; S4-R8; S4-R9; S4-N1)</t>
+          <t>SV-8603 (SBC spec v13 2026-07-31 Story 4 S4-R7; S4-R8; S4-R9; S4-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -776,7 +786,9 @@
         <is>
           <t>1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
-3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,7 +835,9 @@
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
-3. There is no "All Time" option.</t>
+3. There is no "All Time" option.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -869,14 +883,16 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Choosing "Custom" opens a date-picker dialog for a start and end date.
+          <t>1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen on this build. There is no separate "Custom" item to choose.
 2. A range of 366 days or fewer applies normally.
-3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.</t>
+3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R3; S2-R4; S2-N2)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R3; S2-R4; S2-N2)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -918,12 +934,14 @@
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. The chosen date range value is written into the page link.
-2. Opening that link in a browser with no saved view for this report restores the sender's date range.</t>
+2. Opening that link in a browser with no saved view for this report restores the sender's date range.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R6; S2-R9 (context))</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R6; S2-R9 (context))</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -970,7 +988,9 @@
 2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
 3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
-5. The whole invoice is classified by its number prefix — there is no per-line-item split.</t>
+5. The whole invoice is classified by its number prefix — there is no per-line-item split.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1021,7 +1041,9 @@
 2. It lists the locations the signed-in user has access to.
 3. An "All locations" option is pinned to the top.
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
-5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.</t>
+5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1073,7 +1095,9 @@
 2. Adding a second location adds that location's invoices to the rows and totals.
 3. With "All locations," the report includes data from every location the user has access to.
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1119,8 +1143,7 @@
 4. Expand to an invoice row and read its Location cell.
 5. Open the column selector and look for Location in the list.
 6. Narrow the Location filter to a single location and read the headers again.
-7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.
-8. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
+7. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1131,13 +1154,14 @@
 4. An invoice row always shows its own exact location — never "Multiple".
 5. Location is NOT offered in the column selector — it appears and disappears on its own, following the location scope.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-8. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)</t>
+7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8603; SV-8612; SV-8613 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
+          <t>SV-8603; SV-8612; SV-8613 (SBC spec v13 2026-07-31 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1181,12 +1205,14 @@
           <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
-4. The hint yields to the typed query while you are searching.</t>
+4. The hint yields to the typed query while you are searching.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R1; S18-R2)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1230,12 +1256,14 @@
         <is>
           <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
-3. A selected customer is shown with a checkmark.</t>
+3. A selected customer is shown with a checkmark.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1279,12 +1307,14 @@
           <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
 3. The control is pinned to the top of the dropdown in both states.
-4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."</t>
+4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R3; S18-N1; S17-E1)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1331,12 +1361,14 @@
           <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
-4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.</t>
+4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1381,12 +1413,14 @@
           <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
-4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.</t>
+4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R5)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1429,12 +1463,14 @@
         <is>
           <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
-3. The totals row updates to cover only the selected customers' matching invoices.</t>
+3. The totals row updates to cover only the selected customers' matching invoices.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R5; S18-R11)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1478,12 +1514,14 @@
           <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
 3. Customer C (newly present) is NOT auto-selected and is not shown.
-4. The Customer filter selection itself is not cleared by the date change.</t>
+4. The Customer filter selection itself is not cleared by the date change.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R9; S18-E1)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1527,13 +1565,16 @@
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
-3. The count is rendered in color #616161 at font-weight 600, the same font size as the name.
-4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.</t>
+3. The count is the same size as the customer name next to it, in a slightly softer grey, and is easy to read.
+4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
+5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1574,12 +1615,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. The customer is not shown — there are no zero-value placeholder rows.</t>
+          <t>1. The customer is not shown — there are no zero-value placeholder rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-N1).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-N1)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-N1)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1627,12 +1670,14 @@
 4. The Date cell is blank on asset rows.
 5. Asset rows are indented one level under the customer.
 6. Each chevron toggles back to collapsed on a second activation.
-7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.</t>
+7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1674,12 +1719,14 @@
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
-3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.</t>
+3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1721,12 +1768,14 @@
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
-2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.</t>
+2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R3).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R3)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R3)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1768,12 +1817,14 @@
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
-3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.</t>
+3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1816,12 +1867,14 @@
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
-3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.</t>
+3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1865,12 +1918,14 @@
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
-3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.</t>
+3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1911,12 +1966,14 @@
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
-2. Customer B shows a single "Parts Sales" row and no vehicle rows.</t>
+2. Customer B shows a single "Parts Sales" row and no vehicle rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E1; S8-E2)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1956,12 +2013,14 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.</t>
+          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E3).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E3)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E3)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2005,12 +2064,14 @@
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
-3. The customer/asset totals drop by exactly that invoice's amounts.</t>
+3. The customer/asset totals drop by exactly that invoice's amounts.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2046,7 +2107,7 @@
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
-3. Inspect the font weights on a customer summary row (dev tools).</t>
+3. Look at a customer summary row and compare how heavy its text looks with the invoice rows beneath it.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2054,12 +2115,15 @@
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
 3. The Date cell on the customer summary row is blank.
-4. Every cell on a customer summary row uses font-weight 600, except the Subtotal cell which uses font-weight 700.</t>
+4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
+5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2102,7 +2166,9 @@
 2. Asset (b) (no VIN) is identified by its Unit # instead.
 3. Asset (c) (no VIN or Unit #) is identified by its plate instead.
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
-5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.</t>
+5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2149,12 +2215,14 @@
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
-2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.</t>
+2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R11).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R11)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R11)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2196,12 +2264,14 @@
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
-3. A parts invoice opens the associated part sale's Part Requests tab.</t>
+3. A parts invoice opens the associated part sale's Part Requests tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2245,12 +2315,14 @@
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
-3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).</t>
+3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R3; S9-R4)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2293,12 +2365,14 @@
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
 3. The link has no underline at rest, on hover, or after it has been clicked.
-4. The link never recolors to the browser's visited-link (purple) color.</t>
+4. The link never recolors to the browser's visited-link (purple) color.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2340,12 +2414,14 @@
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
-2. Pressing back returns you to the report.</t>
+2. Pressing back returns you to the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N1).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N1)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-N1)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2390,12 +2466,14 @@
         <is>
           <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
-3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.</t>
+3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2437,12 +2515,14 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
-2. Clicking a column header replaces the default with that column's sort.</t>
+2. Clicking a column header replaces the default with that column's sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2483,12 +2563,14 @@
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
-2. Descending: the em-dash row sorts to the top.</t>
+2. Descending: the em-dash row sorts to the top.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R3).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R3)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2529,12 +2611,14 @@
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
-2. The Date cells on customer rows stay blank — the sort still works.</t>
+2. The Date cells on customer rows stay blank — the sort still works.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R5).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R5)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2578,7 +2662,9 @@
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
-4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).</t>
+4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2627,12 +2713,14 @@
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
 3. Margin % is monochrome — no green or red coloring.
-4. The same calculation and format apply to customer rows, asset rows, and invoice rows.</t>
+4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2677,12 +2765,14 @@
 3. A positive value shows a leading + sign in the application's standard positive (green) color — for example, +1.5.
 4. A negative value shows a leading - sign in the standard negative (red) color — for example, -1.5.
 5. A zero/break-even value shows 0.0 in the default text color.
-6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.</t>
+6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
+          <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2724,12 +2814,14 @@
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
-3. A negative value shows a minus sign and one decimal — for example, -0.5.</t>
+3. A negative value shows a minus sign and one decimal — for example, -0.5.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2)</t>
+          <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2772,12 +2864,14 @@
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
-3. This holds for every financial column, not only Subtotal.</t>
+3. This holds for every financial column, not only Subtotal.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R13).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R13)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R13)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2820,13 +2914,15 @@
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
-3. Subtotal values are rendered at font-weight 700 on the header, every customer/asset/invoice row, and the totals row.
-4. This holds regardless of permission, data, filters, or sort — the Subtotal column is always present, pinned, and bold.</t>
+3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
+4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8609 (specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
+          <t>SV-8609 (SBC spec v13 2026-07-31 Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2868,12 +2964,14 @@
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
-2. The totals do not change when you move between pages — they never reflect only the visible page.</t>
+2. The totals do not change when you move between pages — they never reflect only the visible page.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2918,7 +3016,9 @@
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.</t>
+5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2966,12 +3066,14 @@
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
-3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.</t>
+3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1)</t>
+          <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3014,7 +3116,9 @@
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
-3. There are no separate always-visible export buttons - all exports live behind this one menu.</t>
+3. There are no separate always-visible export buttons - all exports live behind this one menu.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3066,12 +3170,14 @@
 2. {range} follows this map: Today → today; Yesterday → yesterday; This Week → this_week; Last Week → last_week; This Month → this_month; Last Month → last_month; This Year → this_year; Last Year → last_year; This Quarter → this_quarter; Last Quarter → last_quarter; Custom → custom.
 3. For Custom the literal word "custom" is used — the actual start and end dates are not in the file name.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
-5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.</t>
+5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3118,12 +3224,14 @@
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
 5. Customer names are plain — the "(N)" invoice count is not included.
 6. Work with no vehicle appears as an asset row named "Parts Sales".
-7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.</t>
+7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
+          <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3166,12 +3274,14 @@
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
-4. The CSV has no color; the signed Inv. Hrs value still conveys direction.</t>
+4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
+          <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3214,12 +3324,14 @@
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
-3. The chosen date range and Product Type are reflected in both exports.</t>
+3. The chosen date range and Product Type are reflected in both exports.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3248,7 +3360,8 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with a large enough data set that a download takes a visible moment.</t>
+          <t>1. You are on the report with a large enough data set that a download takes a visible moment.
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3262,12 +3375,14 @@
         <is>
           <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
-3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.</t>
+3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3308,12 +3423,14 @@
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
-2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."</t>
+2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3356,7 +3473,9 @@
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
-4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).</t>
+4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3405,12 +3524,14 @@
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With no uploaded logo, the bundled ShopView logo is used.
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
-4. The logo is embedded in the PDF (renders offline, not loaded from a network address).</t>
+4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3439,7 +3560,8 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.</t>
+          <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.
+2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3456,12 +3578,14 @@
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
 5. The Subtotal column is bold - header, every row, and the totals row.
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
-7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.</t>
+7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
+          <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3505,12 +3629,15 @@
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
-4. Below the cap the export succeeds normally.</t>
+4. Below the cap the export succeeds normally.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3551,12 +3678,14 @@
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The export still downloads — no error and no warning is shown.
-2. The file contains the column headers and a totals row of zeros, with no data rows.</t>
+2. The file contains the column headers and a totals row of zeros, with no data rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R10).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R10)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R10)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3601,7 +3730,9 @@
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).</t>
+5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3648,12 +3779,14 @@
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
-2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.</t>
+2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3697,12 +3830,14 @@
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
 3. The scroll position is not restored.
-4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.</t>
+4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3745,12 +3880,14 @@
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
-3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.</t>
+3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3791,12 +3928,14 @@
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
-2. Sales By Customer still restores its own saved view.</t>
+2. Sales By Customer still restores its own saved view.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R7).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R7)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3843,12 +3982,14 @@
 3. Location = the single location you are currently working in (your active location) — not all locations.
 4. Customer filter = all customers selected (label "All customers").
 5. Sort = Customer name ascending.
-6. All nine toggleable columns visible.</t>
+6. All nine toggleable columns visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3890,12 +4031,14 @@
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
-2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.</t>
+2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R9).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R9)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3937,12 +4080,14 @@
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
-2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.</t>
+2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R8)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3989,12 +4134,14 @@
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
-5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.</t>
+5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4023,7 +4170,8 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).</t>
+          <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4035,12 +4183,14 @@
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
-2. The message appears only after the table finishes its initial loading and shows zero customers.</t>
+2. The message appears only after the table finishes its initial loading and shows zero customers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-N1).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-N1)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4069,7 +4219,8 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. You can interrupt the network (browser dev tools offline mode).</t>
+          <t>1. You can interrupt the network (browser dev tools offline mode).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4081,7 +4232,9 @@
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
-2. The toast auto-fades after 5 seconds.</t>
+2. The toast auto-fades after 5 seconds.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4120,26 +4273,31 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Inspect the page background, toolbar surface, and paddings with dev tools.
-2. Check the toolbar's position against the top of the page and the table against the side edges.
-3. Compare the title's left edge and the action cluster's right edge with the leftmost/rightmost data-cell positions.
-4. Check the line between the toolbar and the headers, the date-range picker's dropdown arrow size, the table corners, and the outermost cell paddings.</t>
+          <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
+2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
+3. Compare the left edge of the title and the right edge of the action cluster with the leftmost and rightmost columns of data.
+4. Look at the line between the toolbar and the column headers, the size of the date-range picker's dropdown arrow next to the other filter arrows, the table's corners, and the space at the far left and far right of the rows.
+5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. The page has no padding; the page background is the standard blue-grey (#f9fafb in light mode).
-2. The toolbar surface is white (#ffffff); its padding is 32px top, 24px bottom, and 2rem left and right; it touches the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
-3. The left edge of the title and the right edge of the action cluster line up with the leftmost and rightmost data-cell positions.
-4. A 1px horizontal line in the standard table-header border color separates the toolbar from the column headers.
-5. The date-range picker's dropdown arrow is 24px, the same size as the other filter dropdown arrows.
-6. The table has no rounded corners; the leftmost cell (header, body, totals) has 2rem left padding and the rightmost cell 2rem right padding.
-7. When the table content does not fill the viewport, the blue-grey page background shows through below the table — no white strip.</t>
+          <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
+2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
+3. The left edge of the title lines up with the leftmost column of data, and the right edge of the action cluster lines up with the rightmost column.
+4. A thin dividing line separates the toolbar from the column headers.
+5. The date-range picker's dropdown arrow is the same size as the other filter dropdown arrows next to it.
+6. The table has square corners, and the first and last columns sit clear of the left and right edges of the table — the text is not touching the edge.
+7. When there are too few rows to fill the screen, the blue-grey page background shows through below the table — there is no white strip left over.
+8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
+9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4168,7 +4326,8 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report in light mode with a customer expanded down to invoice rows.</t>
+          <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
+2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4184,12 +4343,14 @@
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
 3. The totals row uses the white surface with a top border and bold text (white on purpose, matching Technician Efficiency).
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
-5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.</t>
+5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4230,12 +4391,14 @@
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
-2. The PDF export always renders in light-mode colors regardless of the user's app mode.</t>
+2. The PDF export always renders in light-mode colors regardless of the user's app mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R18).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R18)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4278,12 +4441,14 @@
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
-3. At 1024px and above the toolbar uses the desktop single-row layout.</t>
+3. At 1024px and above the toolbar uses the desktop single-row layout.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3)</t>
+          <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4326,12 +4491,14 @@
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
-3. The invoice number link opens the invoice in the same tab, the same as on desktop.</t>
+3. The invoice number link opens the invoice in the same tab, the same as on desktop.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6)</t>
+          <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4360,7 +4527,8 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with several customers, with the browser's network activity panel open.</t>
+          <t>1. You are on the report with several customers, with the browser's network activity panel open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4375,12 +4543,14 @@
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
-3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.</t>
+3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4409,7 +4579,8 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
+          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4424,12 +4595,14 @@
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
 3. The ordering is not done by re-shuffling rows already in the browser.
-4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.</t>
+4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4458,7 +4631,8 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with the browser's network panel open.</t>
+          <t>1. You are on the report with the browser's network panel open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4472,12 +4646,14 @@
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
-3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.</t>
+3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4506,7 +4682,8 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
+          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4520,12 +4697,14 @@
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
-3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.</t>
+3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4554,7 +4733,8 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.</t>
+          <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4566,12 +4746,15 @@
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
-2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.</t>
+2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
+          <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4601,7 +4784,8 @@
       <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
-2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.</t>
+2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4620,7 +4804,9 @@
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
 3. For the user WITHOUT reports access, the data request is refused with HTTP 403 and a message reading "Access denied." — no report data comes back.
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
-5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.</t>
+5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report in light mode on a desktop browser with dev tools available.</t>
+          <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -530,6 +530,8 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
@@ -837,6 +839,8 @@
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -887,6 +891,8 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
@@ -1043,6 +1049,8 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1156,6 +1164,8 @@
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
@@ -2168,6 +2178,8 @@
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3526,6 +3538,8 @@
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
@@ -3732,6 +3746,8 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
@@ -4116,7 +4132,8 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data on screen.</t>
+          <t>1. You are on the report with data on screen.
+2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4135,13 +4152,14 @@
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
+6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4150,7 +4168,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>The empty-state message never appears while the table is still loading</t>
+          <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4170,27 +4188,27 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).
+          <t>1. You can interrupt the network (browser dev tools offline mode).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>1. Change a filter and watch the table area during the load.
-2. Watch what appears once loading finishes with zero customers.</t>
+          <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
+2. Read the toast and time how long it stays.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
-2. The message appears only after the table finishes its initial loading and shows zero customers.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-N1).</t>
+          <t>1. An error toast is shown: "An error occurred while fetching the report data."
+2. The toast auto-fades after 5 seconds.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-N1)</t>
+          <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4199,17 +4217,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
+          <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SBC — Empty &amp; Edge States</t>
+          <t>SBC — Visual Conformance</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4219,59 +4237,10 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. You can interrupt the network (browser dev tools offline mode).
-2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
+          <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
-2. Read the toast and time how long it stays.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>1. An error toast is shown: "An error occurred while fetching the report data."
-2. The toast auto-fades after 5 seconds.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Visual Conformance</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
 2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
@@ -4280,7 +4249,7 @@
 5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4295,49 +4264,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4345,12 +4314,62 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Dark mode darkens every surface while the PDF always renders light</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Visual Conformance</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1. You can switch the application to dark mode.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
+2. While still in dark mode, download the PDF and open it.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
+2. The PDF export always renders in light-mode colors regardless of the user's app mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R18).</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4359,12 +4378,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Dark mode darkens every surface while the PDF always renders light</t>
+          <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SBC — Visual Conformance</t>
+          <t>SBC — Mobile</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4379,65 +4398,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1. You can switch the application to dark mode.</t>
+          <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
-2. While still in dark mode, download the PDF and open it.</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
-2. The PDF export always renders in light-mode colors regardless of the user's app mode.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R18).</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Mobile</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
@@ -4446,48 +4417,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
@@ -4496,42 +4467,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4539,7 +4510,7 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
@@ -4548,49 +4519,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -4600,49 +4571,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
@@ -4651,49 +4622,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
@@ -4702,48 +4673,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
@@ -4752,43 +4723,43 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>The back end serves SBC report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
 2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the user WHO HAS ordinary reports access and open Sales By Customer.
 2. In the network panel, find the request the page makes for the report's data and read its response code.
@@ -4798,7 +4769,7 @@
 6. Ask for the same export by its address and read that response code too.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
@@ -4809,13 +4780,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8600 (SBC spec v13 2026-07-31 S1-R2; S1-N1 — the back-end half of the ordinary-reports-access gate; the SBC twin of the Parts Velocity back-end case C30391; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -530,8 +530,6 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
@@ -839,8 +837,6 @@
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -891,8 +887,6 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
@@ -1049,8 +1043,6 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1164,8 +1156,6 @@
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
@@ -2178,8 +2168,6 @@
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3538,8 +3526,6 @@
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
@@ -3746,8 +3732,6 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
@@ -4132,8 +4116,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data on screen.
-2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
+          <t>1. You are on the report with data on screen.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4152,14 +4135,13 @@
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
-6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4314,8 +4296,6 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -530,6 +530,8 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
@@ -837,6 +839,8 @@
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -887,6 +891,8 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
@@ -1043,6 +1049,8 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1156,6 +1164,8 @@
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
@@ -2168,6 +2178,8 @@
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3526,6 +3538,8 @@
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
@@ -3732,6 +3746,8 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
@@ -4116,7 +4132,8 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data on screen.</t>
+          <t>1. You are on the report with data on screen.
+2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4135,13 +4152,14 @@
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
+6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4296,6 +4314,8 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -532,7 +532,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-N1).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
           <t>1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N2).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
 3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
           <t>1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-N1).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R3).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E3).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R11).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N1).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R3).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2625,7 +2625,7 @@
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R5).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R13).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
 4. With no saved selection, all nine toggleable columns default to visible.
 5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3287,8 +3287,10 @@
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
+On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3338,7 +3340,7 @@
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3389,7 +3391,7 @@
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3437,7 +3439,7 @@
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3487,7 +3489,7 @@
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3540,7 +3542,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3594,7 +3596,7 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3646,7 +3648,7 @@
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3694,7 +3696,7 @@
           <t>1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R10).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3748,7 +3750,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3797,7 +3799,7 @@
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3848,7 +3850,7 @@
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3898,7 +3900,7 @@
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3946,7 +3948,7 @@
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R7).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4000,7 +4002,7 @@
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4049,7 +4051,7 @@
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R9).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4098,7 +4100,7 @@
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4154,7 +4156,7 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4203,7 +4205,7 @@
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4261,7 +4263,7 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4316,7 +4318,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4364,7 +4366,7 @@
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R18).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4414,7 +4416,7 @@
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4464,7 +4466,7 @@
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4516,7 +4518,7 @@
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4568,7 +4570,7 @@
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4619,7 +4621,7 @@
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4670,7 +4672,7 @@
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4720,7 +4722,7 @@
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4777,7 +4779,7 @@
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -836,12 +836,10 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. A date range picker is visible in the report toolbar.
-2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
+3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -855,7 +853,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Custom range opens a start/end date dialog and cannot exceed a 366-day span</t>
+          <t>Building a custom range on the calendar cannot exceed a 366-day span</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -891,9 +889,7 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1049,9 +1045,7 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1160,13 +1154,14 @@
 2. A customer or asset row whose invoices are all at one location shows that location's name.
 3. A customer or asset row whose invoices come from more than one location shows "Multiple".
 4. An invoice row always shows its own exact location — never "Multiple".
-5. Location is NOT offered in the column selector — it appears and disappears on its own, following the location scope.
+5. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+---
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2178,9 +2173,7 @@
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3094,37 +3087,92 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>A one-location user never sees Location in the column-selection list</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Column Selector</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You are signed in as a person who has access to exactly ONE location. Check this in administration under that person's location access, and put their access back as you found it when you finish.
+3. This one test covers all six reports, so keep this same sign-in for the whole of it.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report and open the column-selection control (the toolbar button beside the overflow menu; hovering it reads "Column Selection.").
+2. Read the whole list of switches from top to bottom and look for an entry called Location.
+3. Do the same on Sales By Representative, then Parts Velocity, then Technician Utilization, then Work In Progress, then Inventory Value.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On every one of the six reports the column-selection list does NOT contain an entry called Location.
+2. Nothing else about each list changes - only the Location entry is missing.
+3. No Location column shows on the table either, because this person only ever has one location in view.
+4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 13 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
+AUTOMATION: HOLD - nobody has run this test yet, and it needs a sign-in that has access to exactly one location.
+</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R4 with S4-R12; the never-offered rule itself comes from Chris Ward's answer T1-1 option C of 2026-08-05 and is in no specification)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
@@ -3133,41 +3181,41 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Download file names carry the version and the active date range</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Set the range to This Month, choose "Download Summary (CSV)" and note the downloaded file name.
 2. Choose "Download Expanded View (CSV)" and note that file name.
@@ -3176,59 +3224,59 @@
 5. Repeat steps 1-3 for "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
-2. {range} follows this map: Today → today; Yesterday → yesterday; This Week → this_week; Last Week → last_week; This Month → this_month; Last Month → last_month; This Year → this_year; Last Year → last_year; This Quarter → this_quarter; Last Quarter → last_quarter; Custom → custom.
-3. For Custom the literal word "custom" is used — the actual start and end dates are not in the file name.
+2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Record the exact word the file uses for each - the mapping is confirmed in the build.
+3. For a range you built yourself on the calendar, record what the file name uses in place of a period name - the exact wording is confirmed in the build.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
@@ -3241,47 +3289,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>CSV formats: Margin % plain; dates mm-dd-yyyy; currency plain; no color</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
@@ -3293,48 +3341,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF hold exactly the customers matching the active filters and sort</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
@@ -3343,49 +3391,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Each download item shows a loading state and its own export-failed toast</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a large enough data set that a download takes a visible moment.
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
 2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
 3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
@@ -3394,47 +3442,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
@@ -3442,47 +3490,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3492,101 +3540,100 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
-2. With no uploaded logo, the bundled ShopView logo is used.
-3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
+2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
+3. When no logo is printed, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF body matches the CSV's columns and on-screen rules</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Read the body table's columns and row structure.
 2. Check a date cell, a customer row's Date cell, a Margin % dash, the Subtotal column weight, and the Inv. Hrs colors (use a color picker on the PDF if available).</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
@@ -3599,48 +3646,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose "Download (CSV)".
 2. Choose "Download (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3651,47 +3698,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>A no-match export still downloads headers and a zero totals row</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and open the file.
 2. Choose "Download (PDF)" and open the file.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
@@ -3699,102 +3746,155 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R10).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the four items.
 2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
 3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>A logo that is set but will not load falls back to the ShopView logo</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser and you can change the organization's uploaded logo in administration.
+2. You will need the organization in a state where a logo IS set but the picture will not load - for example an uploaded logo whose file has since been removed or renamed. Ask a developer to help you produce that state if you cannot.
+3. Write down the organization's original logo first, because you will put it back at the end.
+4. This one test covers the printable download on all six reports, so do the setup once and check all six.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. With a logo uploaded and loading normally, download the printable file from each of the six reports and look at the top right of the header.
+2. Put the organization into the state where a logo is set but the picture will not load.
+3. Download the printable file again from each of the six reports and look at the top right of the header.
+4. Remove the uploaded logo altogether, download again from each of the six reports, and look at the top right of the header.
+5. Put the organization's original logo back.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. With a logo that loads, that logo is shown at the top right, sized to fit without being stretched.
+2. With a logo that is set but will not load, the built-in ShopView logo is shown in its place - not a blank space, not a broken-picture icon, and no error message.
+3. With no logo uploaded at all, NO logo is shown and the header text spreads out to fill the space.
+4. All six reports behave the same way.
+5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 13 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
+AUTOMATION: HOLD - nobody has run this test yet, and it needs an organization whose logo is set but will not load, which a tester cannot always produce.
+</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
@@ -3802,48 +3902,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -3853,48 +3953,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
@@ -3903,47 +4003,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
@@ -3951,49 +4051,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R7).</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -4005,48 +4105,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
@@ -4054,48 +4154,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R9).</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
@@ -4103,42 +4203,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R8).</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.
 2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -4147,7 +4247,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -4159,48 +4259,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
@@ -4208,41 +4308,41 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
 2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
@@ -4251,7 +4351,7 @@
 5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4266,49 +4366,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4321,47 +4421,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
@@ -4369,48 +4469,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R18).</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
@@ -4419,48 +4519,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
@@ -4469,42 +4569,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4512,7 +4612,7 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
@@ -4521,49 +4621,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -4573,49 +4673,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
@@ -4624,49 +4724,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
@@ -4675,48 +4775,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
@@ -4725,43 +4825,43 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>The back end serves SBC report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
 2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the user WHO HAS ordinary reports access and open Sales By Customer.
 2. In the network panel, find the request the page makes for the report's data and read its response code.
@@ -4771,7 +4871,7 @@
 6. Ask for the same export by its address and read that response code too.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
@@ -4782,13 +4882,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8600 (SBC spec v13 2026-07-31 S1-R2; S1-N1 — the back-end half of the ordinary-reports-access gate; the SBC twin of the Parts Velocity back-end case C30391; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -524,15 +524,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
+          <t xml:space="preserve">1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
-5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
+5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -578,12 +578,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
+          <t xml:space="preserve">1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -630,12 +632,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Customer" does not appear in the Reports navigation.
+          <t xml:space="preserve">1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-N1).</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -682,10 +686,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. The destination page shows the application's standard access-denied state.
+          <t xml:space="preserve">1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -734,12 +740,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The administrator's filter lists every location in the organization.
+          <t xml:space="preserve">1. The administrator's filter lists every location in the organization.
 2. The non-administrator's filter lists only the locations assigned to them.
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -786,11 +794,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
+          <t xml:space="preserve">1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
-3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -835,11 +845,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. A date range picker is visible in the report toolbar.
+          <t xml:space="preserve">1. A date range picker is visible in the report toolbar.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -885,11 +897,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen on this build. There is no separate "Custom" item to choose.
+          <t xml:space="preserve">1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen. There is no separate "Custom" item to choose.
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -935,10 +949,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The chosen date range value is written into the page link.
+          <t xml:space="preserve">1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -986,13 +1002,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
+          <t xml:space="preserve">1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
 2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
 3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1039,13 +1057,15 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The location filter is the rightmost filter in the toolbar.
+          <t xml:space="preserve">1. The location filter is the rightmost filter in the toolbar.
 2. It lists the locations the signed-in user has access to.
 3. An "All locations" option is pinned to the top.
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1093,13 +1113,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. With one or more locations selected, the report includes only data from those locations.
+          <t xml:space="preserve">1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
 3. With "All locations," the report includes data from every location the user has access to.
-4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1150,18 +1171,19 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
 2. A customer or asset row whose invoices are all at one location shows that location's name.
 3. A customer or asset row whose invoices come from more than one location shows "Multiple".
 4. An invoice row always shows its own exact location — never "Multiple".
 5. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
-7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
+7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
 ---
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19) differs, his decision is the authority.</t>
+---
+This is the expected behaviour as per the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1207,12 +1229,14 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
+          <t xml:space="preserve">1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1259,11 +1283,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
+          <t xml:space="preserve">1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1309,12 +1335,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
+          <t xml:space="preserve">1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1363,12 +1391,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The Customer filter's collapsed label reads "All customers."
+          <t xml:space="preserve">1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1415,12 +1445,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. With an empty selection the collapsed label reads "None."
+          <t xml:space="preserve">1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1466,11 +1498,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. The report shows only the two selected customers.
+          <t xml:space="preserve">1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1516,12 +1550,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. Customer A (still present in the new results) stays selected and is shown.
+          <t xml:space="preserve">1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1568,13 +1604,15 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. The customer occupies exactly one summary row at the top level of the table.
+          <t xml:space="preserve">1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
 3. The count is the same size as the customer name next to it, in a slightly softer grey, and is easy to read.
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1620,9 +1658,11 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. The customer is not shown — there are no zero-value placeholder rows.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-N1).</t>
+          <t xml:space="preserve">1. The customer is not shown — there are no zero-value placeholder rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1669,7 +1709,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
+          <t xml:space="preserve">1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
 3. Each asset row shows the same financial columns as the customer row, rolled up for that asset.
 4. The Date cell is blank on asset rows.
@@ -1677,7 +1717,9 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1722,11 +1764,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
+          <t xml:space="preserve">1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1772,10 +1816,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
+          <t xml:space="preserve">1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1820,11 +1866,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
+          <t xml:space="preserve">1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1870,11 +1918,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
+          <t xml:space="preserve">1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1921,11 +1971,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
+          <t xml:space="preserve">1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1970,10 +2022,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
+          <t xml:space="preserve">1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2018,9 +2072,11 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E3).</t>
+          <t xml:space="preserve">1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2067,11 +2123,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The reversed/voided invoice never appears as an invoice row.
+          <t xml:space="preserve">1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2117,13 +2175,15 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
+          <t xml:space="preserve">1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
 3. The Date cell on the customer summary row is blank.
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2167,13 +2227,15 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. Asset (a) is identified by its VIN.
+          <t xml:space="preserve">1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
 3. Asset (c) (no VIN or Unit #) is identified by its plate instead.
-4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
+4. For asset (d) (no VIN, Unit #, or plate), the label reads "Unknown Asset" when all three are missing.
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2219,10 +2281,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
+          <t xml:space="preserve">1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2267,11 +2331,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
+          <t xml:space="preserve">1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2318,11 +2384,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. Before navigating, the active date range and Product Type are written to the page link.
+          <t xml:space="preserve">1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2367,12 +2435,14 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. The customer name on the summary row is plain text, not a link.
+          <t xml:space="preserve">1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2418,10 +2488,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. The destination page shows the application's standard "not found" state.
+          <t xml:space="preserve">1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2469,11 +2541,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. Every column is sortable except the chevron column.
+          <t xml:space="preserve">1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2519,10 +2593,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
+          <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2567,10 +2643,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
+          <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2615,10 +2693,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. Customer rows order by each customer's most recent invoice date in the current view.
+          <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2664,12 +2744,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
+          <t xml:space="preserve">1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2715,12 +2797,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
+          <t xml:space="preserve">1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2765,14 +2849,16 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
+          <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
 3. A positive value shows a leading + sign in the application's standard positive (green) color — for example, +1.5.
 4. A negative value shows a leading - sign in the standard negative (red) color — for example, -1.5.
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2817,11 +2903,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
+          <t xml:space="preserve">1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2867,11 +2955,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
+          <t xml:space="preserve">1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2917,12 +3007,14 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. Subtotal is the rightmost column in the table.
+          <t xml:space="preserve">1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2968,10 +3060,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
+          <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3017,13 +3111,16 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
+          <t xml:space="preserve">1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
+5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3069,11 +3166,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
+          <t xml:space="preserve">1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3126,8 +3225,8 @@
 3. No Location column shows on the table either, because this person only ever has one location in view.
 4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 13 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
-AUTOMATION: HOLD - nobody has run this test yet, and it needs a sign-in that has access to exactly one location.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 14 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
+AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
       </c>
@@ -3174,11 +3273,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
+          <t xml:space="preserve">1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3226,13 +3327,15 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
-2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Record the exact word the file uses for each - the mapping is confirmed in the build.
+          <t xml:space="preserve">1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
+2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The specification gives the word for each period, so check the file against it.
 3. For a range you built yourself on the calendar, record what the file name uses in place of a period name - the exact wording is confirmed in the build.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3278,7 +3381,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
+          <t xml:space="preserve">1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3286,7 +3389,9 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3331,14 +3436,16 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
+          <t xml:space="preserve">1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
 On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+AUTOMATION: READY - EXPECT FAIL (SV-8823)
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3384,11 +3491,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
+          <t xml:space="preserve">1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3435,11 +3544,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
+          <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3484,10 +3595,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
+          <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3532,12 +3645,14 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
+          <t xml:space="preserve">1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
-4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. The header also carries a "Locations:" line naming the location(s) the report was scoped to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3583,13 +3698,15 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
+          <t xml:space="preserve">1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 3. When no logo is printed, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3635,7 +3752,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
+          <t xml:space="preserve">1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
 3. The Date cell is blank on customer rows and on asset rows, matching the screen.
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
@@ -3643,7 +3760,9 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3689,13 +3808,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. For both CSV and PDF: no file is generated and no download starts.
+          <t xml:space="preserve">1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3740,10 +3861,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. The export still downloads — no error and no warning is shown.
+          <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3789,13 +3912,15 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
+          <t xml:space="preserve">1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3852,8 +3977,8 @@
 4. All six reports behave the same way.
 5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 13 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
-AUTOMATION: HOLD - nobody has run this test yet, and it needs an organization whose logo is set but will not load, which a tester cannot always produce.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
+AUTOMATION: HOLD - nobody has run this test yet; it needs one live check of a logo that fails to load
 </t>
         </is>
       </c>
@@ -3896,10 +4021,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
+          <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3945,12 +4072,14 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
+          <t xml:space="preserve">1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3996,11 +4125,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
+          <t xml:space="preserve">1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4045,10 +4176,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
+          <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4095,14 +4228,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. Date range = This Month (nothing saved and no range in the page link).
+          <t xml:space="preserve">1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
 3. Location = the single location you are currently working in (your active location) — not all locations.
 4. Customer filter = all customers selected (label "All customers").
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4148,10 +4283,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. The saved view is applied (Last Month) and the link value is ignored.
+          <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4197,10 +4334,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
+          <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4249,14 +4388,16 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
+          <t xml:space="preserve">1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4302,10 +4443,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast is shown: "An error occurred while fetching the report data."
+          <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4353,7 +4496,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
+          <t xml:space="preserve">1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
 3. The left edge of the title lines up with the leftmost column of data, and the right edge of the action cluster lines up with the rightmost column.
 4. A thin dividing line separates the toolbar from the column headers.
@@ -4363,7 +4506,9 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4410,15 +4555,15 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
+          <t xml:space="preserve">1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
 3. The totals row uses the white surface with a top border and bold text (white on purpose, matching Technician Efficiency).
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4463,10 +4608,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
+          <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R18).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4512,11 +4659,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. Every toolbar control is visible and works on touch.
+          <t xml:space="preserve">1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4562,11 +4711,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
+          <t xml:space="preserve">1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4614,11 +4765,13 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
+          <t xml:space="preserve">1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4665,12 +4818,14 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
+          <t xml:space="preserve">1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4717,11 +4872,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown does not load the full customer list into the browser up front.
+          <t xml:space="preserve">1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4768,11 +4925,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
+          <t xml:space="preserve">1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4818,11 +4977,13 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
+          <t xml:space="preserve">1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4873,13 +5034,15 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
+          <t xml:space="preserve">1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
 3. For the user WITHOUT reports access, the data request is refused with HTTP 403 and a message reading "Access denied." — no report data comes back.
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -530,7 +530,8 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
@@ -583,7 +584,8 @@
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -637,7 +639,8 @@
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -689,7 +692,8 @@
           <t xml:space="preserve">1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -745,7 +749,8 @@
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -798,7 +803,8 @@
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
 3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -849,7 +855,8 @@
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -901,7 +908,8 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -952,7 +960,8 @@
           <t xml:space="preserve">1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1008,7 +1017,8 @@
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1063,7 +1073,8 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1118,7 +1129,8 @@
 3. With "All locations," the report includes data from every location the user has access to.
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1175,14 +1187,13 @@
 2. A customer or asset row whose invoices are all at one location shows that location's name.
 3. A customer or asset row whose invoices come from more than one location shows "Multiple".
 4. An invoice row always shows its own exact location — never "Multiple".
-5. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
+5. If the signed-in person only has access to ONE location, no Location column is shown to them at all and Location is not offered in their column-selection list.
+6. When the Location column is not shown, the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row.
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
----
-This is the expected behaviour as per the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -1234,7 +1245,8 @@
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1287,7 +1299,8 @@
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1340,7 +1353,8 @@
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1396,7 +1410,8 @@
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1450,7 +1465,8 @@
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1502,7 +1518,8 @@
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1555,7 +1572,8 @@
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1610,7 +1628,8 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1660,7 +1679,8 @@
         <is>
           <t xml:space="preserve">1. The customer is not shown — there are no zero-value placeholder rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1717,7 +1737,8 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1768,7 +1789,8 @@
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1819,7 +1841,8 @@
           <t xml:space="preserve">1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1870,7 +1893,8 @@
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1922,7 +1946,8 @@
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1975,7 +2000,8 @@
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2025,7 +2051,8 @@
           <t xml:space="preserve">1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2074,7 +2101,8 @@
         <is>
           <t xml:space="preserve">1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2127,7 +2155,8 @@
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2181,7 +2210,8 @@
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2233,7 +2263,8 @@
 4. For asset (d) (no VIN, Unit #, or plate), the label reads "Unknown Asset" when all three are missing.
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2284,7 +2315,8 @@
           <t xml:space="preserve">1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2335,7 +2367,8 @@
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2388,7 +2421,8 @@
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2440,7 +2474,8 @@
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2491,7 +2526,8 @@
           <t xml:space="preserve">1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2545,7 +2581,8 @@
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2596,7 +2633,8 @@
           <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2646,7 +2684,8 @@
           <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2696,7 +2735,8 @@
           <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2749,7 +2789,8 @@
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2802,7 +2843,8 @@
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2856,7 +2898,8 @@
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2907,7 +2950,8 @@
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2959,7 +3003,8 @@
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3012,7 +3057,8 @@
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3063,7 +3109,8 @@
           <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3115,11 +3162,11 @@
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -3170,7 +3217,8 @@
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3225,8 +3273,9 @@
 3. No Location column shows on the table either, because this person only ever has one location in view.
 4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 14 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
-AUTOMATION: HOLD - waiting on an answer from the product owner
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R12), which states that a user with access to a single location is never shown the Location column and that it never appears in their column selector; the Technician Utilization report specification version 6 (S10-R4) and the Work In Progress report specification version 7 (S4-R3) say the same, and on the other three reports the written description keeps the column out of that list for everyone, so the result is the same for all six. Chris Ward asked for this in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This has not yet been checked against a build.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3277,7 +3326,8 @@
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3328,12 +3378,13 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
-2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The specification gives the word for each period, so check the file against it.
-3. For a range you built yourself on the calendar, record what the file name uses in place of a period name - the exact wording is confirmed in the build.
+2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The written description gives the word for eight of them - this_week, last_week, this_month, last_month, this_year, last_year, this_quarter, last_quarter - so check the file against those. It does not give a word for Last 12 Months, so for that one record what you see rather than judging it right or wrong.
+3. For a range you built yourself on the calendar the file name uses the word custom in place of a period name - for example sales-by-customer-summary-custom.csv.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3389,7 +3440,8 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3443,7 +3495,8 @@
 On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8823)
 </t>
         </is>
@@ -3495,7 +3548,8 @@
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3548,7 +3602,8 @@
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3598,7 +3653,8 @@
           <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3650,7 +3706,8 @@
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3704,7 +3761,8 @@
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -3760,7 +3818,8 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3814,7 +3873,8 @@
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -3864,7 +3924,8 @@
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3918,7 +3979,8 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
+This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
         </is>
@@ -3977,12 +4039,17 @@
 4. All six reports behave the same way.
 5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails.
+This has not yet been checked against a build.
 AUTOMATION: HOLD - nobody has run this test yet; it needs one live check of a logo that fails to load
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R17 and S15-R18 - the logo order and the no-logo layout; the set-but-fails-to-load step is Chris Ward's answer T3-4 option C of 2026-08-05 alone)</t>
+        </is>
+      </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
     </row>
@@ -4024,7 +4091,8 @@
           <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4077,7 +4145,8 @@
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4129,7 +4198,8 @@
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4179,7 +4249,8 @@
           <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4235,7 +4306,8 @@
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4286,7 +4358,8 @@
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4337,7 +4410,8 @@
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4395,7 +4469,8 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4446,7 +4521,8 @@
           <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4506,7 +4582,8 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4561,8 +4638,9 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
-AUTOMATION: HOLD - waiting on an answer from the product owner
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4611,7 +4689,8 @@
           <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R18).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R18).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4663,7 +4742,8 @@
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4715,7 +4795,8 @@
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4769,7 +4850,8 @@
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4823,7 +4905,8 @@
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -4876,7 +4959,8 @@
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4929,7 +5013,8 @@
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4981,7 +5066,8 @@
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -5040,7 +5126,8 @@
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -530,7 +530,7 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R1, S1-R3, S1-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
@@ -584,7 +584,7 @@
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -639,7 +639,7 @@
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -692,7 +692,7 @@
           <t xml:space="preserve">1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-N2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -749,7 +749,7 @@
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R7, S4-R8, S4-R9, S4-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -803,7 +803,7 @@
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
 3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -855,7 +855,7 @@
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 15 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -908,7 +908,7 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, his decision is the later word and is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 15 (S2-R3, S2-R4, S2-N2) says something different, his decision is the later word and is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -960,7 +960,7 @@
           <t xml:space="preserve">1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S2-R6, S2-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1017,7 +1017,7 @@
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1073,7 +1073,7 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1129,7 +1129,7 @@
 3. With "All locations," the report includes data from every location the user has access to.
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1191,7 +1191,7 @@
 6. When the Location column is not shown, the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R12, S4-R12a, S4-R13, S20-R19). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
@@ -1245,7 +1245,7 @@
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R1, S18-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1299,7 +1299,7 @@
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1353,7 +1353,7 @@
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R3, S18-N1, S17-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1410,7 +1410,7 @@
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R4, S18-R5, S18-R9, S18-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1465,7 +1465,7 @@
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1518,7 +1518,7 @@
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R5, S18-R11).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1572,7 +1572,7 @@
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R9, S18-E1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1628,7 +1628,7 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1679,7 +1679,7 @@
         <is>
           <t xml:space="preserve">1. The customer is not shown — there are no zero-value placeholder rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1737,7 +1737,7 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1789,7 +1789,7 @@
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R4, S8-R12, S8-R12a, S20-R14).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1841,7 +1841,7 @@
           <t xml:space="preserve">1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1893,7 +1893,7 @@
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R6, S8-R6a, S10-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1946,7 +1946,7 @@
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R16, S8-R17, S8-R18, S8-R19).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2000,7 +2000,7 @@
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2051,7 +2051,7 @@
           <t xml:space="preserve">1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-E1, S8-E2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2101,7 +2101,7 @@
         <is>
           <t xml:space="preserve">1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-E3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2155,7 +2155,7 @@
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R7, S7-N2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2210,7 +2210,7 @@
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2263,7 +2263,7 @@
 4. For asset (d) (no VIN, Unit #, or plate), the label reads "Unknown Asset" when all three are missing.
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2315,7 +2315,7 @@
           <t xml:space="preserve">1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R11).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2367,7 +2367,7 @@
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-R1, S9-R2, S9-R2a, S9-R2b).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2421,7 +2421,7 @@
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-R3, S9-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2474,7 +2474,7 @@
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-R5, S9-R6, S9-R7, S9-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2526,7 +2526,7 @@
           <t xml:space="preserve">1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2581,7 +2581,7 @@
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R1, S10-R2, S10-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2633,7 +2633,7 @@
           <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R4, S10-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2684,7 +2684,7 @@
           <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2735,7 +2735,7 @@
           <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R5).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2789,7 +2789,7 @@
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R6, S11-R1, S4-R12, S20-R19).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2843,7 +2843,7 @@
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R11, S7-R12, S7-R13, S7-R14).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2898,7 +2898,7 @@
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -2950,7 +2950,7 @@
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S12-N1, S12-E1, S12-E2).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3003,7 +3003,7 @@
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3057,7 +3057,7 @@
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S11-R1, S11-R2, S11-R3, S11-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3109,7 +3109,7 @@
           <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3164,7 +3164,7 @@
 4. With no saved selection, all nine toggleable columns default to visible.
 5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
@@ -3217,7 +3217,7 @@
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S13-R5, S13-R6, S13-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3273,7 +3273,7 @@
 3. No Location column shows on the table either, because this person only ever has one location in view.
 4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R12), which states that a user with access to a single location is never shown the Location column and that it never appears in their column selector; the Technician Utilization report specification version 6 (S10-R4) and the Work In Progress report specification version 7 (S4-R3) say the same, and on the other three reports the written description keeps the column out of that list for everyone, so the result is the same for all six. Chris Ward asked for this in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R12), which states that a user with access to a single location is never shown the Location column and that it never appears in their column selector; the Technician Utilization report specification version 6 (S10-R4) and the Work In Progress report specification version 9 (S4-R3) say the same, and on the other three reports the written description keeps the column out of that list for everyone, so the result is the same for all six. Chris Ward asked for this in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
 This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
@@ -3326,7 +3326,7 @@
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3383,7 +3383,7 @@
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, his decision is the later word and is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 15 (S14-R14, S14-R15, S15-R6) says something different, his decision is the later word and is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3440,7 +3440,7 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3495,7 +3495,7 @@
 On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8823)
 </t>
@@ -3548,7 +3548,7 @@
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3602,7 +3602,7 @@
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-E1, S14-N1, S15-E1, S15-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3653,7 +3653,7 @@
           <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S15-R5, S15-R6, S15-R7, S15-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3706,7 +3706,7 @@
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3761,7 +3761,7 @@
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Customer report specification version 15 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
@@ -3818,7 +3818,7 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3873,7 +3873,7 @@
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
@@ -3924,7 +3924,7 @@
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R10).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3979,7 +3979,7 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Customer report specification version 15 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
 This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
@@ -4039,7 +4039,7 @@
 4. All six reports behave the same way.
 5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 15 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails.
 This has not yet been checked against a build.
 AUTOMATION: HOLD - nobody has run this test yet; it needs one live check of a logo that fails to load
 </t>
@@ -4091,7 +4091,7 @@
           <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4145,7 +4145,7 @@
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R3, S8-R22).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4198,7 +4198,7 @@
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R5, S6-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4249,7 +4249,7 @@
           <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R7).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4306,7 +4306,7 @@
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-N1, S2-R5, S4-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4358,7 +4358,7 @@
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S2-R9).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4410,7 +4410,7 @@
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R8).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4469,7 +4469,7 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4521,7 +4521,7 @@
           <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (§7 User Feedback Summary).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4582,7 +4582,7 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4638,7 +4638,7 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4689,7 +4689,7 @@
           <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R18).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S20-R18).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4742,7 +4742,7 @@
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S21-R1, S21-R2, S21-R3).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4795,7 +4795,7 @@
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S21-R4, S21-R5, S21-R6).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4850,7 +4850,7 @@
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R14, S8-R16).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4905,7 +4905,7 @@
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R8, S10-R8b).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
@@ -4959,7 +4959,7 @@
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R2, S18-R4).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5013,7 +5013,7 @@
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R6, S18-R11).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -5066,7 +5066,7 @@
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R3, S14-R14, S15-R3, S15-R22).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
@@ -5126,7 +5126,7 @@
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R2, S1-N1).
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -691,10 +691,11 @@
         <is>
           <t xml:space="preserve">1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-N2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
+3. Note for the tester: the written description now says two different things about this, so do not fail the test on what the invoice number LOOKS like. The part this test was written from says the person clicks the link and lands on a page telling them they are not allowed in. Another part, added on 5 August 2026, says that person is not given a link at all and simply sees the invoice number as ordinary plain text. Both are in the same description today. The product owner has been asked which he wants. Write down exactly what you saw — a link leading to a not-allowed page, or plain text with nothing to click — and carry on. The one thing that would be a real failure is that person actually SEEING the invoice they are not allowed to see.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-N2), which states that a user who lacks permission to open the destination invoice is shown the standard access-denied page and can press back to return to the report. The same version's S9-R1a, added on 5 August 2026, instead states that such a user is never given a link and sees the invoice number as plain text; the two have not been reconciled and the product owner has been asked which applies.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - waiting on one answer from the product owner about whether this person is given a link at all
 </t>
         </is>
       </c>
@@ -2543,31 +2544,89 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>You cannot reach an invoice you have no permission to open</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Invoice Links &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. You need TWO sign-ins: one person who can open work orders and part sales, and one person who can see reports but CANNOT open them. Ask whoever manages permissions to set the second one up, or set it up yourself in administration and put it back as you found it afterwards.
+3. On the Sales By Customer report you have expanded a customer and then an asset, so you can see the invoice rows underneath. You need one service invoice and one parts invoice — use a different customer for the second one if you have to.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as the person who CAN open them, click a service invoice's Invoice # and note where it takes you. Come back, then do the same for a parts invoice.
+2. Sign in as the person who CANNOT open them and open the Sales By Customer report again.
+3. Expand down to the same invoice rows and look carefully at the Invoice # values.
+4. Try to click one.
+5. Write down exactly what you see and what happens, in your own words.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. For the person who CAN open them, each Invoice # is a link: a service invoice opens the work order's Finance tab, and a parts invoice opens the part sale's Part Requests tab, both in the same browser tab.
+2. For the person who CANNOT open them, the invoice's contents stay out of reach — they must not end up looking at a work order or a part sale they are not allowed to see.
+3. The report itself keeps working: the customer, asset and invoice rows are all still listed with their figures, and nothing on the page breaks.
+4. Note for the tester: what the Invoice # should LOOK like for that second person is an open question and you should not fail the test on it either way. The written description says two different things — in one place it says the number is shown as ordinary plain text with no link at all, and in another place it says the person clicks the link and lands on a page telling them they are not allowed in. The product owner has been asked which he wants. So write down exactly what you saw — plain text, or a link that leads to a not-allowed page — and carry on. Only report a failure if that person actually gets to SEE the work order or part sale.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15. Two parts of that description disagree: S9-R1a says the invoice number is rendered as a link only when the user has permission to open the target and that a user without that permission sees it as plain text, while S9-N2 says that a user who lacks permission to open the destination invoice is shown the standard access-denied page and can press back. This case therefore asserts only what both of them require — that the person cannot reach the invoice — and the product owner has been asked to settle the rest.
+This has not yet been checked against a build.
+AUTOMATION: HOLD - waiting on one answer from the product owner about what the invoice number should look like, and it needs a second sign-in that cannot open work orders or part sales
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>SV-8607 (SBC spec v15 2026-08-05 Story 9 S9-R1a and S9-N2 — the two say different things about what the invoice number looks like; this case asserts only what both of them agree on)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>All columns sortable except chevron; text alphabetical, numbers by value</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. Several customers with differing values are in the current view.
 2. A customer with multiple assets and invoices is in the view.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
@@ -2575,7 +2634,7 @@
 4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
@@ -2587,48 +2646,48 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Default sort is Customer name ascending case-insensitive</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. No saved view exists (first visit or cleared storage).
 2. Customer names with mixed upper/lower-case first letters exist in the view (seed ZZAUTOTEST names like "acme test" and "Best Test").</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the customer order.
 2. Click the Subtotal header and read the order again.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
@@ -2639,47 +2698,47 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Missing values sort to the bottom ascending and to the top descending</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer row shows an em dash (—) in Margin % (Subtotal zero or below — seed a zero-subtotal case if possible) alongside rows with real Margin % values.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Margin % ascending and note where the em-dash row lands.
 2. Sort by Margin % descending and note it again.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
@@ -2690,47 +2749,47 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sorting by Date orders customers by their most recent invoice date</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. Two customers exist whose most recent invoice dates differ clearly (seed ZZAUTOTEST invoices on different dates).</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date column header.
 2. Compare the customer order with each customer's most recent invoice date (expand to check the invoice dates).</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
@@ -2741,48 +2800,48 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Financial columns run in the specified order with Subtotal and Margin rules</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known labor, parts, and shop-supply amounts and known costs, in the current range.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Expand down to that invoice's detail row and read its values.
 3. Recalculate Subtotal and Margin by hand from the known amounts.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
@@ -2795,48 +2854,48 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Margin % is Margin over Subtotal to one decimal; em dash when Subtotal &lt;= 0</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Rows with a normal positive Subtotal exist, and (if seedable) one row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on a customer row, an asset row, and an invoice row; recalculate one by hand (Margin ÷ Subtotal × 100).
 2. Find (or seed) a row with Subtotal ≤ 0 and read its Margin % cell.
 3. Look at the Margin % coloring.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
@@ -2849,47 +2908,47 @@
 </t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim; value shows +green / -red / 0.0 on every row</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist where billed hours exceed worked hours, where worked exceeds billed, and where they are equal (seed ZZAUTOTEST work orders with clocked time).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
@@ -2904,47 +2963,47 @@
 </t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is never blank: no-labor rows and near-zero values both show 0.0</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice (no labor at all) exists in range; if possible also an invoice whose delta rounds to zero (for example +0.04).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
 2. If seeded, read the near-zero row's Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
@@ -2956,48 +3015,48 @@
 </t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Invoice subtotals sum to their asset row and asset subtotals to the customer</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. A customer with two or more assets, each with two or more invoices, is in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and every asset.
 2. Sum the invoice-level values by hand for each column and compare with each asset row.
 3. Sum the asset rows and compare with the customer row.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
@@ -3009,48 +3068,48 @@
 </t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R13)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Subtotal is the rightmost column; pinned on scroll and bold everywhere</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, on a window narrow enough to force horizontal scrolling (or with all columns visible).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Subtotal column is the last column on the right.
 2. Scroll the table sideways and watch the Subtotal column.
 3. Inspect the font weight of the Subtotal header, a customer row, an asset row, an invoice row, and the totals row.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
@@ -3063,48 +3122,48 @@
 </t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8609 (SBC spec v13 2026-07-31 Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>The totals row covers the whole filtered set; not just the current page</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page of results, with known amounts (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Read the totals row on page 1.
 2. Move to page 2 and read the totals row again.
 3. Compare the totals against the sum over ALL matching customers (not just one page).</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
@@ -3115,48 +3174,48 @@
 </t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Column selector is its own toolbar button with nine toggles all on</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no saved column selection (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector button in the toolbar's action area, next to the overflow menu.
 2. Hover it and read the tooltip.
 3. Click it and read the toggle list top to bottom.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
@@ -3170,48 +3229,48 @@
 </t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Column toggles hide header+cells; Customer, Subtotal and chevron never in list</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data and the column selector open.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Turn the "Shop Supplies" toggle off, then on again, watching the table.
 2. Read the toggle list for Customer, Subtotal, or a chevron entry.
 3. Turn all nine toggles off and read the table.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
@@ -3223,50 +3282,50 @@
 </t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>A one-location user never sees Location in the column-selection list</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to exactly ONE location. Check this in administration under that person's location access, and put their access back as you found it when you finish.
 3. This one test covers all six reports, so keep this same sign-in for the whole of it.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report and open the column-selection control (the toolbar button beside the overflow menu; hovering it reads "Column Selection.").
 2. Read the whole list of switches from top to bottom and look for an entry called Location.
 3. Do the same on Sales By Representative, then Parts Velocity, then Technician Utilization, then Work In Progress, then Inventory Value.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. On every one of the six reports the column-selection list does NOT contain an entry called Location.
 2. Nothing else about each list changes - only the Location entry is missing.
@@ -3279,48 +3338,48 @@
 </t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R4 with S4-R12; the never-offered rule itself comes from Chris Ward's answer T1-1 option C of 2026-08-05 and is in no specification)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
@@ -3332,41 +3391,41 @@
 </t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Download file names carry the version and the active date range</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Set the range to This Month, choose "Download Summary (CSV)" and note the downloaded file name.
 2. Choose "Download Expanded View (CSV)" and note that file name.
@@ -3375,7 +3434,7 @@
 5. Repeat steps 1-3 for "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
 2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The written description gives the word for eight of them - this_week, last_week, this_month, last_month, this_year, last_year, this_quarter, last_quarter - so check the file against those. It does not give a word for Last 12 Months, so for that one record what you see rather than judging it right or wrong.
@@ -3389,48 +3448,48 @@
 </t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
@@ -3446,47 +3505,47 @@
 </t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>CSV formats: Margin % plain; dates mm-dd-yyyy; currency plain; no color</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
@@ -3501,48 +3560,48 @@
 </t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF hold exactly the customers matching the active filters and sort</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
@@ -3554,49 +3613,49 @@
 </t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Each download item shows a loading state and its own export-failed toast</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a large enough data set that a download takes a visible moment.
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
 2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
 3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
@@ -3608,47 +3667,47 @@
 </t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
@@ -3659,47 +3718,47 @@
 </t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3712,48 +3771,48 @@
 </t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
@@ -3767,48 +3826,48 @@
 </t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Expanded View PDF body matches the CSV's columns and on-screen rules</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Read the body table's columns and row structure.
 2. Check a date cell, a customer row's Date cell, a Margin % dash, the Subtotal column weight, and the Inv. Hrs colors (use a color picker on the PDF if available).</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
@@ -3824,48 +3883,48 @@
 </t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose "Download (CSV)".
 2. Choose "Download (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3879,47 +3938,47 @@
 </t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>A no-match export still downloads headers and a zero totals row</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and open the file.
 2. Choose "Download (PDF)" and open the file.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
@@ -3930,48 +3989,48 @@
 </t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the four items.
 2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
 3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
@@ -3985,36 +4044,36 @@
 </t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>A logo that is set but will not load falls back to the ShopView logo</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser and you can change the organization's uploaded logo in administration.
 2. You will need the organization in a state where a logo IS set but the picture will not load - for example an uploaded logo whose file has since been removed or renamed. Ask a developer to help you produce that state if you cannot.
@@ -4022,7 +4081,7 @@
 4. This one test covers the printable download on all six reports, so do the setup once and check all six.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. With a logo uploaded and loading normally, download the printable file from each of the six reports and look at the top right of the header.
 2. Put the organization into the state where a logo is set but the picture will not load.
@@ -4031,7 +4090,7 @@
 5. Put the organization's original logo back.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. With a logo that loads, that logo is shown at the top right, sized to fit without being stretched.
 2. With a logo that is set but will not load, the built-in ShopView logo is shown in its place - not a blank space, not a broken-picture icon, and no error message.
@@ -4045,48 +4104,48 @@
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R17 and S15-R18 - the logo order and the no-logo layout; the set-but-fails-to-load step is Chris Ward's answer T3-4 option C of 2026-08-05 alone)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
@@ -4097,48 +4156,48 @@
 </t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -4151,48 +4210,48 @@
 </t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
@@ -4204,47 +4263,47 @@
 </t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
@@ -4255,49 +4314,49 @@
 </t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -4312,48 +4371,48 @@
 </t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
@@ -4364,48 +4423,48 @@
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
@@ -4416,42 +4475,42 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.
 2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -4460,7 +4519,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -4475,48 +4534,48 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
@@ -4527,41 +4586,41 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
 2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
@@ -4570,7 +4629,7 @@
 5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4588,49 +4647,49 @@
 </t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4644,47 +4703,47 @@
 </t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
@@ -4695,48 +4754,48 @@
 </t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
@@ -4748,48 +4807,48 @@
 </t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
@@ -4801,42 +4860,42 @@
 </t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4844,7 +4903,7 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
@@ -4856,49 +4915,49 @@
 </t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -4911,49 +4970,49 @@
 </t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
@@ -4965,49 +5024,49 @@
 </t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
@@ -5019,48 +5078,48 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
@@ -5072,43 +5131,43 @@
 </t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>The back end serves SBC report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
 2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the user WHO HAS ordinary reports access and open Sales By Customer.
 2. In the network panel, find the request the page makes for the report's data and read its response code.
@@ -5118,7 +5177,7 @@
 6. Ask for the same export by its address and read that response code too.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
@@ -5132,13 +5191,13 @@
 </t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8600 (SBC spec v13 2026-07-31 S1-R2; S1-N1 — the back-end half of the ordinary-reports-access gate; the SBC twin of the Parts Velocity back-end case C30391; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -524,16 +524,16 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
+          <t>1. "Sales By Customer" is listed in the Reports left-side navigation and can be opened from there.
+1a. Note for the tester: the written description says only that it appears in the Reports navigation - it does not say WHICH group it belongs in. Write down the group heading you find it under and carry on; do not fail the test on the group name. The product owner has been asked to settle which group each of the six new reports belongs in.
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R1, S1-R3, S1-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - waiting on an answer from the product owner
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S1-R1, S1-R3, S1-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -584,7 +584,7 @@
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R2).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S1-R2), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -639,7 +639,7 @@
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-N1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S1-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -693,7 +693,7 @@
 2. Pressing back returns you to the Sales By Customer report.
 3. Note for the tester: the written description now says two different things about this, so do not fail the test on what the invoice number LOOKS like. The part this test was written from says the person clicks the link and lands on a page telling them they are not allowed in. Another part, added on 5 August 2026, says that person is not given a link at all and simply sees the invoice number as ordinary plain text. Both are in the same description today. The product owner has been asked which he wants. Write down exactly what you saw — a link leading to a not-allowed page, or plain text with nothing to click — and carry on. The one thing that would be a real failure is that person actually SEEING the invoice they are not allowed to see.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-N2), which states that a user who lacks permission to open the destination invoice is shown the standard access-denied page and can press back to return to the report. The same version's S9-R1a, added on 5 August 2026, instead states that such a user is never given a link and sees the invoice number as plain text; the two have not been reconciled and the product owner has been asked which applies.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S9-N2), read on 11 August 2026, which states that a user who lacks permission to open the destination invoice is shown the standard access-denied page and can press back to return to the report. The same version's S9-R1a, added on 5 August 2026, instead states that such a user is never given a link and sees the invoice number as plain text; the two have not been reconciled and the product owner has been asked which applies.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on one answer from the product owner about whether this person is given a link at all
 </t>
@@ -750,7 +750,7 @@
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R7, S4-R8, S4-R9, S4-N1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S4-R7, S4-R8, S4-R9, S4-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -804,7 +804,7 @@
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
 3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R2).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S1-R2), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -821,7 +821,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Date range picker offers eleven options in the specified order</t>
+          <t>Date range picker offers nine periods in the specified order, no All Time</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -852,14 +852,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A date range picker is visible in the report toolbar.
+          <t>1. A date range picker is visible in the report toolbar.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 15 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Sales By Customer report specification version 17 (S2-R1, S2-R2), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -905,14 +904,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen. There is no separate "Custom" item to choose.
+          <t>1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen. There is no separate "Custom" item to choose.
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 15 (S2-R3, S2-R4, S2-N2) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Sales By Customer report specification version 17 (S2-R3, S2-R4, S2-N2), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - the calendar cannot be driven past the 366-day span from this harness; the back end refuses a wider range but the on-screen prevention was not seen</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -958,13 +956,16 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The chosen date range value is written into the page link.
+          <t>1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S2-R6, S2-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the address bar never changes - it stays at the plain report address after the range is applied, so there is nothing to copy and share. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8955
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S2-R6, S2-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8955)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1012,16 +1013,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
+          <t>1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
 2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
 3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S4-R1, S4-R2, S4-R3), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1125,15 +1125,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With one or more locations selected, the report includes only data from those locations.
+          <t>1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
 3. With "All locations," the report includes data from every location the user has access to.
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S4-R5, S4-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,7 +1146,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>The Location column shows only with more than one location; Multiple on totals</t>
+          <t>Location column: shown to any multi-location user, Multiple on aggregating rows</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1173,7 +1172,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Select two or more locations in the Location filter and read the column headers.
+          <t>1. With every location selected in the Location filter, read the column headers.
 2. Read the Location cell on a customer row whose invoices are all at one location.
 3. Read the Location cell on a customer row and an asset row whose invoices span two locations.
 4. Expand to an invoice row and read its Location cell.
@@ -1184,18 +1183,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
+          <t>1. Because the signed-in person has access to more than one location, a Location column is shown by default, positioned immediately after the Date column.
 2. A customer or asset row whose invoices are all at one location shows that location's name.
 3. A customer or asset row whose invoices come from more than one location shows "Multiple".
-4. An invoice row always shows its own exact location — never "Multiple".
-5. If the signed-in person only has access to ONE location, no Location column is shown to them at all and Location is not offered in their column-selection list.
-6. When the Location column is not shown, the surrounding columns close up with no gap.
-7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R12, S4-R12a, S4-R13, S20-R19). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+4. An invoice row always shows its own exact location - never "Multiple".
+5. Location is offered in the column-selection control and can be switched on and off by hand.
+6. Narrowing to a single location does NOT remove the column: what decides whether it is shown is how many locations the person can reach, not how many are currently selected.
+7. If the signed-in person only has access to ONE location, no Location column is shown to them at all and Location is not offered in their column-selection list.
+8. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read.
+What you should see today: the Location column behaves by how many locations are SELECTED, not by what the signed-in person can reach. With every location selected the column appears; narrow the Location filter to a single location and the column disappears, even though the person still has access to five locations. The column is also not listed in the column-selection control at all, so it cannot be switched on or off by hand. This was seen on all three handed-off reports.
+- If you see exactly that, mark this test FAILED and do not raise anything new - it is already written up for the QA lead.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S4-R12, S4-R12a, S4-R13, S20-R19), read on 11 August 2026. Chris Ward confirmed this same rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree, so the earlier note saying the description contradicted itself no longer applies.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1241,15 +1244,18 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
+          <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R1, S18-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Customer filter has no magnifier icon on it - the only icon is the drop-down arrow. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8962
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R1, S18-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8962)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1296,14 +1302,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
+          <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1352,11 +1357,15 @@
           <t xml:space="preserve">1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
 3. The control is pinned to the top of the dropdown in both states.
-4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R3, S18-N1, S17-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
+4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters." The collapsed label reads "None", and the totals row shows zeros.
+What you should see today: everything in item 4 happens except the totals row - the empty-state message appears and the collapsed label reads "None", but there is no totals row on the report at all, of zeros or otherwise. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8991.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above - for example a totals row appears but the figures are not zeros, or the empty-state message or the "None" label is wrong, or the pinned control in items 1 to 3 does not behave as described - that is a NEW problem, so please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R3, S18-N1, S17-E1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8991)
 </t>
         </is>
       </c>
@@ -1406,15 +1415,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Customer filter's collapsed label reads "All customers."
+          <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R4, S18-R5, S18-R9, S18-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R4, S18-R5, S18-R9, S18-E1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1461,15 +1469,18 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With an empty selection the collapsed label reads "None."
+          <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: with two customers picked the closed control reads "2 customers" instead of "2 selected", and while you type the closed control keeps showing the summary label instead of what you typed. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8962
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8962)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1515,14 +1526,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report shows only the two selected customers.
+          <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R5, S18-R11).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R5, S18-R11), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1568,15 +1578,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Customer A (still present in the new results) stays selected and is shown.
+          <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R9, S18-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R9, S18-E1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1623,16 +1632,15 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The customer occupies exactly one summary row at the top level of the table.
+          <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
 3. The count is the same size as the customer name next to it, in a slightly softer grey, and is easy to read.
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1678,12 +1686,11 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The customer is not shown — there are no zero-value placeholder rows.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The customer is not shown — there are no zero-value placeholder rows.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1730,7 +1737,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
+          <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
 3. Each asset row shows the same financial columns as the customer row, rolled up for that asset.
 4. The Date cell is blank on asset rows.
@@ -1738,10 +1745,9 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1786,14 +1792,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
+          <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R4, S8-R12, S8-R12a, S20-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R4, S8-R12, S8-R12a, S20-R14), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1839,13 +1844,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
+          <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1890,14 +1894,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
+          <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R6, S8-R6a, S10-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R6, S8-R6a, S10-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1943,14 +1946,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
+          <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R16, S8-R17, S8-R18, S8-R19).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R16, S8-R17, S8-R18, S8-R19), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1997,14 +1999,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
+          <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2049,13 +2050,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The single-invoice asset expands and shows exactly one invoice detail row.
+          <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-E1, S8-E2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-E1, S8-E2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2100,12 +2100,11 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-E3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-E3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - this organisation has no service invoice without a vehicle, so nothing lands in the Parts Sales bucket from the service side</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2152,14 +2151,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The reversed/voided invoice never appears as an invoice row.
+          <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R7, S7-N2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-R7, S7-N2), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - this organisation has no reversed or voided invoice inside the report date range</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2205,16 +2203,15 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
+          <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
 3. The Date cell on the customer summary row is blank.
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2258,16 +2255,15 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Asset (a) is identified by its VIN.
+          <t>1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
 3. Asset (c) (no VIN or Unit #) is identified by its plate instead.
 4. For asset (d) (no VIN, Unit #, or plate), the label reads "Unknown Asset" when all three are missing.
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R7, S8-R8, S8-R9, S8-R10), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2313,13 +2309,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
+          <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R11).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R11), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - no customer in this organisation has two assets that produce the same label, so the numbered suffix cannot appear</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2364,14 +2359,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
+          <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-R1, S9-R2, S9-R2a, S9-R2b).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S9-R1, S9-R2, S9-R2a, S9-R2b), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2418,14 +2412,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Before navigating, the active date range and Product Type are written to the page link.
+          <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-R3, S9-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S9-R3, S9-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2470,15 +2463,14 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The customer name on the summary row is plain text, not a link.
+          <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-R5, S9-R6, S9-R7, S9-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S9-R5, S9-R6, S9-R7, S9-R8), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2524,13 +2516,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The destination page shows the application's standard "not found" state.
+          <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S9-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S9-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - deleting a real invoice while the report is open is not something to do on a shared environment</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2580,15 +2571,14 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For the person who CAN open them, each Invoice # is a link: a service invoice opens the work order's Finance tab, and a parts invoice opens the part sale's Part Requests tab, both in the same browser tab.
+          <t>1. For the person who CAN open them, each Invoice # is a link: a service invoice opens the work order's Finance tab, and a parts invoice opens the part sale's Part Requests tab, both in the same browser tab.
 2. For the person who CANNOT open them, the invoice's contents stay out of reach — they must not end up looking at a work order or a part sale they are not allowed to see.
 3. The report itself keeps working: the customer, asset and invoice rows are all still listed with their figures, and nothing on the page breaks.
 4. Note for the tester: what the Invoice # should LOOK like for that second person is an open question and you should not fail the test on it either way. The written description says two different things — in one place it says the number is shown as ordinary plain text with no link at all, and in another place it says the person clicks the link and lands on a page telling them they are not allowed in. The product owner has been asked which he wants. So write down exactly what you saw — plain text, or a link that leads to a not-allowed page — and carry on. Only report a failure if that person actually gets to SEE the work order or part sale.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15. Two parts of that description disagree: S9-R1a says the invoice number is rendered as a link only when the user has permission to open the target and that a user without that permission sees it as plain text, while S9-N2 says that a user who lacks permission to open the destination invoice is shown the standard access-denied page and can press back. This case therefore asserts only what both of them require — that the person cannot reach the invoice — and the product owner has been asked to settle the rest.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17, read on 11 August 2026. Two parts of that description disagree: S9-R1a says the invoice number is rendered as a link only when the user has permission to open the target and that a user without that permission sees it as plain text, while S9-N2 says that a user who lacks permission to open the destination invoice is shown the standard access-denied page and can press back. This case therefore asserts only what both of them require — that the person cannot reach the invoice — and the product owner has been asked to settle the rest.
 This has not yet been checked against a build.
-AUTOMATION: HOLD - waiting on one answer from the product owner about what the invoice number should look like, and it needs a second sign-in that cannot open work orders or part sales
-</t>
+AUTOMATION: HOLD - waiting on one answer from the product owner about what the invoice number should look like, and it needs a second sign-in that cannot open work orders or part sales</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2636,14 +2626,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every column is sortable except the chevron column.
+          <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R1, S10-R2, S10-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: every column heading sorts except Location, which has no sort arrow and does not respond when you click it. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8963
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S10-R1, S10-R2, S10-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2689,13 +2682,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
+          <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R4, S10-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S10-R4, S10-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2740,13 +2732,16 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
+          <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: sorting Margin % smallest-first puts the rows with a dash at the TOP, and largest-first puts them at the BOTTOM - the opposite way round. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8963
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S10-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2791,13 +2786,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
+          <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S10-R5), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2843,15 +2837,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
+          <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R6, S11-R1, S4-R12, S20-R19).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-R6, S11-R1, S4-R12, S20-R19), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2897,15 +2890,14 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
+          <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S7-R11, S7-R12, S7-R13, S7-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-R11, S7-R12, S7-R13, S7-R14), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2950,17 +2942,16 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (including the period after "Inv").
+          <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
 3. A positive value shows a leading + sign in the application's standard positive (green) color — for example, +1.5.
 4. A negative value shows a leading - sign in the standard negative (red) color — for example, -1.5.
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3005,14 +2996,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
+          <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S12-N1, S12-E1, S12-E2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S12-N1, S12-E1, S12-E2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3058,14 +3048,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. An asset's invoice subtotals sum exactly to that asset's row total.
+          <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R13), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3111,15 +3100,14 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Subtotal is the rightmost column in the table.
+          <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S11-R1, S11-R2, S11-R3, S11-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S11-R1, S11-R2, S11-R3, S11-N1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3165,13 +3153,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
+          <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3217,16 +3204,15 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
+          <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
 5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3272,14 +3258,13 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
+          <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S13-R5, S13-R6, S13-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S13-R5, S13-R6, S13-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3327,15 +3312,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On every one of the six reports the column-selection list does NOT contain an entry called Location.
+          <t>1. On every one of the six reports the column-selection list does NOT contain an entry called Location.
 2. Nothing else about each list changes - only the Location entry is missing.
 3. No Location column shows on the table either, because this person only ever has one location in view.
 4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S4-R12), which states that a user with access to a single location is never shown the Location column and that it never appears in their column selector; the Technician Utilization report specification version 6 (S10-R4) and the Work In Progress report specification version 9 (S4-R3) say the same, and on the other three reports the written description keeps the column out of that list for everyone, so the result is the same for all six. Chris Ward asked for this in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S4-R12), read on 11 August 2026, which states that a user with access to a single location is never shown the Location column and that it never appears in their column selector; the Technician Utilization report specification version 7 (S10-R4), read on 11 August 2026, and the Work In Progress report specification version 11 (S4-R3), read on 11 August 2026, say the same, and on the other three reports the written description keeps the column out of that list for everyone, so the result is the same for all six. Chris Ward asked for this in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
 This has not yet been checked against a build.
-AUTOMATION: READY
-</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3381,14 +3365,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
+          <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3436,16 +3419,19 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
+          <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
 2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The written description gives the word for eight of them - this_week, last_week, this_month, last_month, this_year, last_year, this_quarter, last_quarter - so check the file against those. It does not give a word for Last 12 Months, so for that one record what you see rather than judging it right or wrong.
 3. For a range you built yourself on the calendar the file name uses the word custom in place of a period name - for example sales-by-customer-summary-custom.csv.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
----
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 15 (S14-R14, S14-R15, S15-R6) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the two spreadsheets come out as sales-by-customer-summary.csv and sales-by-customer-expanded.csv, with no period in either name. The files themselves do carry a "Date Range:" line, so the information is there, just not in the name. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8956
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Sales By Customer report specification version 17 (S14-R14, S14-R15, S15-R6), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8956)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3491,7 +3477,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
+          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3499,10 +3485,9 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3547,17 +3532,19 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
+          <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
 On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8823)
-</t>
+What you should see today: in the spreadsheet the money arrives as text with a dollar sign and thousands separators, such as $11,176.88, and the columns come out in the file's own fixed order - Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Total Cost, Total Sell, Margin, Margin % - which is not the order on screen, does not put Total Cost last, and leaves out the Location column even when it is showing on screen. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3603,70 +3590,69 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
+          <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Each download item shows a loading state and its own export-failed toast</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the report with a large enough data set that a download takes a visible moment.
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
+2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
+3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
+2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
+3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-E1, S14-N1, S15-E1, S15-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Each download item shows a loading state and its own export-failed toast</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Exports</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the report with a large enough data set that a download takes a visible moment.
-2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
-2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
-3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
-2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
-3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-E1, S14-N1, S15-E1, S15-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
@@ -3709,13 +3695,16 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
+          <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S15-R5, S15-R6, S15-R7, S15-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Expanded View PDF comes out on A3 paper (1190 by 842 points) instead of A4. The Summary PDF from the same menu is correctly A4. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8964
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S15-R5, S15-R6, S15-R7, S15-R8), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8964)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3760,15 +3749,18 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
+          <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the heading date range shows an end date one day LATER than the range you asked for - ask for 1 to 6 August and the PDF heading reads "Aug 1, 2026 - Aug 7, 2026". Every other line of the heading is correct, and the spreadsheet for the same view prints the correct end date. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8937
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8937)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3814,16 +3806,15 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
+          <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 3. When no logo is printed, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Customer report specification version 15 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Sales By Customer report specification version 17 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18), read on 11 August 2026, differs, his decision is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3837,7 +3828,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Expanded View PDF body matches the CSV's columns and on-screen rules</t>
+          <t>Expanded CSV body: column set and order, the Customer → Asset → Invoice tree, blank dates and em-dash Margin %</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3857,30 +3848,28 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.
-2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
+          <t>1. You are on Sales By Customer with a view containing positive and negative Inv. Hrs values and, if seedable, a row whose Subtotal is zero or below.
+2. Nothing to install — this test reads a downloaded CSV as text.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. Read the body table's columns and row structure.
-2. Check a date cell, a customer row's Date cell, a Margin % dash, the Subtotal column weight, and the Inv. Hrs colors (use a color picker on the PDF if available).</t>
+          <t>1. Download "Expanded View (CSV)" from the ⋯ menu.
+2. Read the header row and compare it against the column list below.
+3. Walk the data rows for one customer: the customer row, its asset rows, and the invoice rows beneath them.
+4. Find a row whose Subtotal is zero or below and read its Margin % cell.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
-2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
-3. The Date cell is blank on customer rows and on asset rows, matching the screen.
-4. Margin % shows an em dash when the row's Subtotal is zero or below.
-5. The Subtotal column is bold - header, every row, and the totals row.
-6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
-7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The Expanded CSV's header row carries the Expanded column set, in this exact order and with these labels — thirteen columns with a single location in scope, plus the Location column immediately after Date when more than one location is in scope.
+2. The body contains the full Customer → Asset → Invoice breakdown: one customer row, its asset rows beneath it, and each asset's invoice rows beneath that.
+3. The Date cell is empty on customer rows and on asset rows, and carries the invoice date only on invoice rows — matching the screen.
+4. Margin % is an em dash on any row whose Subtotal is zero or below.
+5. The file carries the "Locations:" metadata line above the header row.
+---
+Scope note: this case covers the CSV only. The Expanded PDF renders the same data, but its page geometry, fonts, colours and bold weights are not observable by the automation suite (no PDF parser) — those assertions live in the PDF-visual cases, which are Deferred.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification (S14-R5 Expanded contents; S4-R13 Locations line), read on 11 August 2026.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3919,23 +3908,25 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1. With the over-cap filter set, choose "Download (CSV)".
-2. Choose "Download (PDF)".
+          <t>1. With the over-cap filter set, choose a CSV download - "Download Summary (CSV)" or "Download Expanded View (CSV)".
+2. Choose a PDF download - "Download Summary (PDF)" or "Download Expanded View (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For both CSV and PDF: no file is generated and no download starts.
+          <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
 4. Below the cap the export succeeds normally.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R16, S15-R25, S14-R14, S15-R22), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3974,18 +3965,22 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1. Choose "Download (CSV)" and open the file.
-2. Choose "Download (PDF)" and open the file.</t>
+          <t>1. Choose a CSV download - "Download Summary (CSV)" or "Download Expanded View (CSV)" - and open the file.
+2. Choose a PDF download - "Download Summary (PDF)" or "Download Expanded View (PDF)" - and open the file.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
-2. The file contains the column headers and a totals row of zeros, with no data rows.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
+2. The file contains the column headers, a totals row of zeros, and no data rows.
+What you should see today: the file downloads with the column headings and nothing after them - there is no totals row at all, of zeros or otherwise. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8991.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above - for example the download errors, or a totals row appears but the figures are not zeros - that is a NEW problem, so please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R10), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8991)
 </t>
         </is>
       </c>
@@ -4032,16 +4027,15 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
+          <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Customer report specification version 15 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
-This has not yet been checked against a build.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. the Sales By Customer report specification version 17 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4092,16 +4086,15 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With a logo that loads, that logo is shown at the top right, sized to fit without being stretched.
+          <t>1. With a logo that loads, that logo is shown at the top right, sized to fit without being stretched.
 2. With a logo that is set but will not load, the built-in ShopView logo is shown in its place - not a blank space, not a broken-picture icon, and no error message.
 3. With no logo uploaded at all, NO logo is shown and the header text spreads out to fill the space.
 4. All six reports behave the same way.
 5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 15 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails.
-This has not yet been checked against a build.
-AUTOMATION: HOLD - nobody has run this test yet; it needs one live check of a logo that fails to load
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 17 (S15-R17), read on 11 August 2026, which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - this organisation has a logo that loads correctly, so the set-but-will-not-load fallback cannot be produced</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4147,13 +4140,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
+          <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4199,15 +4191,14 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The type-ahead search text is gone (only the resulting customer selection is saved).
+          <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R3, S8-R22).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S6-R3, S8-R22), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4253,14 +4244,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
+          <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R5, S6-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: a remembered location or customer that is no longer usable is kept rather than dropped (the filter reads "1 selected" for something with no name), and a remembered date range that is no longer valid leaves the date control reading "Select Date Range" with an empty report instead of going back to This Month. Product Type and the chosen columns do fall back correctly. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8966
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S6-R5, S6-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8966)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4305,13 +4299,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
+          <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S6-R7), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4358,71 +4351,70 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Date range = This Month (nothing saved and no range in the page link).
+          <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
 3. Location = the single location you are currently working in (your active location) — not all locations.
 4. Customer filter = all customers selected (label "All customers").
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S6-N1, S2-R5, S4-R4).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S6-N1, S2-R5, S4-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>When a saved view and a page-link range clash the saved view wins</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Saved View &amp; Persistence</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. You have a saved view with a known date range (for example Last Month).
+2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the report using the link with the different range.
+2. Read the date range picker.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
+2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S2-R9), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>When a saved view and a page-link range clash the saved view wins</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SBC — Saved View &amp; Persistence</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>1. You have a saved view with a known date range (for example Last Month).
-2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the report using the link with the different range.
-2. Read the date range picker.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
-2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S2-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
@@ -4469,7 +4461,7 @@
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R8).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R8), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4521,17 +4513,16 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
+          <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4577,13 +4568,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
+          <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (§7 User Feedback Summary).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (§7 User Feedback Summary), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: HOLD - a failing data fetch cannot be forced from the application</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4631,7 +4621,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
+          <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
 3. The left edge of the title lines up with the leftmost column of data, and the right edge of the action cluster lines up with the rightmost column.
 4. A thin dividing line separates the toolbar from the column headers.
@@ -4640,11 +4630,14 @@
 7. When there are too few rows to fill the screen, the blue-grey page background shows through below the table — there is no white strip left over.
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the outer cells of the table have about 14 pixels of side padding instead of 2rem (32 pixels). This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8965
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4691,16 +4684,19 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Column-header cells and customer summary rows use the white surface (#ffffff).
+          <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
 3. The totals row uses the white surface with a top border and bold text (white on purpose, matching Technician Efficiency).
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the column headings, the customer rows and the totals row are all the pale blue-grey instead of white; the asset and invoice rows are a third, darker grey; and invoice rows are not indented any deeper than customer rows. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8965
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4745,13 +4741,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
+          <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S20-R18).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S20-R18), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4797,14 +4792,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every toolbar control is visible and works on touch.
+          <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S21-R1, S21-R2, S21-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S21-R1, S21-R2, S21-R3), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4850,14 +4844,13 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
+          <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S21-R4, S21-R5, S21-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S21-R4, S21-R5, S21-R6), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4905,14 +4898,13 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
+          <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S8-R14, S8-R16).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R14, S8-R16), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4964,9 +4956,9 @@
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S10-R8, S10-R8b).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - this part of the report is not built yet
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S10-R8, S10-R8b), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -5014,14 +5006,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The dropdown does not load the full customer list into the browser up front.
+          <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R2, S18-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R2, S18-R4), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5068,14 +5059,13 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
+          <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S18-R6, S18-R11).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S18-R6, S18-R11), read on 11 August 2026.
+Last checked against build v3.5-7168d14 on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5115,20 +5105,22 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1. Trigger "Download (CSV)" and "Download (PDF)" and observe where the file content comes from.
+          <t>1. Trigger a CSV download ("Download Summary (CSV)" or "Download Expanded View (CSV)") and a PDF download ("Download Summary (PDF)" or "Download Expanded View (PDF)"), and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
+          <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S14-R3, S14-R14, S15-R3, S15-R22).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R3, S14-R14, S15-R3, S15-R22), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5177,7 @@
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 15 (S1-R2, S1-N1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S1-R2, S1-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Product Type: three options with Parts &amp; Service default; S/P prefix filtering</t>
+          <t>Product Type multi-select: both toggles on by default; S/P prefix filtering</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1005,19 +1005,21 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Find the "Product Type" dropdown in the report toolbar; read its value before touching it, then open it and read the options in order.
-2. Set Product Type to "Service only," expand a customer down to invoice rows, and read the invoice numbers.
-3. Set Product Type to "Parts only" and read the invoice numbers again.
-4. Set Product Type back to "Parts &amp; Service."</t>
+          <t>1. Find the "Product Type" filter in the report toolbar; read its current selection before touching it, then open it and read the action rows and the toggle options in order.
+2. Select only "Services" (leave "Parts" unselected), expand a customer down to invoice rows, and read the invoice numbers.
+3. Select only "Parts" and read the invoice numbers again.
+4. Use "All products" to select both toggles again.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
-2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
-3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
-4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
-5. The whole invoice is classified by its number prefix — there is no per-line-item split.
+          <t>1. The "Product Type" filter in the toolbar is a multi-select, behaving like the Customer and Location filters. Opened, it pins two action rows at the top — "All products" and "Clear all" — above two toggle options: "Parts" and "Services."
+2. On first load both toggles are selected, so all products are included and no product-type filter is applied.
+3. With only "Services" selected, every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
+4. With only "Parts" selected, every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
+5. With both toggles selected again, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
+6. The whole invoice is classified by its number prefix — there is no per-line-item split.
+Note for the tester: the toggles read "Parts" and "Services", but the filter summary line printed in the exports uses the older wordings — "Parts &amp; Service" with both toggles on, "Service only" with only Services on, and "Parts only" with only Parts on. That difference is expected and is not a fault.
 ---
 This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6), read on 11 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
@@ -1035,30 +1037,87 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Clear all leaves neither Product Type toggle on and shows the empty state</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Product Type Filter</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Sales By Customer report with a date range that normally returns rows, so you can tell an empty result from a genuinely empty range.
+2. The Product Type filter is at its default with both toggles selected.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the "Product Type" filter and read the two action rows at the top.
+2. Choose "Clear all" and read the table body.
+3. Read the toolbar and check the filter still opens.
+4. Switch the "Parts" toggle back on and read the table body again.
+5. Choose "All products" and read the table body once more.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1. The filter pins two action rows at the top — "All products" and "Clear all" — above the "Parts" and "Services" toggles.
+2. After "Clear all" neither toggle is selected and the table body shows the empty-state message "No sales data found for the selected filters."
+3. The empty state is shown in the table body only — the toolbar stays usable and the filter still opens.
+4. Switching "Parts" back on brings rows back straight away, limited to invoices whose number starts with P.
+5. "All products" selects both toggles again and the full set of rows returns.
+Note for the tester: an empty report here is the correct result of clearing both toggles, not a fault — it stays empty until you switch a toggle back on.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S3-R6a, S3-R2, S17-R1), read on 11 August 2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SV-8602 (SBC spec v17 2026-08-10 Story 3 S3-R6a — new in v17: with neither toggle selected after "Clear all" the report shows the Story 17 empty state until a toggle is selected; S3-R2 pins the two action rows; S17-R1 gives the message)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Location filter: rightmost, lists accessible locations, All locations on top</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report as a user with access to two or more locations.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Look at the report toolbar's filters from left to right.
 2. Open the location filter and read its options.
@@ -1066,7 +1125,7 @@
 4. Then sign in as a user with access to only ONE location, open the report and look for the Location filter again.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The location filter is the rightmost filter in the toolbar.
 2. It lists the locations the signed-in user has access to.
@@ -1080,42 +1139,42 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>SV-8603 (SBC spec Story 4 S4-R1; S4-R2; S4-R3 + single-location filter HIDDEN per Chris Ward answer 2026-07-31 Q1=A; applied suite-wide)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Selecting locations scopes the data; All locations covers every accessible one</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. At least two accessible locations each have invoices in the chosen date range (seed ZZAUTOTEST data if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A in the location filter and note the customers/totals.
 2. Select locations A and B together and note the change.
@@ -1123,7 +1182,7 @@
 4. With "All locations" active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
@@ -1135,42 +1194,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>SV-8603 (SBC spec Story 4 S4-R5; S4-R6 — per-row location identifier in All-locations view ADDED per kickoff video P10; [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward msg 2026-07-29 [newest-wins]</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Location column: shown to any multi-location user, Multiple on aggregating rows</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>SBC — Location Filter</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report as a user with access to two or more locations.
 2. At least one customer has invoices at two different locations, and at least one asset has invoices at two different locations.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. With every location selected in the Location filter, read the column headers.
 2. Read the Location cell on a customer row whose invoices are all at one location.
@@ -1181,7 +1240,7 @@
 7. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Because the signed-in person has access to more than one location, a Location column is shown by default, positioned immediately after the Date column.
 2. A customer or asset row whose invoices are all at one location shows that location's name.
@@ -1201,48 +1260,48 @@
 AUTOMATION: HOLD - the build does not follow the ratified Location rule; the defect is written up in DEFECTS-FOR-PERMISSION.md and needs the QA lead's permission before a ticket exists to point at</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SV-8603; SV-8612; SV-8613 (SBC spec v13 2026-07-31 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Customer filter sits between Product Type and Location, carries a search icon</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer in the current results.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar filters from left to right.
 2. Open the Customer filter without typing anything.
 3. Read what the dropdown shows before any query is typed.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
@@ -1258,49 +1317,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8962)</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R1; S18-R2)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Typing in the Customer filter lists matching customers by contains match</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. At least two customers with distinct names have invoices in the current date range/Product Type/location (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and type a fragment from the MIDDLE of a customer's name, in different letter case (for example type "corp" for "Acme Corp").
 2. Read the list of customers shown.
 3. Click one listed customer to select it and look at its row in the dropdown.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
@@ -1311,48 +1370,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Pinned control toggles All customers and Clear all; clearing shows empty state</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with several customers in the current results.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter while it is in the all-customers state and read the pinned control at the top of the dropdown.
 2. Activate it ("Clear all") and read the table body, the totals row, and the filter's collapsed label.
 3. Read the pinned control again and activate it once more.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
@@ -1369,43 +1428,43 @@
 </t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R3; S18-N1; S17-E1)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>First load starts in the all-customers state and the report shows every customer</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. Your browser has no saved view for this report.
 2. Several customers have invoices in the default date range.
 3. A customer exists that has invoices ONLY in a wider date range than the current one (seed a ZZAUTOTEST invoice dated last month if needed).</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read the Customer filter's collapsed label.
@@ -1413,7 +1472,7 @@
 4. Widen the date range so the customer with no matching invoices now has one; re-check the label and the rows.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
@@ -1425,41 +1484,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Collapsed label reads None, the customer's name, or N selected</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter and use "Clear all" to empty the selection; read the collapsed label.
 2. Select exactly one customer; read the collapsed label.
@@ -1467,7 +1526,7 @@
 4. Start typing a search query in the filter field and watch the field text, then clear the query or click away.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
@@ -1483,48 +1542,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8962)</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R5)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Changing the customer selection narrows the table and refreshes the totals</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least three customers in the current results.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Note the customers and the totals row values.
 2. Open the Customer filter, clear all, and select exactly two customers.
 3. Read the table rows and the totals row.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
@@ -1535,48 +1594,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R5; S18-R11)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>A subset customer selection reconciles on a filter change; kept if present</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>SBC — Customer Filter</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with three customers A, B, C where: A has invoices in both this month and last month; B has invoices only in this month; C has invoices only in last month (seed ZZAUTOTEST data as needed).
 2. Date range is This Month; you have selected exactly customers A and B in the Customer filter.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range to Last Month.
 2. Read the table rows and the Customer filter selection.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
@@ -1588,49 +1647,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R9; S18-E1)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Each customer gets one summary row with its invoice count in parentheses</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. A customer has a known number of matching invoices in the current date range (seed ZZAUTOTEST data so the count is predictable).</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Find that customer's row at the top level of the table.
 2. Read the text at the start of the row.
 3. Narrow the date range so fewer of that customer's invoices match, and re-read the count.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
@@ -1643,48 +1702,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>A customer with no matching invoices in the current view is not shown</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose invoices all fall OUTSIDE the current date range (seed if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains none of that customer's invoices.
 2. Look for the customer in the table.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.
 ---
@@ -1693,49 +1752,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-N1)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Expanding a customer reveals asset rows; chevrons toggle and are independent</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. A customer in the current view has invoices on at least two different vehicles (seed ZZAUTOTEST work orders on two assets if needed).
 2. At least two customers with assets are in the current view.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron control on customer A's summary row and read the rows that appear beneath it.
 2. Expand one of customer A's assets, then expand customer B.
 3. Click customer A's chevron again and check customer B.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
@@ -1750,47 +1809,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Expanding an asset reveals its invoice rows with number link and date</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded a customer and can see its asset rows.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron on an asset row.
 2. Read the invoice detail rows that appear.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
@@ -1801,48 +1860,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Invoices group into one asset row per vehicle record</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. A customer has two or more invoices on the SAME vehicle record and at least one invoice on a different vehicle (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer.
 2. Count the asset rows and compare each asset's invoice count with the invoices you created.
 3. If the environment has an older invoice with no vehicle record linked (only a stored vehicle snapshot), check which asset row it lands under.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
@@ -1852,47 +1911,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R3)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Asset rows order A to Z with the Parts Sales bucket always last</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. A customer has invoices on at least two vehicles AND at least one no-vehicle invoice (counter/parts sale) in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the asset rows top to bottom.
 2. Click a financial column header to change the table sort, and re-read the asset rows.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
@@ -1903,48 +1962,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Header-row chevron expands or collapses every customer on the current page</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Several customers are visible on the current page.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Hover the chevron in the table header row and read the tooltip.
 2. Click it and watch the customer rows.
 3. Hover it again and read the tooltip, then click it again.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
@@ -1955,49 +2014,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Reload-causing changes collapse expansion; Customer filter typing does not</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one customer expanded down to invoice rows.
 2. Enough customers exist to fill more than one page of results (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. With rows expanded, open the Customer filter and TYPE a search query (do not change the selection); watch the expanded rows.
 2. Now change the date range (or Product Type, location, Customer selection, or sort).
 3. Look at the previously expanded rows, the loading state, and the set of customers on the page.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
@@ -2008,47 +2067,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Edge: a single-invoice asset can still be expanded</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. Customer A has an asset with exactly one invoice; customer B has ONLY no-vehicle (counter/parts sale) invoices in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Expand customer A and click the chevron of the single-invoice asset.
 2. Expand customer B and read its asset rows.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
@@ -2058,47 +2117,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E1; S8-E2)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. A customer has an invoice whose number starts with S but whose work order has NO vehicle (seed a ZZAUTOTEST no-vehicle service work order and invoice it, if the app allows).</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Expand that customer.
 2. Find which asset row the S invoice sits under.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
@@ -2107,41 +2166,41 @@
 AUTOMATION: HOLD - this organisation has no service invoice without a vehicle, so nothing lands in the Parts Sales bucket from the service side</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E3)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Reversed and voided invoices are excluded from every row; count and total</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. A customer has a known set of invoices in the current range, one of which you then reverse (or void) — seed ZZAUTOTEST data and note the totals before and after.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Note the customer's invoice count "(N)" and totals with all invoices normal.
 2. Reverse (or void) one of the invoices in the application.
@@ -2149,7 +2208,7 @@
 4. Expand down to invoice rows and look for the reversed invoice.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
@@ -2160,48 +2219,48 @@
 AUTOMATION: HOLD - this organisation has no reversed or voided invoice inside the report date range</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Every row type renders the same columns in the same order</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a customer expanded down to invoice rows and the totals row visible.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
 3. Look at a customer summary row and compare how heavy its text looks with the invoice rows beneath it.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
@@ -2214,46 +2273,46 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Asset identified by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a VIN recorded, (b) one with no VIN but a Unit # recorded, (c) one with no VIN or Unit # but a plate recorded, (d) one with no VIN, Unit #, or plate (blank the fields as far as the asset form allows).</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read each asset row's label.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
@@ -2266,48 +2325,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward msg 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's year/make/model rule)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. One customer has TWO ZZAUTOTEST assets whose labels come out identical (same year/make/model and same identifier situation), each with an invoice in range.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the two asset labels.
 2. Note which asset carries " (#1)" and which " (#2)".
 3. Reload the page and expand again.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
@@ -2317,47 +2376,47 @@
 AUTOMATION: HOLD - no customer in this organisation has two assets that produce the same label, so the numbered suffix cannot appear</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R11)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>The invoice number opens the invoice in the same browser tab</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded an asset and can see at least one S invoice and (under another customer/asset if needed) one P invoice.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Click a service (S) invoice number link and note where it opens.
 2. Go back, then click a parts (P) invoice number link and note where it opens.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
@@ -2368,49 +2427,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Browser back from an invoice restores filters; sort and columns; rows shut</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with non-default filters set (for example Last Month + Service only), a non-default sort, and one column hidden.
 2. You have expanded down to an invoice detail row.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Watch the browser address bar, then click an invoice number link.
 2. From the invoice page, press the browser back button.
 3. Check the report's filters, sort, visible columns, and row expansion.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
@@ -2421,47 +2480,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R3; S9-R4)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Customer name is plain text; the invoice link never turns visited-purple</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded down to invoice detail rows and have already clicked at least one invoice link earlier in the session.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Try clicking the customer NAME on a summary row.
 2. Look at an invoice number link at rest, on hover, and one you have already visited.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
@@ -2473,48 +2532,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>An invoice deleted after load shows the not-found state and back returns</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with an invoice detail row visible.
 2. In another tab/session, that invoice is deleted or reversed AFTER the report loaded (do not refresh the report).</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Back in the report (unrefreshed), click that invoice's number link.
 2. Read the destination page, then press the browser back button.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
@@ -2524,43 +2583,43 @@
 AUTOMATION: HOLD - deleting a real invoice while the report is open is not something to do on a shared environment</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-N1)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>You cannot reach an invoice you have no permission to open</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You need TWO sign-ins: one person who can open work orders and part sales, and one person who can see reports but CANNOT open them. Ask whoever manages permissions to set the second one up, or set it up yourself in administration and put it back as you found it afterwards.
 3. On the Sales By Customer report you have expanded a customer and then an asset, so you can see the invoice rows underneath. You need one service invoice and one parts invoice — use a different customer for the second one if you have to.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as the person who CAN open them, click a service invoice's Invoice # and note where it takes you. Come back, then do the same for a parts invoice.
 2. Sign in as the person who CANNOT open them and open the Sales By Customer report again.
@@ -2569,7 +2628,7 @@
 5. Write down exactly what you see and what happens, in your own words.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. For the person who CAN open them, each Invoice # is a link: a service invoice opens the work order's Finance tab, and a parts invoice opens the part sale's Part Requests tab, both in the same browser tab.
 2. For the person who CANNOT open them, the invoice's contents stay out of reach — they must not end up looking at a work order or a part sale they are not allowed to see.
@@ -2581,42 +2640,42 @@
 AUTOMATION: HOLD - waiting on one answer from the product owner about what the invoice number should look like, and it needs a second sign-in that cannot open work orders or part sales</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v15 2026-08-05 Story 9 S9-R1a and S9-N2 — the two say different things about what the invoice number looks like; this case asserts only what both of them agree on)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>All columns sortable except chevron; text alphabetical, numbers by value</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. Several customers with differing values are in the current view.
 2. A customer with multiple assets and invoices is in the view.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
@@ -2624,7 +2683,7 @@
 4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
@@ -2639,48 +2698,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Default sort is Customer name ascending case-insensitive</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. No saved view exists (first visit or cleared storage).
 2. Customer names with mixed upper/lower-case first letters exist in the view (seed ZZAUTOTEST names like "acme test" and "Best Test").</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the customer order.
 2. Click the Subtotal header and read the order again.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
@@ -2690,47 +2749,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Missing values sort to the bottom ascending and to the top descending</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer row shows an em dash (—) in Margin % (Subtotal zero or below — seed a zero-subtotal case if possible) alongside rows with real Margin % values.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Margin % ascending and note where the em-dash row lands.
 2. Sort by Margin % descending and note it again.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
@@ -2744,47 +2803,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sorting by Date orders customers by their most recent invoice date</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Two customers exist whose most recent invoice dates differ clearly (seed ZZAUTOTEST invoices on different dates).</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date column header.
 2. Compare the customer order with each customer's most recent invoice date (expand to check the invoice dates).</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
@@ -2794,48 +2853,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Financial columns run in the specified order with Subtotal and Margin rules</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known labor, parts, and shop-supply amounts and known costs, in the current range.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Expand down to that invoice's detail row and read its values.
 3. Recalculate Subtotal and Margin by hand from the known amounts.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
@@ -2847,48 +2906,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Margin % is Margin over Subtotal to one decimal; em dash when Subtotal &lt;= 0</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Rows with a normal positive Subtotal exist, and (if seedable) one row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on a customer row, an asset row, and an invoice row; recalculate one by hand (Margin ÷ Subtotal × 100).
 2. Find (or seed) a row with Subtotal ≤ 0 and read its Margin % cell.
 3. Look at the Margin % coloring.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
@@ -2900,47 +2959,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim; value shows +green / -red / 0.0 on every row</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist where billed hours exceed worked hours, where worked exceeds billed, and where they are equal (seed ZZAUTOTEST work orders with clocked time).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
@@ -2954,47 +3013,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is never blank: no-labor rows and near-zero values both show 0.0</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice (no labor at all) exists in range; if possible also an invoice whose delta rounds to zero (for example +0.04).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
 2. If seeded, read the near-zero row's Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
@@ -3005,48 +3064,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Invoice subtotals sum to their asset row and asset subtotals to the customer</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. A customer with two or more assets, each with two or more invoices, is in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and every asset.
 2. Sum the invoice-level values by hand for each column and compare with each asset row.
 3. Sum the asset rows and compare with the customer row.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
@@ -3057,48 +3116,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R13)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Subtotal is the rightmost column; pinned on scroll and bold everywhere</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, on a window narrow enough to force horizontal scrolling (or with all columns visible).</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Subtotal column is the last column on the right.
 2. Scroll the table sideways and watch the Subtotal column.
 3. Inspect the font weight of the Subtotal header, a customer row, an asset row, an invoice row, and the totals row.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
@@ -3110,48 +3169,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8609 (SBC spec v13 2026-07-31 Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The totals row covers the whole filtered set; not just the current page</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page of results, with known amounts (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Read the totals row on page 1.
 2. Move to page 2 and read the totals row again.
 3. Compare the totals against the sum over ALL matching customers (not just one page).</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
@@ -3161,48 +3220,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Column selector is its own toolbar button with nine toggles all on</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no saved column selection (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector button in the toolbar's action area, next to the overflow menu.
 2. Hover it and read the tooltip.
 3. Click it and read the toggle list top to bottom.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
@@ -3215,48 +3274,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Column toggles hide header+cells; Customer, Subtotal and chevron never in list</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data and the column selector open.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Turn the "Shop Supplies" toggle off, then on again, watching the table.
 2. Read the toggle list for Customer, Subtotal, or a chevron entry.
 3. Turn all nine toggles off and read the table.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
@@ -3267,50 +3326,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>A one-location user never sees Location in the column-selection list</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to exactly ONE location. Check this in administration under that person's location access, and put their access back as you found it when you finish.
 3. This one test covers all six reports, so keep this same sign-in for the whole of it.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report and open the column-selection control (the toolbar button beside the overflow menu; hovering it reads "Column Selection.").
 2. Read the whole list of switches from top to bottom and look for an entry called Location.
 3. Do the same on Sales By Representative, then Parts Velocity, then Technician Utilization, then Work In Progress, then Inventory Value.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. On every one of the six reports the column-selection list does NOT contain an entry called Location.
 2. Nothing else about each list changes - only the Location entry is missing.
@@ -3322,48 +3381,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R4 with S4-R12; the never-offered rule itself comes from Chris Ward's answer T1-1 option C of 2026-08-05 and is in no specification)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
@@ -3374,41 +3433,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Download file names carry the version and the active date range</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Set the range to This Month, choose "Download Summary (CSV)" and note the downloaded file name.
 2. Choose "Download Expanded View (CSV)" and note that file name.
@@ -3417,7 +3476,7 @@
 5. Repeat steps 1-3 for "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
 2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The written description gives the word for eight of them - this_week, last_week, this_month, last_month, this_year, last_year, this_quarter, last_quarter - so check the file against those. It does not give a word for Last 12 Months, so for that one record what you see rather than judging it right or wrong.
@@ -3434,50 +3493,50 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8956)</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When the Location column is shown on screen the file also carries it — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3490,47 +3549,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>CSV formats: Margin % plain; dates mm-dd-yyyy; currency plain; no color</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
@@ -3547,48 +3606,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF hold exactly the customers matching the active filters and sort</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
@@ -3599,49 +3658,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Each download item shows a loading state and its own export-failed toast</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a large enough data set that a download takes a visible moment.
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
 2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
 3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
@@ -3653,47 +3712,47 @@
 </t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
@@ -3707,47 +3766,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8964)</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3763,48 +3822,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8937)</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
@@ -3817,42 +3876,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Expanded CSV body: column set and order, the Customer → Asset → Invoice tree, blank dates and em-dash Margin %</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Expanded CSV body: column set and order, Customer/Asset/Invoice tree, blanks</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on Sales By Customer with a view containing positive and negative Inv. Hrs values and, if seedable, a row whose Subtotal is zero or below.
 2. Nothing to install — this test reads a downloaded CSV as text.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Download "Expanded View (CSV)" from the ⋯ menu.
 2. Read the header row and compare it against the column list below.
@@ -3860,60 +3919,61 @@
 4. Find a row whose Subtotal is zero or below and read its Margin % cell.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>1. The Expanded CSV's header row carries the Expanded column set, in this exact order and with these labels — thirteen columns with a single location in scope, plus the Location column immediately after Date when more than one location is in scope.
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. The Expanded CSV's header row carries the Expanded column set, in this exact order and with these labels — thirteen columns when the Location column is not shown on screen, plus the Location column immediately after Date whenever it is shown.
 2. The body contains the full Customer → Asset → Invoice breakdown: one customer row, its asset rows beneath it, and each asset's invoice rows beneath that.
 3. The Date cell is empty on customer rows and on asset rows, and carries the invoice date only on invoice rows — matching the screen.
 4. Margin % is an em dash on any row whose Subtotal is zero or below.
 5. The file carries the "Locations:" metadata line above the header row.
 ---
 Scope note: this case covers the CSV only. The Expanded PDF renders the same data, but its page geometry, fonts, colours and bold weights are not observable by the automation suite (no PDF parser) — those assertions live in the PDF-visual cases, which are Deferred.
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification (S14-R5 Expanded contents; S4-R13 Locations line), read on 11 August 2026.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R5 Expanded contents; S4-R13 Locations line), read on 11 August 2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose a CSV download - "Download Summary (CSV)" or "Download Expanded View (CSV)".
 2. Choose a PDF download - "Download Summary (PDF)" or "Download Expanded View (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3929,47 +3989,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>A no-match export still downloads headers and a zero totals row</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Choose a CSV download - "Download Summary (CSV)" or "Download Expanded View (CSV)" - and open the file.
 2. Choose a PDF download - "Download Summary (PDF)" or "Download Expanded View (PDF)" - and open the file.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers, a totals row of zeros, and no data rows.
@@ -3984,90 +4044,90 @@
 </t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the four items.
 2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
 3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
+5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When the Location column is shown on screen a Location column is added immediately after the Customer name and before the money columns.
 ---
 This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. the Sales By Customer report specification version 17 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
 Last checked against build v3.5-7168d14 on 8/6/2026.
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>A logo that is set but will not load falls back to the ShopView logo</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser and you can change the organization's uploaded logo in administration.
 2. You will need the organization in a state where a logo IS set but the picture will not load - for example an uploaded logo whose file has since been removed or renamed. Ask a developer to help you produce that state if you cannot.
@@ -4075,7 +4135,7 @@
 4. This one test covers the printable download on all six reports, so do the setup once and check all six.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. With a logo uploaded and loading normally, download the printable file from each of the six reports and look at the top right of the header.
 2. Put the organization into the state where a logo is set but the picture will not load.
@@ -4084,7 +4144,7 @@
 5. Put the organization's original logo back.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. With a logo that loads, that logo is shown at the top right, sized to fit without being stretched.
 2. With a logo that is set but will not load, the built-in ShopView logo is shown in its place - not a blank space, not a broken-picture icon, and no error message.
@@ -4097,48 +4157,48 @@
 AUTOMATION: HOLD - this organisation has a logo that loads correctly, so the set-but-will-not-load fallback cannot be produced</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R17 and S15-R18 - the logo order and the no-logo layout; the set-but-fails-to-load step is Chris Ward's answer T3-4 option C of 2026-08-05 alone)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
@@ -4148,48 +4208,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -4201,48 +4261,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
@@ -4257,47 +4317,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8966)</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
@@ -4307,49 +4367,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -4363,48 +4423,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
@@ -4415,48 +4475,48 @@
 </t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
@@ -4467,42 +4527,42 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.
 2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -4511,7 +4571,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -4525,48 +4585,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
@@ -4576,41 +4636,41 @@
 AUTOMATION: HOLD - a failing data fetch cannot be forced from the application</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
 2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
@@ -4619,7 +4679,7 @@
 5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4640,49 +4700,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4699,47 +4759,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
@@ -4749,48 +4809,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
@@ -4801,48 +4861,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
@@ -4853,42 +4913,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4896,7 +4956,7 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
@@ -4907,49 +4967,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -4962,49 +5022,49 @@
 </t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
@@ -5015,49 +5075,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
@@ -5068,48 +5128,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a CSV download ("Download Summary (CSV)" or "Download Expanded View (CSV)") and a PDF download ("Download Summary (PDF)" or "Download Expanded View (PDF)"), and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
@@ -5123,43 +5183,43 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>The back end serves SBC report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
 2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the user WHO HAS ordinary reports access and open Sales By Customer.
 2. In the network panel, find the request the page makes for the report's data and read its response code.
@@ -5169,7 +5229,7 @@
 6. Ask for the same export by its address and read that response code too.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
@@ -5183,13 +5243,13 @@
 </t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8600 (SBC spec v13 2026-07-31 S1-R2; S1-N1 — the back-end half of the ordinary-reports-access gate; the SBC twin of the Parts Velocity back-end case C30391; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1658,38 +1658,89 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>Each invoice detail row shows a per-invoice Adjustments value</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Tree &amp; Rows</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A customer asset has an invoice carrying an invoice-level fee or discount.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report.
+2. Expand a customer to its assets, and an asset to its invoices.
+3. Read the invoice detail row.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. The invoice detail row shows the invoice number (as a link), the invoice date, and per-invoice Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin % and Subtotal.
+2. The per-invoice Adjustments value is the signed net of that invoice's invoice-level fees and discounts.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9280, and the Sales By Customer report specification version 20 (S8-R12), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SV-9280 (SBC spec v20 2026-08-12 S8-R12 — invoice detail row shows per-invoice Adjustments)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Each customer gets one summary row with its invoice count in parentheses</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.
 2. A customer has a known number of matching invoices in the current date range (seed ZZAUTOTEST data so the count is predictable).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Find that customer's row at the top level of the table.
 2. Read the text at the start of the row.
 3. Narrow the date range so fewer of that customer's invoices match, and re-read the count.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
@@ -1702,48 +1753,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>A customer with no matching invoices in the current view is not shown</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. A customer exists whose invoices all fall OUTSIDE the current date range (seed if needed).
 2. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains none of that customer's invoices.
 2. Look for the customer in the table.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.
 ---
@@ -1752,49 +1803,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-N1)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Expanding a customer reveals asset rows; chevrons toggle and are independent</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. A customer in the current view has invoices on at least two different vehicles (seed ZZAUTOTEST work orders on two assets if needed).
 2. At least two customers with assets are in the current view.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron control on customer A's summary row and read the rows that appear beneath it.
 2. Expand one of customer A's assets, then expand customer B.
 3. Click customer A's chevron again and check customer B.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
@@ -1809,47 +1860,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Expanding an asset reveals its invoice rows with number link and date</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded a customer and can see its asset rows.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Click the chevron on an asset row.
 2. Read the invoice detail rows that appear.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
@@ -1860,48 +1911,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Invoices group into one asset row per vehicle record</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. A customer has two or more invoices on the SAME vehicle record and at least one invoice on a different vehicle (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer.
 2. Count the asset rows and compare each asset's invoice count with the invoices you created.
 3. If the environment has an older invoice with no vehicle record linked (only a stored vehicle snapshot), check which asset row it lands under.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
@@ -1911,47 +1962,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R3)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Asset rows order A to Z with the Parts Sales bucket always last</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. A customer has invoices on at least two vehicles AND at least one no-vehicle invoice (counter/parts sale) in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the asset rows top to bottom.
 2. Click a financial column header to change the table sort, and re-read the asset rows.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
@@ -1962,48 +2013,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Header-row chevron expands or collapses every customer on the current page</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. Several customers are visible on the current page.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Hover the chevron in the table header row and read the tooltip.
 2. Click it and watch the customer rows.
 3. Hover it again and read the tooltip, then click it again.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
@@ -2014,49 +2065,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Reload-causing changes collapse expansion; Customer filter typing does not</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least one customer expanded down to invoice rows.
 2. Enough customers exist to fill more than one page of results (seed ZZAUTOTEST customers if needed).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. With rows expanded, open the Customer filter and TYPE a search query (do not change the selection); watch the expanded rows.
 2. Now change the date range (or Product Type, location, Customer selection, or sort).
 3. Look at the previously expanded rows, the loading state, and the set of customers on the page.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
@@ -2067,47 +2118,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Edge: a single-invoice asset can still be expanded</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. Customer A has an asset with exactly one invoice; customer B has ONLY no-vehicle (counter/parts sale) invoices in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Expand customer A and click the chevron of the single-invoice asset.
 2. Expand customer B and read its asset rows.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
@@ -2117,47 +2168,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E1; S8-E2)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>A service (S) invoice with no vehicle also lands in the Parts Sales bucket</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. A customer has an invoice whose number starts with S but whose work order has NO vehicle (seed a ZZAUTOTEST no-vehicle service work order and invoice it, if the app allows).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Expand that customer.
 2. Find which asset row the S invoice sits under.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
@@ -2166,41 +2217,41 @@
 AUTOMATION: HOLD - this organisation has no service invoice without a vehicle, so nothing lands in the Parts Sales bucket from the service side</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E3)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Reversed and voided invoices are excluded from every row; count and total</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. A customer has a known set of invoices in the current range, one of which you then reverse (or void) — seed ZZAUTOTEST data and note the totals before and after.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Note the customer's invoice count "(N)" and totals with all invoices normal.
 2. Reverse (or void) one of the invoices in the application.
@@ -2208,7 +2259,7 @@
 4. Expand down to invoice rows and look for the reversed invoice.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
@@ -2219,48 +2270,48 @@
 AUTOMATION: HOLD - this organisation has no reversed or voided invoice inside the report date range</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Every row type renders the same columns in the same order</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>SBC — Tree &amp; Rows</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a customer expanded down to invoice rows and the totals row visible.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
 3. Look at a customer summary row and compare how heavy its text looks with the invoice rows beneath it.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
@@ -2273,46 +2324,46 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Asset identified by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. One customer has ZZAUTOTEST assets with invoices in range: (a) one with a VIN recorded, (b) one with no VIN but a Unit # recorded, (c) one with no VIN or Unit # but a plate recorded, (d) one with no VIN, Unit #, or plate (blank the fields as far as the asset form allows).</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read each asset row's label.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
@@ -2325,48 +2376,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec Story 8 S8-R7; S8-R8; S8-R9; S8-R10 - identifier RE-RULED to the VIN chain (VIN -&gt; Unit # -&gt; plate); by Chris Ward msg 2026-07-29 [newest-wins]; supersedes video P24 serial ruling AND the spec's year/make/model rule)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Duplicate asset labels get stable (#1)/(#2) suffixes that survive reloads</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>SBC — Asset Labels</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. One customer has TWO ZZAUTOTEST assets whose labels come out identical (same year/make/model and same identifier situation), each with an invoice in range.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and read the two asset labels.
 2. Note which asset carries " (#1)" and which " (#2)".
 3. Reload the page and expand again.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
@@ -2376,47 +2427,47 @@
 AUTOMATION: HOLD - no customer in this organisation has two assets that produce the same label, so the numbered suffix cannot appear</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R11)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>The invoice number opens the invoice in the same browser tab</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded an asset and can see at least one S invoice and (under another customer/asset if needed) one P invoice.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Click a service (S) invoice number link and note where it opens.
 2. Go back, then click a parts (P) invoice number link and note where it opens.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
@@ -2427,49 +2478,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Browser back from an invoice restores filters; sort and columns; rows shut</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with non-default filters set (for example Last Month + Service only), a non-default sort, and one column hidden.
 2. You have expanded down to an invoice detail row.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Watch the browser address bar, then click an invoice number link.
 2. From the invoice page, press the browser back button.
 3. Check the report's filters, sort, visible columns, and row expansion.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
@@ -2480,47 +2531,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R3; S9-R4)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Customer name is plain text; the invoice link never turns visited-purple</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. You have expanded down to invoice detail rows and have already clicked at least one invoice link earlier in the session.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Try clicking the customer NAME on a summary row.
 2. Look at an invoice number link at rest, on hover, and one you have already visited.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
@@ -2532,48 +2583,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>An invoice deleted after load shows the not-found state and back returns</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. The report is open with an invoice detail row visible.
 2. In another tab/session, that invoice is deleted or reversed AFTER the report loaded (do not refresh the report).</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Back in the report (unrefreshed), click that invoice's number link.
 2. Read the destination page, then press the browser back button.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
@@ -2583,43 +2634,43 @@
 AUTOMATION: HOLD - deleting a real invoice while the report is open is not something to do on a shared environment</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-N1)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>You cannot reach an invoice you have no permission to open</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>SBC — Invoice Links &amp; Navigation</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You need TWO sign-ins: one person who can open work orders and part sales, and one person who can see reports but CANNOT open them. Ask whoever manages permissions to set the second one up, or set it up yourself in administration and put it back as you found it afterwards.
 3. On the Sales By Customer report you have expanded a customer and then an asset, so you can see the invoice rows underneath. You need one service invoice and one parts invoice — use a different customer for the second one if you have to.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as the person who CAN open them, click a service invoice's Invoice # and note where it takes you. Come back, then do the same for a parts invoice.
 2. Sign in as the person who CANNOT open them and open the Sales By Customer report again.
@@ -2628,7 +2679,7 @@
 5. Write down exactly what you see and what happens, in your own words.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. For the person who CAN open them, each Invoice # is a link: a service invoice opens the work order's Finance tab, and a parts invoice opens the part sale's Part Requests tab, both in the same browser tab.
 2. For the person who CANNOT open them, the invoice's contents stay out of reach — they must not end up looking at a work order or a part sale they are not allowed to see.
@@ -2640,42 +2691,42 @@
 AUTOMATION: HOLD - waiting on one answer from the product owner about what the invoice number should look like, and it needs a second sign-in that cannot open work orders or part sales</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>SV-8607 (SBC spec v15 2026-08-05 Story 9 S9-R1a and S9-N2 — the two say different things about what the invoice number looks like; this case asserts only what both of them agree on)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>All columns sortable except chevron; text alphabetical, numbers by value</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Several customers with differing values are in the current view.
 2. A customer with multiple assets and invoices is in the view.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
@@ -2683,7 +2734,7 @@
 4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
@@ -2698,48 +2749,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Default sort is Customer name ascending case-insensitive</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. No saved view exists (first visit or cleared storage).
 2. Customer names with mixed upper/lower-case first letters exist in the view (seed ZZAUTOTEST names like "acme test" and "Best Test").</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Open the report and read the customer order.
 2. Click the Subtotal header and read the order again.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
@@ -2749,47 +2800,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Missing values sort to the bottom ascending and to the top descending</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. At least one customer row shows an em dash (—) in Margin % (Subtotal zero or below — seed a zero-subtotal case if possible) alongside rows with real Margin % values.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Margin % ascending and note where the em-dash row lands.
 2. Sort by Margin % descending and note it again.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
@@ -2803,47 +2854,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R3)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sorting by Date orders customers by their most recent invoice date</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>SBC — Sorting</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Two customers exist whose most recent invoice dates differ clearly (seed ZZAUTOTEST invoices on different dates).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Click the Date column header.
 2. Compare the customer order with each customer's most recent invoice date (expand to check the invoice dates).</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
@@ -2853,48 +2904,203 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R5)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Adjustments column appears between Shop Supplies and Margin</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Totals &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A customer has at least one invoice carrying an invoice-level fee or discount in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report.
+2. Look at the financial columns left to right.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1. The financial columns appear in this order: Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %.
+2. "Adjustments" sits between "Shop Supplies" and "Margin".
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9280, and the Sales By Customer report specification version 20 (S7-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>SV-9280 (SBC spec v20 2026-08-12 S7-R6 — Adjustments in the financial column order between Shop Supplies and Margin)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Adjustments is the signed net of invoice-level fees and discounts</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Totals &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A customer has invoices with invoice-level fees and invoice-level discounts in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report.
+2. Read the Adjustments value on a customer row, an asset row and an invoice row.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1. Adjustments shows the signed net of invoice-level fees and discounts: fees count positive, discounts count negative.
+2. A line-level fee or discount stays folded into that line's Labor or Parts value and is not part of Adjustments.
+3. Adjustments is never allocated into the Labor or Parts columns.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9280, and the Sales By Customer report specification version 20 (S7-R17), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>SV-9280 (SBC spec v20 2026-08-12 S7-R17 — signed net of invoice-level fees/discounts; never allocated into Labor/Parts)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Every row ties out once Adjustments is included</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Totals &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A customer has an invoice carrying an invoice-level fee or discount in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report.
+2. On a customer row, add Labor Invoiced, Parts Invoiced, Shop Supplies and Adjustments.
+3. Compare the total to Subtotal.
+4. Add Labor Margin, Parts Margin and Adjustments and compare to Margin.
+5. Repeat the checks on an asset row, an invoice row and the totals row.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1. Labor Invoiced + Parts Invoiced + Shop Supplies + Adjustments equals Subtotal.
+2. Labor Margin + Parts Margin + Adjustments equals Margin.
+3. The ties hold on customer rows, asset rows, invoice rows and the totals row alike.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9280, and the Sales By Customer report specification version 20 (S7-R18), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>SV-9280 (SBC spec v20 2026-08-12 S7-R18 — row ties out: Labor+Parts+Supplies+Adjustments=Subtotal; LaborMargin+PartsMargin+Adjustments=Margin)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Financial columns run in the specified order with Subtotal and Margin rules</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. A ZZAUTOTEST invoice exists with known labor, parts, and shop-supply amounts and known costs, in the current range.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Read the column headers left to right.
 2. Expand down to that invoice's detail row and read its values.
 3. Recalculate Subtotal and Margin by hand from the known amounts.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
@@ -2906,48 +3112,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Margin % is Margin over Subtotal to one decimal; em dash when Subtotal &lt;= 0</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. Rows with a normal positive Subtotal exist, and (if seedable) one row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Read Margin % on a customer row, an asset row, and an invoice row; recalculate one by hand (Margin ÷ Subtotal × 100).
 2. Find (or seed) a row with Subtotal ≤ 0 and read its Margin % cell.
 3. Look at the Margin % coloring.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
@@ -2959,47 +3165,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs heading is verbatim; value shows +green / -red / 0.0 on every row</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. Invoices exist where billed hours exceed worked hours, where worked exceeds billed, and where they are equal (seed ZZAUTOTEST work orders with clocked time).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
 2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
@@ -3013,47 +3219,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Inv. Hrs is never blank: no-labor rows and near-zero values both show 0.0</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. A parts-only invoice (no labor at all) exists in range; if possible also an invoice whose delta rounds to zero (for example +0.04).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
 2. If seeded, read the near-zero row's Inv. Hrs.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
@@ -3064,48 +3270,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Invoice subtotals sum to their asset row and asset subtotals to the customer</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. A customer with two or more assets, each with two or more invoices, is in the current view (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Expand the customer and every asset.
 2. Sum the invoice-level values by hand for each column and compare with each asset row.
 3. Sum the asset rows and compare with the customer row.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
@@ -3116,48 +3322,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R13)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Subtotal is the rightmost column; pinned on scroll and bold everywhere</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data, on a window narrow enough to force horizontal scrolling (or with all columns visible).</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the Subtotal column is the last column on the right.
 2. Scroll the table sideways and watch the Subtotal column.
 3. Inspect the font weight of the Subtotal header, a customer row, an asset row, an invoice row, and the totals row.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
@@ -3169,48 +3375,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8609 (SBC spec v13 2026-07-31 Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>The totals row covers the whole filtered set; not just the current page</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>SBC — Totals &amp; Calculations</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page of results, with known amounts (seed ZZAUTOTEST data).</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Read the totals row on page 1.
 2. Move to page 2 and read the totals row again.
 3. Compare the totals against the sum over ALL matching customers (not just one page).</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
@@ -3220,48 +3426,97 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>The column selector lists ten toggleable columns including Adjustments</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Column Selector</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report.
+2. Open the column selector.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. The column selector lists ten toggleable columns, in order: Date, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %.
+2. "Adjustments" is one of the toggleable columns, between Shop Supplies and Margin.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9280, and the Sales By Customer report specification version 20 (S13-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-9280 (SBC spec v20 2026-08-12 S13-R4 — ten toggleable columns including Adjustments)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Column selector is its own toolbar button with nine toggles all on</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with no saved column selection (first visit or cleared storage).</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector button in the toolbar's action area, next to the overflow menu.
 2. Hover it and read the tooltip.
 3. Click it and read the toggle list top to bottom.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
@@ -3274,48 +3529,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Column toggles hide header+cells; Customer, Subtotal and chevron never in list</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data and the column selector open.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Turn the "Shop Supplies" toggle off, then on again, watching the table.
 2. Read the toggle list for Customer, Subtotal, or a chevron entry.
 3. Turn all nine toggles off and read the table.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
@@ -3326,50 +3581,50 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>A one-location user never sees Location in the column-selection list</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>SBC — Column Selector</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. You are signed in as a person who has access to exactly ONE location. Check this in administration under that person's location access, and put their access back as you found it when you finish.
 3. This one test covers all six reports, so keep this same sign-in for the whole of it.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report and open the column-selection control (the toolbar button beside the overflow menu; hovering it reads "Column Selection.").
 2. Read the whole list of switches from top to bottom and look for an entry called Location.
 3. Do the same on Sales By Representative, then Parts Velocity, then Technician Utilization, then Work In Progress, then Inventory Value.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. On every one of the six reports the column-selection list does NOT contain an entry called Location.
 2. Nothing else about each list changes - only the Location entry is missing.
@@ -3381,48 +3636,100 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R4 with S4-R12; the never-offered rule itself comes from Chris Ward's answer T1-1 option C of 2026-08-05 and is in no specification)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Both CSV exports include the Adjustments column in the specified position</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A customer has an invoice with an invoice-level fee or discount in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Sales By Customer report.
+2. Download the Summary CSV and open it.
+3. Download the Expanded CSV and open it.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1. The Summary CSV columns, in order, are: Customer, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, Subtotal.
+2. The Expanded CSV columns, in order, are: Customer, Asset, Invoice #, Date, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, Subtotal.
+3. Adjustments carries the same signed values as on screen (fees positive, discounts negative).
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and story SV-9280, and the Sales By Customer report specification version 20 (S14-R4, S14-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>SV-9280 (SBC spec v20 2026-08-12 S14-R4; S14-R5 — Summary and Expanded CSV column order includes Adjustments)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>The overflow menu holds exactly the four download items - no Print</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Find the overflow menu in the toolbar's action area and note its position.
 2. Open it and read the items in order.
 3. Look around the toolbar for any separate always-visible export buttons.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
@@ -3433,41 +3740,41 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Download file names carry the version and the active date range</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Set the range to This Month, choose "Download Summary (CSV)" and note the downloaded file name.
 2. Choose "Download Expanded View (CSV)" and note that file name.
@@ -3476,7 +3783,7 @@
 5. Repeat steps 1-3 for "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
 2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The written description gives the word for eight of them - this_week, last_week, this_month, last_month, this_year, last_year, this_quarter, last_quarter - so check the file against those. It does not give a word for Last 12 Months, so for that one record what you see rather than judging it right or wrong.
@@ -3493,48 +3800,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8956)</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Expanded View CSV: column order, blank-cell rules, and the Locations line</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the CSV for a view with at least one customer with several invoices.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Read the header row.
 2. Read a customer row and an invoice row.
 3. Look for any asset-level rows.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When the Location column is shown on screen the file also carries it — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
@@ -3549,54 +3856,53 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>CSV formats: Margin % plain; dates mm-dd-yyyy; currency plain; no color</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded a CSV containing rows with real values, including (if seedable) a row whose Subtotal is zero or below.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Read a Margin % cell, a Date cell, and a currency cell in a text editor.
 2. Check the row whose Subtotal is ≤ 0.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
-On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
-What you should see today: in the spreadsheet the money arrives as text with a dollar sign and thousands separators, such as $11,176.88, and the columns come out in the file's own fixed order - Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Total Cost, Total Sell, Margin, Margin % - which is not the order on screen, does not put Total Cost last, and leaves out the Location column even when it is showing on screen. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
+What you should see today: the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
@@ -3606,48 +3912,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>CSV and PDF hold exactly the customers matching the active filters and sort</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. Data exists across two locations, both product types, and several customers.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Set a specific date range, Product Type "Service only", one location, a two-customer selection in the Customer filter, and a Subtotal sort.
 2. Download the CSV and the PDF.
 3. Compare each file's contents against the on-screen rows.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
@@ -3658,49 +3964,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Each download item shows a loading state and its own export-failed toast</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with a large enough data set that a download takes a visible moment.
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (CSV)" and immediately look at that menu item.
 2. To provoke a failure, disconnect the network (or use the browser's offline mode) and choose "Download Summary (CSV)" again.
 3. Repeat both checks for "Download Expanded View (CSV)", "Download Summary (PDF)" and "Download Expanded View (PDF)".</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
@@ -3712,47 +4018,47 @@
 </t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>PDF page: A4 landscape, uniform margins, ShopView footer and page numbers</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF for a view with enough rows to span more than one page.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the PDF and check the page setup.
 2. Read the footer on each page.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
@@ -3766,47 +4072,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8964)</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>PDF header: title, organization, date range, Product Type and Locations lines</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You have downloaded the PDF with a known date range, Product Type, and a specific location selected.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Read the header's text block top to bottom.
 2. Look for any mention of the selected location.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
@@ -3822,48 +4128,48 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8937)</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>PDF logo is embedded, scales without distortion</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the organization's uploaded logo on/off in administration (restore it afterwards).</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded org logo, download the PDF and check the top-right.
 2. Remove the uploaded logo, download again, and check.
 3. Open a PDF while offline to confirm the logo still renders.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
@@ -3876,42 +4182,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Expanded CSV body: column set and order, Customer/Asset/Invoice tree, blanks</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on Sales By Customer with a view containing positive and negative Inv. Hrs values and, if seedable, a row whose Subtotal is zero or below.
 2. Nothing to install — this test reads a downloaded CSV as text.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Download "Expanded View (CSV)" from the ⋯ menu.
 2. Read the header row and compare it against the column list below.
@@ -3919,7 +4225,7 @@
 4. Find a row whose Subtotal is zero or below and read its Margin % cell.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The Expanded CSV's header row carries the Expanded column set, in this exact order and with these labels — thirteen columns when the Location column is not shown on screen, plus the Location column immediately after Date whenever it is shown.
 2. The body contains the full Customer → Asset → Invoice breakdown: one customer row, its asset rows beneath it, and each asset's invoice rows beneath that.
@@ -3932,48 +4238,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>An export over 10,000 data rows is refused with the too-large toast</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. A filter combination exists whose customer rows plus invoice rows exceed 10,000 (widest range, all locations, all customers). If the environment cannot reach 10,000 rows even fully widened, record the max reachable and mark Blocked-Env with reason.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. With the over-cap filter set, choose a CSV download - "Download Summary (CSV)" or "Download Expanded View (CSV)".
 2. Choose a PDF download - "Download Summary (PDF)" or "Download Expanded View (PDF)".
 3. Narrow the filters below the cap and re-try one export.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
@@ -3989,47 +4295,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>A no-match export still downloads headers and a zero totals row</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The Customer filter selection is empty ("Clear all") or the filters otherwise match no customers.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Choose a CSV download - "Download Summary (CSV)" or "Download Expanded View (CSV)" - and open the file.
 2. Choose a PDF download - "Download Summary (PDF)" or "Download Expanded View (PDF)" - and open the file.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers, a totals row of zeros, and no data rows.
@@ -4044,48 +4350,48 @@
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R10)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Summary and Expanded View downloads exist for both PDF and CSV</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Sales By Customer report with at least one customer and several invoices in the chosen date range.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the download (overflow) menu and read the four items.
 2. Download the Summary version in both formats (Download Summary (PDF) and Download Summary (CSV)) and open the files.
 3. Download the Expanded View version in both formats and compare against the Summary files.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
@@ -4098,36 +4404,36 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>A logo that is set but will not load falls back to the ShopView logo</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>SBC — Exports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser and you can change the organization's uploaded logo in administration.
 2. You will need the organization in a state where a logo IS set but the picture will not load - for example an uploaded logo whose file has since been removed or renamed. Ask a developer to help you produce that state if you cannot.
@@ -4135,7 +4441,7 @@
 4. This one test covers the printable download on all six reports, so do the setup once and check all six.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. With a logo uploaded and loading normally, download the printable file from each of the six reports and look at the top right of the header.
 2. Put the organization into the state where a logo is set but the picture will not load.
@@ -4144,7 +4450,7 @@
 5. Put the organization's original logo back.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. With a logo that loads, that logo is shown at the top right, sized to fit without being stretched.
 2. With a logo that is set but will not load, the built-in ShopView logo is shown in its place - not a blank space, not a broken-picture icon, and no error message.
@@ -4157,48 +4463,48 @@
 AUTOMATION: HOLD - this organisation has a logo that loads correctly, so the set-but-will-not-load fallback cannot be produced</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R17 and S15-R18 - the logo order and the no-logo layout; the set-but-fails-to-load step is Chris Ward's answer T3-4 option C of 2026-08-05 alone)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
@@ -4208,48 +4514,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -4261,48 +4567,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
@@ -4317,47 +4623,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8966)</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
@@ -4367,49 +4673,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -4423,48 +4729,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
@@ -4475,48 +4781,48 @@
 </t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
@@ -4527,42 +4833,42 @@
 </t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.
 2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -4571,7 +4877,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -4585,48 +4891,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
@@ -4636,41 +4942,41 @@
 AUTOMATION: HOLD - a failing data fetch cannot be forced from the application</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
 2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
@@ -4679,7 +4985,7 @@
 5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -4700,49 +5006,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -4759,47 +5065,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
@@ -4809,48 +5115,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>On a phone every toolbar control works on touch; the toolbar splits in two</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You open the report on a phone-sized viewport (real device or browser device emulation).</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Try each toolbar control by touch: date range, Product Type, the Customer filter, location, the overflow menu, and the column selector.
 2. At a width below 1024px, look at the toolbar rows.
 3. Widen the window to 1024px or more and look again.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
@@ -4861,48 +5167,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>On touch the table scrolls sideways with Subtotal pinned and chevrons work</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>SBC — Mobile</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report on a phone-sized viewport with data.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Swipe the table sideways to reach the far columns.
 2. Tap a customer chevron and an asset chevron.
 3. Tap an invoice number link.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
@@ -4913,42 +5219,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Asset and invoice rows are fetched on first expand; one call per customer</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with several customers, with the browser's network activity panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and note the requests made for the summary rows.
 2. Expand one customer for the first time and watch the network panel.
@@ -4956,7 +5262,7 @@
 4. Use the header chevron's expand-all and count the drill-down requests.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
@@ -4967,49 +5273,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Sorting is applied on the server and re-fetches the first page</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network panel.
 2. Compare the returned first page with the previous page contents.
 3. Optional (API tooling): repeat the request with a made-up sort column name and read the response.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
@@ -5022,49 +5328,49 @@
 </t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>The Customer type-ahead queries the server instead of loading every name</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with the browser's network panel open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Open the Customer filter WITHOUT typing and check whether a full customer list was downloaded.
 2. Type a query and watch the network panel.
 3. Change the query and watch again.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
@@ -5075,49 +5381,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Customer rows are server-paginated; the totals row is server-computed</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the summary-row response and the totals values.
 2. Change the Customer filter selection and watch the requests.
 3. Move between pages and watch the totals.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
@@ -5128,48 +5434,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Exports are server-generated and the 10,000-row cap is counted first</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a CSV download ("Download Summary (CSV)" or "Download Expanded View (CSV)") and a PDF download ("Download Summary (PDF)" or "Download Expanded View (PDF)"), and observe where the file content comes from.
 2. If an over-cap set is available, trigger an export and observe the server's refusal.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
@@ -5183,43 +5489,43 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>The back end serves SBC report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>SBC — API</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
 2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the user WHO HAS ordinary reports access and open Sales By Customer.
 2. In the network panel, find the request the page makes for the report's data and read its response code.
@@ -5229,7 +5535,7 @@
 6. Ask for the same export by its address and read that response code too.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
@@ -5243,13 +5549,13 @@
 </t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-8600 (SBC spec v13 2026-07-31 S1-R2; S1-N1 — the back-end half of the ordinary-reports-access gate; the SBC twin of the Parts Velocity back-end case C30391; Chris Ward Q1=A; SV-8780 Ready to Fix)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Sales-By-Customer-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1903,17 +1903,16 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
-2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
+2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S8-R4, S8-R12, S8-R12a, S20-R14), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S8-R12; S7-R17; S7-R18), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
+          <t>SV-8608 (SBC spec v20 2026-08-17 S8-R12; S7-R17; S7-R18; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2728,7 +2727,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Click each column header in turn (Customer, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal) and watch the order change.
+          <t>1. Click each column header in turn (Customer, Date, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, Subtotal) and watch the order change.
 2. Try clicking the chevron column's header position.
 3. Compare a text sort (Customer) and a numeric sort (Subtotal) against the values.
 4. Sort by Subtotal descending, expand a customer and an asset, and read the asset and invoice order.</t>
@@ -2744,14 +2743,13 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S10-R1, S10-R2, S10-R6), read on 11 August 2026.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8963)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S10-R1; S10-R2; S10-R6; S13-R4), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R1; S10-R2; S10-R6)</t>
+          <t>SV-8608 (SBC spec v20 2026-08-17 S10-R1; S10-R2; S10-R6; S13-R4; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3102,19 +3100,18 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
-2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
+          <t>1. The financial columns appear in this order: Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin % — with Subtotal as the rightmost column.
+2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies + Adjustments, before tax.
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
-4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S7-R6, S11-R1, S4-R12, S20-R19), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+4. Margin = Labor Margin + Parts Margin + Adjustments — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin). Adjustments (the signed net of invoice-level fees and discounts) is never allocated into Labor or Parts and carries no cost, so its full amount flows into Margin.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S7-R17; S7-R18; §Terminology Subtotal and Margin include Adjustments), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (SBC spec v13 2026-07-31 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
+          <t>SV-8609 (SBC spec v20 2026-08-17 S7-R17; S7-R18; §Terminology Subtotal and Margin include Adjustments; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3176,7 +3173,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs heading is verbatim; value shows +green / -red / 0.0 on every row</t>
+          <t>Labor Delta heading is verbatim; value shows +green / -red / 0.0 on every row</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3202,26 +3199,25 @@
       <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Read the column heading.
-2. Read the Inv. Hrs value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
+2. Read the Labor Delta value on rows for each of the three seeded situations, at customer, asset, and invoice level.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
+          <t>1. The column heading reads "Labor Delta".
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
 3. A positive value shows a leading + sign in the application's standard positive (green) color — for example, +1.5.
 4. A negative value shows a leading - sign in the standard negative (red) color — for example, -1.5.
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
+          <t>SV-8610 (SBC spec v20 2026-08-17 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3230,7 +3226,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Inv. Hrs is never blank: no-labor rows and near-zero values both show 0.0</t>
+          <t>Labor Delta is never blank: no-labor rows and near-zero values both show 0.0</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3255,8 +3251,8 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1. Read the Inv. Hrs cell on the parts-only invoice's rows (invoice, asset, customer).
-2. If seeded, read the near-zero row's Inv. Hrs.</t>
+          <t>1. Read the Labor Delta cell on the parts-only invoice's rows (invoice, asset, customer).
+2. If seeded, read the near-zero row's Labor Delta.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3265,14 +3261,13 @@
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S12-N1, S12-E1, S12-E2), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S12-N1, S12-E1, S12-E2), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-N1; S12-E1; S12-E2)</t>
+          <t>SV-8610 (SBC spec v20 2026-08-17 S12-N1,S12-E1,S12-E2; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3486,7 +3481,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Column selector is its own toolbar button with nine toggles all on</t>
+          <t>Column selector is its own toolbar button with ten toggles all on</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3520,18 +3515,17 @@
         <is>
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
-3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
-4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+3. The panel lists ten toggles, in order: Date, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %.
+4. With no saved selection, all ten toggleable columns default to visible.
+5. Note for the tester: this panel lists ten toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S13-R4), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
+          <t>SV-8611 (SBC spec v20 2026-08-17 S13-R4; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3843,7 +3837,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When the Location column is shown on screen the file also carries it — immediately after Date, the position it holds on screen — making fourteen.
+          <t>1. With a single location in scope the Expanded View CSV has these fourteen columns in this exact order: Customer, Asset, Invoice #, Date, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, Subtotal. When the Location column is shown on screen the file also carries it — immediately after Date, the position it holds on screen — making fifteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3851,14 +3845,13 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S14-R5), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
+          <t>SV-8612 (SBC spec v20 2026-08-17 S14-R5; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3901,20 +3894,19 @@
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
-4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
+4. The CSV has no color; the signed Labor Delta value still conveys direction.
 What you should see today: the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8823
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8823)</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
+          <t>SV-8612 (SBC spec v20 2026-08-17 S14-R9,S14-R10,S14-R11,S14-R12,S14-R13; heading renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4213,7 +4205,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1. You are on Sales By Customer with a view containing positive and negative Inv. Hrs values and, if seedable, a row whose Subtotal is zero or below.
+          <t>1. You are on Sales By Customer with a view containing positive and negative Labor Delta values and, if seedable, a row whose Subtotal is zero or below.
 2. Nothing to install — this test reads a downloaded CSV as text.</t>
         </is>
       </c>
@@ -4227,20 +4219,19 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded CSV's header row carries the Expanded column set, in this exact order and with these labels — thirteen columns when the Location column is not shown on screen, plus the Location column immediately after Date whenever it is shown.
+          <t>1. The Expanded CSV's header row carries the Expanded column set, in this exact order and with these labels — fourteen columns (Customer, Asset, Invoice #, Date, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, Subtotal) when the Location column is not shown on screen, plus the Location column immediately after Date whenever it is shown.
 2. The body contains the full Customer → Asset → Invoice breakdown: one customer row, its asset rows beneath it, and each asset's invoice rows beneath that.
 3. The Date cell is empty on customer rows and on asset rows, and carries the invoice date only on invoice rows — matching the screen.
 4. Margin % is an em dash on any row whose Subtotal is zero or below.
 5. The file carries the "Locations:" metadata line above the header row.
 ---
-Scope note: this case covers the CSV only. The Expanded PDF renders the same data, but its page geometry, fonts, colours and bold weights are not observable by the automation suite (no PDF parser) — those assertions live in the PDF-visual cases, which are Deferred.
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Sales By Customer report specification version 17 (S14-R5 Expanded contents; S4-R13 Locations line), read on 11 August 2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S14-R5), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
+          <t>SV-8612 (SBC spec v20 2026-08-17 S14-R5; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -4397,16 +4388,15 @@
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When the Location column is shown on screen a Location column is added immediately after the Customer name and before the money columns.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. the Sales By Customer report specification version 17 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
-Last checked against build v3.5-7168d14 on 8/6/2026.
-AUTOMATION: READY</t>
+5. With a single location in scope the Summary files have these eleven columns in this exact order: Customer, Labor Delta, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Adjustments, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When the Location column is shown on screen a Location column is added immediately after the Customer name and before the money columns.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S14-R4), both read on 17 August 2026. The column was renamed from "Inv. Hrs" to "Labor Delta" per SV-9071; only the name changed.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
+          <t>SV-8612 (SBC spec v20 2026-08-17 S14-R4; renamed to Labor Delta per SV-9071)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4474,37 +4464,90 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>CSV export repeats the PDF header's Product Type and Locations filter lines</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SBC — Exports</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Sales By Customer report is open with at least one filter narrowed (for example a chosen date/scope and one or more locations) so the PDF header would show more than one filter line.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the report as a PDF and read the filter-summary lines in its header area.
+2. Download the report as a CSV and open it in a plain text editor or spreadsheet.
+3. Compare the leading rows of the CSV (above the column-header row) with the PDF header lines.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1. The CSV carries the same filter-summary lines as the PDF header - the date range, the "Product Type: {value}" line, and the "Locations:" line - each as a leading metadata row above the column-header row.
+2. The lines appear verbatim (the same wording) and in the same order as in the PDF header.
+3. A CSV saved or forwarded later is never ambiguous about which filters produced it: every filter the PDF header names is present in the CSV.
+4. Note for the tester: this is the suite-wide rule that the CSV must name the same filters as the PDF. If your report shows no narrowed filters, widen or narrow one so at least one filter line appears, then compare again.
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 20 (S14-R13a), both read on 17 August 2026. S14-R13a is the suite-wide rule (added 2026-08-12, SV-9283) that the CSV carries every filter-summary line the PDF header names.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>SV-8612 (SBC spec v20 2026-08-17 S14-R13a; suite-wide CSV filter-summary rule SV-9283)</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
           <t>Filters; sort and visible columns are restored on the next visit</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in a browser you can revisit.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default date range, Product Type, location selection, a two-customer Customer selection, a non-default sort, and hide one column.
 2. Navigate away to another part of the application, then return to the report.
 3. Watch the report as it loads.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
@@ -4514,48 +4557,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Type-ahead search text, expansion state and scroll position are not saved</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Type a query in the Customer filter (without changing the selection), expand two customers, and scroll down the table.
 2. Reload the browser page.
 3. Check the Customer filter field, the rows, and the scroll position.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
@@ -4567,48 +4610,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid is dropped and falls back to default</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view that includes a specific location selection.
 2. An administrator then removes your access to that location (restore afterwards).</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Return to the report after the access change.
 2. Read the location filter and the report data.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
@@ -4623,47 +4666,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8966)</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>The saved view is specific to this report and does not affect any other report</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. You have set a distinctive saved view on Sales By Customer (for example Last Year + Parts only).</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Open another report in the Reports suite and read its filters.
 2. Return to Sales By Customer.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
@@ -4673,49 +4716,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>With no saved view every setting uses its own default</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Clear the browser's site data for the application (or use a fresh browser profile).
 2. You open the report by its plain address with no date range in the page link.
 3. You are working in a known active location (check the application's location switcher).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Open the Sales By Customer report.
 2. Read every filter, the sort, and the visible columns.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
@@ -4729,48 +4772,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>When a saved view and a page-link range clash the saved view wins</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You have a saved view with a known date range (for example Last Month).
 2. You have a page link carrying a DIFFERENT date range (for example This Year), captured earlier.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Open the report using the link with the different range.
 2. Read the date range picker.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
@@ -4781,48 +4824,48 @@
 </t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Customer filter restore: all-customers stays all; an id set is intersected</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>SBC — Saved View &amp; Persistence</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: leave the report in the all-customers state, then seed a NEW ZZAUTOTEST customer with an invoice in range.
 2. Scenario B: leave the report with two specific customers selected, then remove one of those customers' matching data (or shift the range so one no longer matches).</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: return to the report and check the filter state and rows.
 2. Scenario B: return to the report and check the selection and rows.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
@@ -4833,42 +4876,42 @@
 </t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Empty state shows in the table body; toolbar interactive; kept selection returns</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data on screen.
 2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Set a date range that contains no invoices (for example a Custom range over a quiet week far back).
 2. Read the table body and try each toolbar control.
@@ -4877,7 +4920,7 @@
 5. Narrow the Customer filter to specific customers, change the date range so none of them have data, read the table and the filter, then change the range back.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
@@ -4891,48 +4934,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>A failed data fetch shows the error toast which fades after 5 seconds</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>SBC — Empty &amp; Edge States</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. You can interrupt the network (browser dev tools offline mode).
 2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Go offline, then open the report (or change a filter to force a re-fetch).
 2. Read the toast and time how long it stays.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
@@ -4942,41 +4985,41 @@
 AUTOMATION: HOLD - a failing data fetch cannot be forced from the application</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-8582 (SBC spec §7 User Feedback Summary — the data-fetch error toast; CROSS-CUTTING: the SBC spec carries no error-state story of its own so the epic key is used deliberately)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Page and toolbar match the suite theme in padding; surface and alignment</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
 2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
@@ -4985,7 +5028,7 @@
 5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
@@ -5006,49 +5049,49 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Row surfaces alternate by tree level; header and totals rows stay white</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
 2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the background of the header cells, a customer row, an asset row, an invoice row, and the totals row.
 2. Check the pinned Subtotal cell's background on each row type.
 3. Check the tree indentation levels.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
@@ -5065,47 +5108,47 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8965)</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Dark mode darkens every surface while the PDF always renders light</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>SBC — Visual Conformance</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. You can switch the application to dark mode.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Switch to dark mode and review the page background, toolbar, header cells, customer rows, asset/invoice rows, and totals row.
 2. While still in dark mode, download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
         